--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -463,30 +463,30 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>323</v>
+        <v>410</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>IT</t>
         </is>
       </c>
     </row>
@@ -495,30 +495,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>322</v>
+        <v>376</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>322</v>
+        <v>376</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>302</v>
+        <v>376</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>302</v>
+        <v>356</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>302</v>
+        <v>356</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>302</v>
+        <v>355</v>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>282</v>
+        <v>323</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>282</v>
+        <v>322</v>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>282</v>
+        <v>322</v>
       </c>
       <c r="C11" t="n">
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -783,30 +783,30 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>281</v>
+        <v>315</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Panaf</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>Panaff</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -815,30 +815,30 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>262</v>
+        <v>302</v>
       </c>
       <c r="C13" t="n">
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -847,25 +847,25 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Panaf</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Panaff</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -879,30 +879,30 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>233</v>
+        <v>280</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>WIL1610</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -911,30 +911,30 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>206</v>
+        <v>280</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>IT</t>
         </is>
       </c>
     </row>
@@ -943,30 +943,30 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>206</v>
+        <v>280</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -975,30 +975,30 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>206</v>
+        <v>260</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1007,30 +1007,30 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>206</v>
+        <v>260</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liliane </t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>LilianeB</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1039,122 +1039,118 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>206</v>
+        <v>259</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
         <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>MatuRenard</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>206</v>
+        <v>259</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Liliuus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>186</v>
+        <v>259</v>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>Ppo28</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>186</v>
+        <v>239</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1163,30 +1159,30 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>186</v>
+        <v>239</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>Devilrock95</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1195,25 +1191,25 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>186</v>
+        <v>239</v>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1227,53 +1223,57 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>185</v>
+        <v>239</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>Cleem22</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>185</v>
+        <v>239</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1287,30 +1287,30 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>185</v>
+        <v>239</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>Maruyama</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1319,53 +1319,57 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>185</v>
+        <v>239</v>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ppo28</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Leandrocp</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>166</v>
+        <v>239</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1379,30 +1383,30 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>165</v>
+        <v>239</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>chaychaychay</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1415,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>165</v>
+        <v>233</v>
       </c>
       <c r="C32" t="n">
         <v>2</v>
@@ -1420,21 +1424,21 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>William</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Devilrock95</t>
+          <t>WIL1610</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1443,30 +1447,30 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>165</v>
+        <v>219</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Erwan</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>Erwan#4G91X</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1475,25 +1479,25 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>165</v>
+        <v>219</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>GLR_PRIME</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1507,7 +1511,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>165</v>
+        <v>212</v>
       </c>
       <c r="C35" t="n">
         <v>2</v>
@@ -1516,21 +1520,21 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Loïc</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Exia95</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1543,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>165</v>
+        <v>211</v>
       </c>
       <c r="C36" t="n">
         <v>2</v>
@@ -1548,16 +1552,16 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Maruyama</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1571,30 +1575,30 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>165</v>
+        <v>206</v>
       </c>
       <c r="C37" t="n">
         <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
+          <t>dian-bgt</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1603,30 +1607,30 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>165</v>
+        <v>206</v>
       </c>
       <c r="C38" t="n">
         <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t xml:space="preserve">Liliane </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Marion1822</t>
+          <t>LilianeB</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1635,62 +1639,58 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>165</v>
+        <v>206</v>
       </c>
       <c r="C39" t="n">
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Marilena</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>GOAT#UE2WM8M9</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="C40" t="n">
         <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>Romain_JO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1699,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>145</v>
+        <v>191</v>
       </c>
       <c r="C41" t="n">
         <v>2</v>
@@ -1708,21 +1708,21 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Erwan</t>
+          <t>Jérémy</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Erwan#4G91X</t>
+          <t>JeremFZ</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1731,30 +1731,30 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>145</v>
+        <v>190</v>
       </c>
       <c r="C42" t="n">
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>GLR_PRIME</t>
+          <t>AudreyB225</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1763,30 +1763,30 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>145</v>
+        <v>186</v>
       </c>
       <c r="C43" t="n">
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cécile</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ceciledp</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1795,30 +1795,30 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>145</v>
+        <v>186</v>
       </c>
       <c r="C44" t="n">
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuzo697</t>
+          <t>YassineZ95</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>IT</t>
         </is>
       </c>
     </row>
@@ -1827,30 +1827,30 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>138</v>
+        <v>185</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Loïc</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Exia95</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1859,30 +1859,30 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Antonio Moctezuma</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>abihuts</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1891,30 +1891,30 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>137</v>
+        <v>170</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1923,30 +1923,30 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>117</v>
+        <v>166</v>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Romain J</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1955,30 +1955,30 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>117</v>
+        <v>165</v>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Jérémy</t>
+          <t>Marilena</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>JeremFZ</t>
+          <t>GOAT#UE2WM8M9</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1987,30 +1987,30 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Cécile</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>AudreyB225</t>
+          <t>Ceciledp</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2019,10 +2019,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>98</v>
+        <v>145</v>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -2032,17 +2032,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Antonio Moctezuma</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>abihuts</t>
+          <t>Fuzo697</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2051,25 +2051,25 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>96</v>
+        <v>143</v>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Brieuc</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>Yebri</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2083,30 +2083,30 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>96</v>
+        <v>143</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2115,30 +2115,30 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Brieuc</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Yebri</t>
+          <t>EmyEnzo</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2147,30 +2147,30 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Priscilla</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Priscilla#4LCAF</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2179,30 +2179,30 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Juliie</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>Pipou931</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2211,94 +2211,86 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>EmyEnzo</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>Farah_One</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Priscilla</t>
+          <t>François</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Priscilla#4LCAF</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" t="n">
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Juliie</t>
+          <t>Selver</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pipou931</t>
+          <t>Seesee</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2307,25 +2299,25 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2339,58 +2331,62 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Farah_One</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>C4M</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62" t="n">
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ibra</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>PacoSarra</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2399,30 +2395,30 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>MPP_FMARTY</t>
+          <t>Elisewiss</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2431,30 +2427,30 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Soraya</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>Soraya-Y</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2463,39 +2459,35 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Seesee</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
@@ -2504,21 +2496,21 @@
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2527,25 +2519,25 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>C4M</t>
+          <t>Timy</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2559,30 +2551,30 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>JEVAISGAGNER10</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2591,30 +2583,30 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Elise</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Elisewiss</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2623,30 +2615,30 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Soraya</t>
+          <t>Léa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Soraya-Y</t>
+          <t>LeaBrd</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2655,90 +2647,90 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>davidd23</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1993ahm</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>Nonito20</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mélissa</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>PavelMel</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2747,30 +2739,30 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>Kolas</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2779,25 +2771,25 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Laetitia</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Timy</t>
+          <t>Laetice2020</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -2811,25 +2803,25 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>JEVAISGAGNER10</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -2843,30 +2835,30 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Lison</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>Lyzone</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2875,25 +2867,25 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Léa</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>LeaBrd</t>
+          <t>Melissagzb</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -2907,58 +2899,62 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>davidd23</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+          <t>Marie__92</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>K_Marp</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2967,30 +2963,30 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Cindie</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Cindie_JJA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2999,30 +2995,30 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3031,30 +3027,30 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Camss</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3063,94 +3059,86 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>goat</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SabC1</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Kolas</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>Camillewbl</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Killian</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>KIKS999</t>
+          <t>Emma_Noel</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3159,30 +3147,30 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Laetitia</t>
+          <t>lea</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Laetice2020</t>
+          <t>RBTL</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3191,39 +3179,35 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D88" t="n">
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>MxKnight</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>compta</t>
-        </is>
-      </c>
+          <t>A-MOE</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="C89" t="n">
         <v>1</v>
@@ -3232,21 +3216,21 @@
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3239,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="C90" t="n">
         <v>1</v>
@@ -3264,30 +3248,26 @@
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>romain</t>
+          <t>Brick</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>RomainLect</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="C91" t="n">
         <v>1</v>
@@ -3296,53 +3276,49 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lison</t>
+          <t>ousmane</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lyzone</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C92" t="n">
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3351,30 +3327,30 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C93" t="n">
         <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Marie__92</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3383,30 +3359,30 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C94" t="n">
         <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Ibra</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>K_Marp</t>
+          <t>PacoSarra</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3415,30 +3391,30 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C95" t="n">
         <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cindie</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cindie_JJA</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3447,30 +3423,30 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C96" t="n">
         <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3488,21 +3464,21 @@
         <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>Mélissa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>PavelMel</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3520,21 +3496,21 @@
         <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3552,21 +3528,21 @@
         <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>Teddbear</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>IT</t>
         </is>
       </c>
     </row>
@@ -3584,19 +3560,23 @@
         <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>goat</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>goat#AD6GS</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>Camss</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -3612,19 +3592,23 @@
         <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Camillewbl</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>SabC1</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -3640,21 +3624,21 @@
         <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Killian</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Emma_Noel</t>
+          <t>KIKS999</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3672,21 +3656,21 @@
         <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sab_M45</t>
+          <t>MxKnight</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3704,21 +3688,21 @@
         <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>romain</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Valentine___</t>
+          <t>RomainLect</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>IT</t>
         </is>
       </c>
     </row>
@@ -3736,21 +3720,21 @@
         <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>lea</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>RBTL</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3768,29 +3752,33 @@
         <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>A-MOE</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr"/>
+          <t>Daviddesco1</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
@@ -3800,45 +3788,49 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>BrickXVI</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+          <t>Sab_M45</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Damien</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>PANENKANY</t>
+          <t>Valentine___</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3856,19 +3848,23 @@
         <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>ousmane</t>
+          <t>Damien</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Taylor2901</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr"/>
+          <t>PANENKANY</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -3884,7 +3880,7 @@
         <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>

--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -1060,7 +1060,11 @@
           <t>MatuRenard</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1120,7 +1124,11 @@
           <t>Ppo28</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2232,7 +2240,11 @@
           <t>Farah_One</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2668,7 +2680,11 @@
           <t>davidd23</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3108,7 +3124,11 @@
           <t>Camillewbl</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3200,7 +3220,11 @@
           <t>A-MOE</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -3892,7 +3916,11 @@
           <t>MT35T</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>410</v>
+        <v>443</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>376</v>
+        <v>409</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,16 +527,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>376</v>
+        <v>409</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -559,16 +559,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>376</v>
+        <v>409</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>356</v>
+        <v>405</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -623,16 +623,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>356</v>
+        <v>389</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -655,16 +655,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>323</v>
+        <v>365</v>
       </c>
       <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
         <v>2</v>
       </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>322</v>
+        <v>356</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>322</v>
+        <v>356</v>
       </c>
       <c r="C11" t="n">
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -783,30 +783,30 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>315</v>
+        <v>355</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Panaf</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Panaff</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -815,30 +815,30 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>302</v>
+        <v>348</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Panaf</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Panaff</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -847,30 +847,30 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>282</v>
+        <v>335</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -879,16 +879,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>280</v>
+        <v>313</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -911,16 +911,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>280</v>
+        <v>313</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -943,16 +943,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>280</v>
+        <v>313</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -975,16 +975,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>260</v>
+        <v>293</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1007,16 +1007,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>260</v>
+        <v>293</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1039,16 +1039,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>259</v>
+        <v>292</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
         <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1071,16 +1071,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>259</v>
+        <v>292</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1103,16 +1103,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>259</v>
+        <v>292</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
         <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1135,16 +1135,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>239</v>
+        <v>272</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1167,16 +1167,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>239</v>
+        <v>272</v>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1199,30 +1199,30 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>239</v>
+        <v>272</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1231,25 +1231,25 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>239</v>
+        <v>272</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1263,30 +1263,30 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>239</v>
+        <v>272</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Maruyama</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1295,25 +1295,25 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>239</v>
+        <v>272</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Maruyama</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1327,30 +1327,30 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>239</v>
+        <v>272</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1359,30 +1359,30 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>239</v>
+        <v>272</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Marion1822</t>
+          <t>chaychaychay</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="C31" t="n">
         <v>3</v>
@@ -1400,21 +1400,21 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>William</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>WIL1610</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1423,30 +1423,30 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Erwan</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>WIL1610</t>
+          <t>Erwan#4G91X</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1455,30 +1455,30 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>219</v>
+        <v>252</v>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Erwan</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Erwan#4G91X</t>
+          <t>GLR_PRIME</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1487,30 +1487,30 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="C34" t="n">
         <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Loïc</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>GLR_PRIME</t>
+          <t>Exia95</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1519,30 +1519,30 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D35" t="n">
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Loïc</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Exia95</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1551,30 +1551,30 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>211</v>
+        <v>239</v>
       </c>
       <c r="C36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" t="n">
         <v>2</v>
       </c>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
       <c r="E36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>dian-bgt</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1583,25 +1583,25 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>206</v>
+        <v>239</v>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
         <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t xml:space="preserve">Liliane </t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
+          <t>LilianeB</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1615,76 +1615,76 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>206</v>
+        <v>239</v>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
         <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liliane </t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>LilianeB</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>206</v>
+        <v>239</v>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Ninaaaa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>191</v>
+        <v>224</v>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1707,16 +1707,16 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>191</v>
+        <v>224</v>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1739,16 +1739,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>190</v>
+        <v>223</v>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>186</v>
+        <v>219</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1803,30 +1803,30 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>186</v>
+        <v>218</v>
       </c>
       <c r="C44" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" t="n">
         <v>2</v>
       </c>
-      <c r="D44" t="n">
-        <v>1</v>
-      </c>
       <c r="E44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1835,62 +1835,58 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>François</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>172</v>
+        <v>206</v>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Antonio Moctezuma</t>
+          <t>Léa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>abihuts</t>
+          <t>LeaBrd</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1899,30 +1895,30 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>170</v>
+        <v>206</v>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1931,30 +1927,30 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>166</v>
+        <v>206</v>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Emma_Noel</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1963,30 +1959,30 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>165</v>
+        <v>206</v>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Marilena</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>GOAT#UE2WM8M9</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1995,25 +1991,25 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cécile</t>
+          <t>Antonio Moctezuma</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ceciledp</t>
+          <t>abihuts</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2027,30 +2023,30 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>145</v>
+        <v>203</v>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuzo697</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2059,30 +2055,30 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>143</v>
+        <v>198</v>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brieuc</t>
+          <t>Marilena</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Yebri</t>
+          <t>GOAT#UE2WM8M9</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2087,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>143</v>
+        <v>186</v>
       </c>
       <c r="C53" t="n">
         <v>2</v>
@@ -2100,21 +2096,21 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>YassineZ95</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2123,25 +2119,25 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>143</v>
+        <v>178</v>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
         <v>4</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>EmyEnzo</t>
+          <t>Fuzo697</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2155,30 +2151,30 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Priscilla</t>
+          <t>Brieuc</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Priscilla#4LCAF</t>
+          <t>Yebri</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2187,30 +2183,30 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D56" t="n">
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Juliie</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pipou931</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2219,30 +2215,30 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Farah_One</t>
+          <t>EmyEnzo</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2251,58 +2247,62 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Priscilla</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Francisco93</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Priscilla#4LCAF</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D59" t="n">
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t>Juliie</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Seesee</t>
+          <t>Pipou931</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2311,30 +2311,30 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>Farah_One</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2343,30 +2343,30 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D61" t="n">
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Selver</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>C4M</t>
+          <t>Seesee</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2375,25 +2375,25 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2407,30 +2407,30 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D63" t="n">
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Elise</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Elisewiss</t>
+          <t>C4M</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2439,30 +2439,30 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D64" t="n">
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Soraya</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Soraya-Y</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2471,58 +2471,62 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D65" t="n">
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1993ahm</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>Elisewiss</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>137</v>
+        <v>176</v>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D66" t="n">
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Soraya</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>Soraya-Y</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2531,39 +2535,35 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>123</v>
+        <v>176</v>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Timy</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="C68" t="n">
         <v>2</v>
@@ -2572,21 +2572,21 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>JEVAISGAGNER10</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="C69" t="n">
         <v>2</v>
@@ -2604,21 +2604,21 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2627,30 +2627,30 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Léa</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>LeaBrd</t>
+          <t>Timy</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2659,30 +2659,30 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>JEVAISGAGNER10</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2691,30 +2691,30 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2723,30 +2723,30 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2755,25 +2755,25 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Kolas</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -2787,30 +2787,30 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Laetitia</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Laetice2020</t>
+          <t>Kolas</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2819,30 +2819,30 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Laetitia</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>Laetice2020</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2851,16 +2851,16 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -2883,16 +2883,16 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -2915,16 +2915,16 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -2947,16 +2947,16 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -2979,16 +2979,16 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3011,16 +3011,16 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3075,16 +3075,16 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -3103,16 +3103,16 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3135,25 +3135,25 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>lea</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Emma_Noel</t>
+          <t>RBTL</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3167,7 +3167,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="C87" t="n">
         <v>2</v>
@@ -3176,21 +3176,21 @@
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>lea</t>
+          <t>Cécile</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>RBTL</t>
+          <t>Ceciledp</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3199,30 +3199,30 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3231,25 +3231,25 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3263,16 +3263,16 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -3291,16 +3291,16 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -3319,16 +3319,16 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
         <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -3351,16 +3351,16 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D93" t="n">
         <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -3383,16 +3383,16 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D94" t="n">
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -3415,16 +3415,16 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
         <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -3447,25 +3447,25 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -3479,30 +3479,30 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mélissa</t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>PavelMel</t>
+          <t>Teddbear</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3511,30 +3511,30 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>SabC1</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3543,30 +3543,30 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t>Killian</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>KIKS999</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3575,30 +3575,30 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Camss</t>
+          <t>MxKnight</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3607,30 +3607,30 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>romain</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SabC1</t>
+          <t>RomainLect</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3639,30 +3639,30 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Killian</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>KIKS999</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3671,30 +3671,30 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="C103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>MxKnight</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3703,10 +3703,10 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="C104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D104" t="n">
         <v>0</v>
@@ -3716,17 +3716,17 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>romain</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>RomainLect</t>
+          <t>Sab_M45</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3735,30 +3735,30 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="C105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>Valentine___</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3767,30 +3767,30 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C106" t="n">
         <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3808,21 +3808,21 @@
         <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Mélissa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sab_M45</t>
+          <t>PavelMel</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3840,21 +3840,21 @@
         <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Valentine___</t>
+          <t>Camss</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3863,16 +3863,16 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="C109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -3895,16 +3895,16 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="C110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>

--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -463,10 +463,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>443</v>
+        <v>410</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -495,10 +495,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -508,17 +508,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -527,10 +527,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>409</v>
+        <v>376</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
@@ -540,17 +540,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -559,10 +559,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>409</v>
+        <v>376</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
@@ -572,17 +572,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -591,25 +591,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>405</v>
+        <v>376</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -623,10 +623,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>389</v>
+        <v>356</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -636,17 +636,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>388</v>
+        <v>356</v>
       </c>
       <c r="C8" t="n">
         <v>4</v>
@@ -668,17 +668,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -719,10 +719,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>356</v>
+        <v>323</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
@@ -732,17 +732,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>356</v>
+        <v>322</v>
       </c>
       <c r="C11" t="n">
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
         <v>5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -783,10 +783,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>355</v>
+        <v>322</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
         <v>3</v>
@@ -815,10 +815,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>348</v>
+        <v>315</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -847,25 +847,25 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>335</v>
+        <v>307</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -879,10 +879,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
@@ -892,17 +892,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -911,10 +911,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
@@ -924,12 +924,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -943,25 +943,25 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>313</v>
+        <v>284</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -975,10 +975,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
@@ -988,12 +988,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1007,30 +1007,30 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1039,10 +1039,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
         <v>2</v>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1071,10 +1071,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
         <v>2</v>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1103,30 +1103,30 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>292</v>
+        <v>260</v>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
         <v>5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1135,10 +1135,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
@@ -1148,17 +1148,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1167,30 +1167,30 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
         <v>5</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Devilrock95</t>
+          <t>MatuRenard</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1199,25 +1199,25 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
         <v>5</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1231,30 +1231,30 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
         <v>5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1263,10 +1263,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>272</v>
+        <v>239</v>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Maruyama</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1295,10 +1295,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>272</v>
+        <v>239</v>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
         <v>1</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
+          <t>Devilrock95</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1327,10 +1327,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>272</v>
+        <v>239</v>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
         <v>1</v>
@@ -1340,17 +1340,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Marion1822</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1359,10 +1359,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>272</v>
+        <v>239</v>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
         <v>1</v>
@@ -1372,17 +1372,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>266</v>
+        <v>239</v>
       </c>
       <c r="C31" t="n">
         <v>3</v>
@@ -1404,17 +1404,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>WIL1610</t>
+          <t>Maruyama</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1423,25 +1423,25 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
         <v>5</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Erwan</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Erwan#4G91X</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1455,30 +1455,30 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
         <v>5</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>GLR_PRIME</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="C34" t="n">
         <v>3</v>
@@ -1500,17 +1500,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Loïc</t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Exia95</t>
+          <t>chaychaychay</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1519,10 +1519,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
         <v>1</v>
@@ -1532,17 +1532,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>William</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>WIL1610</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1551,30 +1551,30 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="C36" t="n">
         <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>5</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Erwan</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
+          <t>Erwan#4G91X</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1583,25 +1583,25 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="C37" t="n">
         <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
         <v>5</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liliane </t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>LilianeB</t>
+          <t>GLR_PRIME</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1615,38 +1615,42 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>239</v>
+        <v>212</v>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
         <v>5</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Loïc</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Exia95</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
         <v>1</v>
@@ -1656,17 +1660,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1675,30 +1679,30 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
         <v>5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Romain J</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
+          <t>dian-bgt</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1707,25 +1711,25 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
         <v>5</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jérémy</t>
+          <t xml:space="preserve">Liliane </t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>JeremFZ</t>
+          <t>LilianeB</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1739,62 +1743,58 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
         <v>5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>AudreyB225</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>compta</t>
-        </is>
-      </c>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
         <v>5</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>Romain_JO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1803,25 +1803,25 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>5</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Jérémy</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>JeremFZ</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1835,10 +1835,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
         <v>1</v>
@@ -1848,45 +1848,49 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Francisco93</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>AudreyB225</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
         <v>5</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Léa</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>LeaBrd</t>
+          <t>Camss</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1895,10 +1899,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
         <v>1</v>
@@ -1908,17 +1912,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1927,10 +1931,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
         <v>1</v>
@@ -1940,17 +1944,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Emma_Noel</t>
+          <t>YassineZ95</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1959,25 +1963,25 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
         <v>5</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -1991,10 +1995,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>205</v>
+        <v>172</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -2023,10 +2027,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>203</v>
+        <v>170</v>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -2055,10 +2059,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
         <v>1</v>
@@ -2087,30 +2091,30 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="C53" t="n">
         <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
         <v>5</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Cécile</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>Ceciledp</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2119,10 +2123,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
@@ -2151,10 +2155,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
         <v>1</v>
@@ -2183,10 +2187,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
         <v>1</v>
@@ -2215,10 +2219,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
         <v>1</v>
@@ -2247,10 +2251,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
         <v>1</v>
@@ -2279,10 +2283,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D59" t="n">
         <v>1</v>
@@ -2311,10 +2315,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
         <v>1</v>
@@ -2343,10 +2347,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
         <v>1</v>
@@ -2356,29 +2360,25 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t>François</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Seesee</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D62" t="n">
         <v>1</v>
@@ -2388,17 +2388,17 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Selver</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>Seesee</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2407,10 +2407,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
         <v>1</v>
@@ -2420,12 +2420,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>C4M</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2439,10 +2439,10 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
         <v>1</v>
@@ -2452,12 +2452,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>C4M</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2471,10 +2471,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
         <v>1</v>
@@ -2484,17 +2484,17 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Elise</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Elisewiss</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2503,10 +2503,10 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
         <v>1</v>
@@ -2516,12 +2516,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Soraya</t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Soraya-Y</t>
+          <t>Elisewiss</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2535,10 +2535,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
         <v>1</v>
@@ -2548,54 +2548,54 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Soraya</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1993ahm</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>Soraya-Y</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="C68" t="n">
         <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
         <v>5</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>compta</t>
-        </is>
-      </c>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>162</v>
+        <v>123</v>
       </c>
       <c r="C69" t="n">
         <v>2</v>
@@ -2608,12 +2608,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>Timy</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -2627,10 +2627,10 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
@@ -2640,17 +2640,17 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Timy</t>
+          <t>JEVAISGAGNER10</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2659,10 +2659,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
@@ -2672,17 +2672,17 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>JEVAISGAGNER10</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2691,10 +2691,10 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -2704,17 +2704,17 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Léa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>LeaBrd</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2723,10 +2723,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
@@ -2755,10 +2755,10 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
@@ -2787,10 +2787,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -2819,10 +2819,10 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -2851,10 +2851,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
@@ -2864,17 +2864,17 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lison</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lyzone</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2883,10 +2883,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -2896,17 +2896,17 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Lison</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>Lyzone</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2915,10 +2915,10 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -2928,12 +2928,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Marie__92</t>
+          <t>Melissagzb</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -2947,10 +2947,10 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
@@ -2960,17 +2960,17 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>K_Marp</t>
+          <t>Marie__92</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2979,10 +2979,10 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -2992,12 +2992,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cindie</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cindie_JJA</t>
+          <t>K_Marp</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3011,10 +3011,10 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
@@ -3024,17 +3024,17 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Cindie</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>Cindie_JJA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3043,10 +3043,10 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
@@ -3056,17 +3056,17 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3075,10 +3075,10 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -3088,25 +3088,29 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>goat</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>goat#AD6GS</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>GOAT#UE4U8KA6</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
@@ -3116,29 +3120,25 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>goat</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Camillewbl</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -3148,12 +3148,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>lea</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>RBTL</t>
+          <t>Camillewbl</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3167,7 +3167,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="C87" t="n">
         <v>2</v>
@@ -3180,17 +3180,17 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cécile</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ceciledp</t>
+          <t>Emma_Noel</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3199,30 +3199,30 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
         <v>5</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>lea</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>RBTL</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3263,10 +3263,10 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
@@ -3276,25 +3276,29 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>BrickXVI</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>Davido#4BZ54</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
@@ -3304,12 +3308,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ousmane</t>
+          <t>Brick</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Taylor2901</t>
+          <t>BrickXVI</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
@@ -3319,42 +3323,38 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
         <v>5</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>ousmane</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
         <v>1</v>
@@ -3364,17 +3364,17 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3383,10 +3383,10 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
         <v>1</v>
@@ -3396,17 +3396,17 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ibra</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>PacoSarra</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3415,10 +3415,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
         <v>1</v>
@@ -3428,12 +3428,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Ibra</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>PacoSarra</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -3447,30 +3447,30 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="C96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E96" t="n">
         <v>5</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3479,30 +3479,30 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="C97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E97" t="n">
         <v>5</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3511,10 +3511,10 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="C98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
@@ -3524,17 +3524,17 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Mélissa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SabC1</t>
+          <t>PavelMel</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3543,10 +3543,10 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="C99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
@@ -3556,17 +3556,17 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Killian</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>KIKS999</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3575,10 +3575,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="C100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -3588,17 +3588,17 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>MxKnight</t>
+          <t>Teddbear</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3607,10 +3607,10 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="C101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
@@ -3620,17 +3620,17 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>romain</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>RomainLect</t>
+          <t>SabC1</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3639,10 +3639,10 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="C102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
@@ -3652,17 +3652,17 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>Killian</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>KIKS999</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3671,10 +3671,10 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="C103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>
@@ -3684,17 +3684,17 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>MxKnight</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3703,30 +3703,30 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="C104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D104" t="n">
         <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>romain</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sab_M45</t>
+          <t>RomainLect</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3735,30 +3735,30 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Valentine___</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3767,30 +3767,30 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="C106" t="n">
         <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E106" t="n">
         <v>5</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3808,21 +3808,21 @@
         <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mélissa</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>PavelMel</t>
+          <t>Sab_M45</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3840,21 +3840,21 @@
         <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Camss</t>
+          <t>Valentine___</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3863,10 +3863,10 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
@@ -3895,10 +3895,10 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>

--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>410</v>
+        <v>552</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>400</v>
+        <v>542</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>376</v>
+        <v>498</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>376</v>
+        <v>497</v>
       </c>
       <c r="C5" t="n">
         <v>4</v>
@@ -568,21 +568,21 @@
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>376</v>
+        <v>457</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Panaf</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Panaff</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>356</v>
+        <v>444</v>
       </c>
       <c r="C7" t="n">
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>356</v>
+        <v>440</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>355</v>
+        <v>407</v>
       </c>
       <c r="C9" t="n">
         <v>3</v>
@@ -696,21 +696,21 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>Timy</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -719,25 +719,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>323</v>
+        <v>407</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>322</v>
+        <v>406</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -783,30 +783,30 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>322</v>
+        <v>402</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -815,30 +815,30 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>315</v>
+        <v>402</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Panaf</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Panaff</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -847,30 +847,30 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>307</v>
+        <v>381</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -879,30 +879,30 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>302</v>
+        <v>381</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -911,30 +911,30 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>298</v>
+        <v>381</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -943,30 +943,30 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>284</v>
+        <v>381</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -975,30 +975,30 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>282</v>
+        <v>381</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>chaychaychay</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1007,25 +1007,25 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>280</v>
+        <v>376</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
         <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1039,30 +1039,30 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>280</v>
+        <v>376</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
         <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1071,30 +1071,30 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>280</v>
+        <v>361</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>Maruyama</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1103,30 +1103,30 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>260</v>
+        <v>356</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1135,30 +1135,30 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>260</v>
+        <v>356</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>259</v>
+        <v>332</v>
       </c>
       <c r="C24" t="n">
         <v>3</v>
@@ -1176,21 +1176,21 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
+          <t>AudreyB225</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1199,30 +1199,30 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>259</v>
+        <v>323</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1231,30 +1231,30 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>259</v>
+        <v>322</v>
       </c>
       <c r="C26" t="n">
         <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>239</v>
+        <v>308</v>
       </c>
       <c r="C27" t="n">
         <v>3</v>
@@ -1272,21 +1272,21 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1295,30 +1295,30 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>239</v>
+        <v>307</v>
       </c>
       <c r="C28" t="n">
         <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Devilrock95</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1327,30 +1327,30 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>239</v>
+        <v>307</v>
       </c>
       <c r="C29" t="n">
         <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1359,30 +1359,30 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>239</v>
+        <v>302</v>
       </c>
       <c r="C30" t="n">
         <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1391,25 +1391,25 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>239</v>
+        <v>285</v>
       </c>
       <c r="C31" t="n">
         <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Maruyama</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1423,39 +1423,35 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>239</v>
+        <v>285</v>
       </c>
       <c r="C32" t="n">
         <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>François</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>239</v>
+        <v>282</v>
       </c>
       <c r="C33" t="n">
         <v>3</v>
@@ -1464,21 +1460,21 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Marion1822</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1487,30 +1483,30 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>239</v>
+        <v>280</v>
       </c>
       <c r="C34" t="n">
         <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1519,25 +1515,25 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>233</v>
+        <v>280</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>WIL1610</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1551,30 +1547,30 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>219</v>
+        <v>280</v>
       </c>
       <c r="C36" t="n">
         <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Erwan</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Erwan#4G91X</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1583,25 +1579,25 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>219</v>
+        <v>265</v>
       </c>
       <c r="C37" t="n">
         <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Brieuc</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>GLR_PRIME</t>
+          <t>Yebri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1615,30 +1611,30 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>212</v>
+        <v>265</v>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Loïc</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Exia95</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1647,25 +1643,25 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>211</v>
+        <v>265</v>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D39" t="n">
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>Kolas</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1679,25 +1675,25 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>206</v>
+        <v>265</v>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1711,30 +1707,30 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>206</v>
+        <v>265</v>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liliane </t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>LilianeB</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1743,90 +1739,90 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>206</v>
+        <v>265</v>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Soraya</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Soraya-Y</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>191</v>
+        <v>265</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Romain J</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>191</v>
+        <v>259</v>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Jérémy</t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>JeremFZ</t>
+          <t>MatuRenard</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1835,30 +1831,30 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>190</v>
+        <v>259</v>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>AudreyB225</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1867,30 +1863,30 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>190</v>
+        <v>259</v>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Camss</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1899,30 +1895,30 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>186</v>
+        <v>239</v>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>Devilrock95</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1931,30 +1927,30 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>186</v>
+        <v>239</v>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1963,30 +1959,30 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>185</v>
+        <v>233</v>
       </c>
       <c r="C49" t="n">
         <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>William</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>WIL1610</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1995,30 +1991,30 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>172</v>
+        <v>219</v>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Antonio Moctezuma</t>
+          <t>Erwan</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>abihuts</t>
+          <t>Erwan#4G91X</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2027,25 +2023,25 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>170</v>
+        <v>219</v>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>GLR_PRIME</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2059,30 +2055,30 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>165</v>
+        <v>218</v>
       </c>
       <c r="C52" t="n">
         <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Marilena</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>GOAT#UE2WM8M9</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2091,30 +2087,30 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>145</v>
+        <v>212</v>
       </c>
       <c r="C53" t="n">
         <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cécile</t>
+          <t>Loïc</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ceciledp</t>
+          <t>Exia95</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2123,30 +2119,30 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>145</v>
+        <v>211</v>
       </c>
       <c r="C54" t="n">
         <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuzo697</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2155,7 +2151,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>143</v>
+        <v>211</v>
       </c>
       <c r="C55" t="n">
         <v>2</v>
@@ -2164,21 +2160,21 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brieuc</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Yebri</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2187,30 +2183,30 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>143</v>
+        <v>206</v>
       </c>
       <c r="C56" t="n">
         <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>dian-bgt</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2219,30 +2215,30 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>143</v>
+        <v>206</v>
       </c>
       <c r="C57" t="n">
         <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t xml:space="preserve">Liliane </t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>EmyEnzo</t>
+          <t>LilianeB</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2251,39 +2247,35 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>143</v>
+        <v>206</v>
       </c>
       <c r="C58" t="n">
         <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Priscilla</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Priscilla#4LCAF</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>143</v>
+        <v>191</v>
       </c>
       <c r="C59" t="n">
         <v>2</v>
@@ -2292,21 +2284,21 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Juliie</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pipou931</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2315,30 +2307,30 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>143</v>
+        <v>191</v>
       </c>
       <c r="C60" t="n">
         <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Farah_One</t>
+          <t>Romain_JO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2347,58 +2339,62 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>143</v>
+        <v>191</v>
       </c>
       <c r="C61" t="n">
         <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Jérémy</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Francisco93</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>JeremFZ</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>143</v>
+        <v>190</v>
       </c>
       <c r="C62" t="n">
         <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Seesee</t>
+          <t>Camss</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2403,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>143</v>
+        <v>186</v>
       </c>
       <c r="C63" t="n">
         <v>2</v>
@@ -2416,21 +2412,21 @@
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>YassineZ95</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2439,25 +2435,25 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="C64" t="n">
         <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Antonio Moctezuma</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>C4M</t>
+          <t>abihuts</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2471,30 +2467,30 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="C65" t="n">
         <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2503,30 +2499,30 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="C66" t="n">
         <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Elise</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Elisewiss</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2535,30 +2531,30 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="C67" t="n">
         <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Soraya</t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Soraya-Y</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2567,7 +2563,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="C68" t="n">
         <v>2</v>
@@ -2576,26 +2572,30 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Marilena</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>1993ahm</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>GOAT#UE2WM8M9</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="C69" t="n">
         <v>2</v>
@@ -2604,16 +2604,16 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Cécile</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Timy</t>
+          <t>Ceciledp</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -2627,7 +2627,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="C70" t="n">
         <v>2</v>
@@ -2640,17 +2640,17 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>JEVAISGAGNER10</t>
+          <t>Fuzo697</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2659,30 +2659,30 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="C71" t="n">
         <v>2</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>EmyEnzo</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2691,25 +2691,25 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="C72" t="n">
         <v>2</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Léa</t>
+          <t>Priscilla</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>LeaBrd</t>
+          <t>Priscilla#4LCAF</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -2723,25 +2723,25 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="C73" t="n">
         <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Juliie</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>Pipou931</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -2755,30 +2755,30 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="C74" t="n">
         <v>2</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Farah_One</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2787,25 +2787,25 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="C75" t="n">
         <v>2</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Selver</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Kolas</t>
+          <t>Seesee</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -2819,25 +2819,25 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="C76" t="n">
         <v>2</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Laetitia</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Laetice2020</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -2851,30 +2851,30 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="C77" t="n">
         <v>2</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>C4M</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2883,25 +2883,25 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="C78" t="n">
         <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lison</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lyzone</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -2915,30 +2915,30 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="C79" t="n">
         <v>2</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>Elisewiss</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2956,21 +2956,21 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Marie__92</t>
+          <t>JEVAISGAGNER10</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2988,21 +2988,21 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Léa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>K_Marp</t>
+          <t>LeaBrd</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3020,21 +3020,21 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cindie</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cindie_JJA</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3052,16 +3052,16 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Laetitia</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>Laetice2020</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3084,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3116,19 +3116,23 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>goat</t>
+          <t>Lison</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>goat#AD6GS</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>Lyzone</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3144,16 +3148,16 @@
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Camillewbl</t>
+          <t>Melissagzb</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3176,16 +3180,16 @@
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Emma_Noel</t>
+          <t>Marie__92</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3208,21 +3212,21 @@
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>lea</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>RBTL</t>
+          <t>K_Marp</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3240,21 +3244,21 @@
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Cindie</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>Cindie_JJA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3263,118 +3267,122 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>goat</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>BrickXVI</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+          <t>Camillewbl</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ousmane</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Taylor2901</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
+          <t>Emma_Noel</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>lea</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>RBTL</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3383,25 +3391,25 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -3415,30 +3423,30 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>69</v>
+        <v>122</v>
       </c>
       <c r="C95" t="n">
         <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ibra</t>
+          <t>Damien</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>PacoSarra</t>
+          <t>PANENKANY</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3447,94 +3455,86 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C96" t="n">
         <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Brick</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C97" t="n">
         <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>ousmane</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C98" t="n">
         <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mélissa</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>PavelMel</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3543,30 +3543,30 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C99" t="n">
         <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Ibra</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>PacoSarra</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3575,30 +3575,30 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C100" t="n">
         <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3616,21 +3616,21 @@
         <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Mélissa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SabC1</t>
+          <t>PavelMel</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3648,21 +3648,21 @@
         <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Killian</t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>KIKS999</t>
+          <t>Teddbear</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3680,21 +3680,21 @@
         <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>MxKnight</t>
+          <t>SabC1</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3712,21 +3712,21 @@
         <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>romain</t>
+          <t>Killian</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>RomainLect</t>
+          <t>KIKS999</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3744,21 +3744,21 @@
         <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>MxKnight</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3776,21 +3776,21 @@
         <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>romain</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>RomainLect</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3808,16 +3808,16 @@
         <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sab_M45</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -3840,21 +3840,21 @@
         <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Valentine___</t>
+          <t>Sab_M45</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3863,30 +3863,30 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Damien</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>PANENKANY</t>
+          <t>Valentine___</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
         <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>

--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>552</v>
+        <v>596</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>542</v>
+        <v>586</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,16 +527,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>498</v>
+        <v>542</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -559,16 +559,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>497</v>
+        <v>541</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -591,16 +591,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>457</v>
+        <v>501</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>444</v>
+        <v>496</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>440</v>
+        <v>488</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>407</v>
+        <v>485</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Timy</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>407</v>
+        <v>483</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>406</v>
+        <v>451</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
@@ -760,21 +760,21 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -783,30 +783,30 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>402</v>
+        <v>450</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -815,16 +815,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>402</v>
+        <v>446</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -847,30 +847,30 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>381</v>
+        <v>440</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -879,30 +879,30 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>381</v>
+        <v>425</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -911,30 +911,30 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>381</v>
+        <v>425</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -943,30 +943,30 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>381</v>
+        <v>425</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Marion1822</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -975,30 +975,30 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>381</v>
+        <v>425</v>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1007,30 +1007,30 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>376</v>
+        <v>425</v>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
         <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>chaychaychay</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1039,30 +1039,30 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>376</v>
+        <v>420</v>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
         <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1071,30 +1071,30 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>361</v>
+        <v>420</v>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Maruyama</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1103,30 +1103,30 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>356</v>
+        <v>411</v>
       </c>
       <c r="C22" t="n">
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1135,30 +1135,30 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>356</v>
+        <v>407</v>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>Timy</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1167,30 +1167,30 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>332</v>
+        <v>401</v>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>AudreyB225</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1199,30 +1199,30 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>323</v>
+        <v>400</v>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1231,30 +1231,30 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>322</v>
+        <v>376</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>AudreyB225</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>308</v>
+        <v>367</v>
       </c>
       <c r="C27" t="n">
         <v>3</v>
@@ -1272,21 +1272,21 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1295,25 +1295,25 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>307</v>
+        <v>366</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1327,30 +1327,30 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>307</v>
+        <v>361</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Maruyama</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1359,25 +1359,25 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>302</v>
+        <v>356</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1391,30 +1391,30 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>285</v>
+        <v>346</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
         <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1423,53 +1423,57 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>285</v>
+        <v>343</v>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Francisco93</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Emilay</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>282</v>
+        <v>329</v>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1483,62 +1487,58 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>280</v>
+        <v>329</v>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
         <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>François</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>280</v>
+        <v>326</v>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1547,30 +1547,30 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>280</v>
+        <v>324</v>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1579,30 +1579,30 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>265</v>
+        <v>324</v>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brieuc</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Yebri</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1611,30 +1611,30 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>265</v>
+        <v>324</v>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1643,30 +1643,30 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>265</v>
+        <v>313</v>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Kolas</t>
+          <t>EmyEnzo</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1675,25 +1675,25 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>265</v>
+        <v>309</v>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D40" t="n">
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Brieuc</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>Yebri</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1707,30 +1707,30 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>265</v>
+        <v>309</v>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D41" t="n">
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1739,30 +1739,30 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>265</v>
+        <v>309</v>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D42" t="n">
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Soraya</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Soraya-Y</t>
+          <t>Kolas</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1771,90 +1771,90 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>265</v>
+        <v>309</v>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D43" t="n">
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1993ahm</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>JKInternational</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>259</v>
+        <v>309</v>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Reste du monde</t>
-        </is>
-      </c>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>259</v>
+        <v>308</v>
       </c>
       <c r="C45" t="n">
         <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1863,25 +1863,25 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>259</v>
+        <v>303</v>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
         <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>MatuRenard</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -1895,30 +1895,30 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>239</v>
+        <v>303</v>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Devilrock95</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1927,30 +1927,30 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>239</v>
+        <v>303</v>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1959,57 +1959,53 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>233</v>
+        <v>293</v>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>goat</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>WIL1610</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Reste du monde</t>
-        </is>
-      </c>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>219</v>
+        <v>283</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Erwan</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Erwan#4G91X</t>
+          <t>Devilrock95</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2023,25 +2019,25 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>219</v>
+        <v>283</v>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>GLR_PRIME</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2055,30 +2051,30 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>218</v>
+        <v>280</v>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>YassineZ95</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2087,30 +2083,30 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>212</v>
+        <v>277</v>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D53" t="n">
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Loïc</t>
+          <t>William</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Exia95</t>
+          <t>WIL1610</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2119,30 +2115,30 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>211</v>
+        <v>265</v>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Soraya</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>Soraya-Y</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2151,25 +2147,25 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>211</v>
+        <v>263</v>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Erwan</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>Erwan#4G91X</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2183,25 +2179,25 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>206</v>
+        <v>262</v>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2215,30 +2211,30 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>206</v>
+        <v>256</v>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liliane </t>
+          <t>Loïc</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>LilianeB</t>
+          <t>Exia95</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2247,58 +2243,62 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>206</v>
+        <v>255</v>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
         <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Krol#4R8XC</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>191</v>
+        <v>250</v>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
+          <t>dian-bgt</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2307,30 +2307,30 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>191</v>
+        <v>250</v>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Romain J</t>
+          <t xml:space="preserve">Liliane </t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
+          <t>LilianeB</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2339,57 +2339,53 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>191</v>
+        <v>250</v>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Jérémy</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>JeremFZ</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>190</v>
+        <v>249</v>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Camss</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2403,30 +2399,30 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>186</v>
+        <v>235</v>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>Romain_JO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2435,25 +2431,25 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>172</v>
+        <v>235</v>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Antonio Moctezuma</t>
+          <t>Jérémy</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>abihuts</t>
+          <t>JeremFZ</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2467,30 +2463,30 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>171</v>
+        <v>225</v>
       </c>
       <c r="C65" t="n">
         <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>Teddbear</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2499,25 +2495,25 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>171</v>
+        <v>219</v>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>GLR_PRIME</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2531,30 +2527,30 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>170</v>
+        <v>217</v>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>Emma_Noel</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2563,30 +2559,30 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>165</v>
+        <v>216</v>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Marilena</t>
+          <t>Antonio Moctezuma</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>GOAT#UE2WM8M9</t>
+          <t>abihuts</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2595,25 +2591,25 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>145</v>
+        <v>215</v>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Cécile</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ceciledp</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -2627,30 +2623,30 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuzo697</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2655,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>143</v>
+        <v>211</v>
       </c>
       <c r="C71" t="n">
         <v>2</v>
@@ -2668,21 +2664,21 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>EmyEnzo</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2691,30 +2687,30 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>143</v>
+        <v>209</v>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D72" t="n">
         <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Priscilla</t>
+          <t>Marilena</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Priscilla#4LCAF</t>
+          <t>GOAT#UE2WM8M9</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2723,25 +2719,25 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>143</v>
+        <v>190</v>
       </c>
       <c r="C73" t="n">
         <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Juliie</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pipou931</t>
+          <t>Camss</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -2755,30 +2751,30 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>143</v>
+        <v>189</v>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Farah_One</t>
+          <t>Fuzo697</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2787,30 +2783,30 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D75" t="n">
         <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t>Priscilla</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Seesee</t>
+          <t>Priscilla#4LCAF</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2819,25 +2815,25 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D76" t="n">
         <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Juliie</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>Pipou931</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -2851,30 +2847,30 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D77" t="n">
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Selver</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>C4M</t>
+          <t>Seesee</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2883,25 +2879,25 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -2915,30 +2911,30 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D79" t="n">
         <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Elise</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Elisewiss</t>
+          <t>C4M</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2947,30 +2943,30 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>123</v>
+        <v>187</v>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>JEVAISGAGNER10</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2979,30 +2975,30 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>123</v>
+        <v>187</v>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Léa</t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>LeaBrd</t>
+          <t>Elisewiss</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3007,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="C82" t="n">
         <v>2</v>
@@ -3020,16 +3016,16 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>SabC1</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3043,7 +3039,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>123</v>
+        <v>171</v>
       </c>
       <c r="C83" t="n">
         <v>2</v>
@@ -3052,21 +3048,21 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Laetitia</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Laetice2020</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3075,25 +3071,25 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>123</v>
+        <v>167</v>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>JEVAISGAGNER10</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3107,30 +3103,30 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>123</v>
+        <v>167</v>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lison</t>
+          <t>Léa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lyzone</t>
+          <t>LeaBrd</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3139,30 +3135,30 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>123</v>
+        <v>167</v>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Lison</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>Lyzone</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3171,25 +3167,25 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>123</v>
+        <v>167</v>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Marie__92</t>
+          <t>Melissagzb</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3203,30 +3199,30 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>123</v>
+        <v>167</v>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D88" t="n">
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>K_Marp</t>
+          <t>Marie__92</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3235,25 +3231,25 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>123</v>
+        <v>167</v>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cindie</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cindie_JJA</t>
+          <t>K_Marp</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3267,58 +3263,62 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>123</v>
+        <v>167</v>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>goat</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>goat#AD6GS</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>Camillewbl</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>123</v>
+        <v>167</v>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Camillewbl</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3327,7 +3327,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="C92" t="n">
         <v>2</v>
@@ -3336,16 +3336,16 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Damien</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Emma_Noel</t>
+          <t>PANENKANY</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3359,30 +3359,30 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>123</v>
+        <v>163</v>
       </c>
       <c r="C93" t="n">
         <v>2</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>lea</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>RBTL</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3391,30 +3391,30 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>123</v>
+        <v>163</v>
       </c>
       <c r="C94" t="n">
         <v>2</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E94" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3423,30 +3423,30 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Damien</t>
+          <t>Cécile</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>PANENKANY</t>
+          <t>Ceciledp</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3455,25 +3455,25 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>74</v>
+        <v>143</v>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>BrickXVI</t>
+          <t>Fa_One</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
@@ -3483,38 +3483,42 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>74</v>
+        <v>143</v>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>ousmane</t>
+          <t>Killian</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Taylor2901</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>KIKS999</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D98" t="n">
         <v>1</v>
@@ -3524,12 +3528,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Valentine___</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -3543,30 +3547,30 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ibra</t>
+          <t>Laetitia</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>PacoSarra</t>
+          <t>Laetice2020</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3575,30 +3579,30 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Cindie</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>Cindie_JJA</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3607,10 +3611,10 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
@@ -3620,12 +3624,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mélissa</t>
+          <t>lea</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>PavelMel</t>
+          <t>RBTL</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -3639,89 +3643,81 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t>Brick</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Teddbear</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Reste du monde</t>
-        </is>
-      </c>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="C103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>ousmane</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SabC1</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="C104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Killian</t>
+          <t>Ibra</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>KIKS999</t>
+          <t>PacoSarra</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -3735,30 +3731,30 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="C105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Mélissa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>MxKnight</t>
+          <t>PavelMel</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3767,30 +3763,30 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="C106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>romain</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>RomainLect</t>
+          <t>MxKnight</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3799,30 +3795,30 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="C107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>romain</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>RomainLect</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3831,25 +3827,25 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="C108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Sab_M45</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -3863,30 +3859,30 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="C109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Valentine___</t>
+          <t>Sab_M45</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3895,16 +3891,16 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="C110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>

--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>596</v>
+        <v>611</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>586</v>
+        <v>601</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,16 +527,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>542</v>
+        <v>557</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -559,16 +559,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>541</v>
+        <v>556</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -591,16 +591,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -623,16 +623,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -655,16 +655,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>488</v>
+        <v>503</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -687,16 +687,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -719,16 +719,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -751,16 +751,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -783,30 +783,30 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -815,30 +815,30 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -847,30 +847,30 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -879,16 +879,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -911,30 +911,30 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -943,30 +943,30 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
+          <t>chaychaychay</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -975,30 +975,30 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Marion1822</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1007,30 +1007,30 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
         <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1039,30 +1039,30 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
         <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C21" t="n">
         <v>5</v>
@@ -1080,16 +1080,16 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1103,30 +1103,30 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
         <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1135,16 +1135,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>407</v>
+        <v>422</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1167,16 +1167,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>401</v>
+        <v>416</v>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1231,16 +1231,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>376</v>
+        <v>391</v>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
         <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1263,16 +1263,16 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1295,16 +1295,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1327,30 +1327,30 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Maruyama</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1359,30 +1359,30 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>356</v>
+        <v>376</v>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D30" t="n">
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>Maruyama</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1391,25 +1391,25 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>346</v>
+        <v>371</v>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1423,16 +1423,16 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D32" t="n">
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1455,16 +1455,16 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1487,16 +1487,16 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
         <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1515,16 +1515,16 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D35" t="n">
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1547,16 +1547,16 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36" t="n">
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1579,16 +1579,16 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D37" t="n">
         <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1611,16 +1611,16 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D38" t="n">
         <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1643,16 +1643,16 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D39" t="n">
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1675,16 +1675,16 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D40" t="n">
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D41" t="n">
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Kolas</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1739,30 +1739,30 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D42" t="n">
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Kolas</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="C43" t="n">
         <v>4</v>
@@ -1780,21 +1780,21 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1803,58 +1803,62 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1993ahm</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>MatuRenard</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1863,25 +1867,25 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D46" t="n">
         <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -1895,30 +1899,30 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="C47" t="n">
         <v>4</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1927,48 +1931,44 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="C48" t="n">
         <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
         <v>8</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ppo28</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Reste du monde</t>
-        </is>
-      </c>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -1987,16 +1987,16 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="C50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D50" t="n">
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2019,16 +2019,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D51" t="n">
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2051,16 +2051,16 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D52" t="n">
         <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2083,16 +2083,16 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D53" t="n">
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2115,16 +2115,16 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D54" t="n">
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2147,16 +2147,16 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2211,16 +2211,16 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D57" t="n">
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2243,16 +2243,16 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
         <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2275,16 +2275,16 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D59" t="n">
         <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2307,16 +2307,16 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2342,50 +2342,54 @@
         <v>250</v>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>Romain_JO</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Jérémy</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>JeremFZ</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2399,39 +2403,35 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="C63" t="n">
         <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E63" t="n">
         <v>8</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Romain J</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="C64" t="n">
         <v>3</v>
@@ -2440,16 +2440,16 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Jérémy</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>JeremFZ</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2463,16 +2463,16 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D65" t="n">
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2495,16 +2495,16 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2527,16 +2527,16 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D67" t="n">
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2559,16 +2559,16 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2591,16 +2591,16 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2623,16 +2623,16 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -2655,16 +2655,16 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D71" t="n">
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2687,16 +2687,16 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D72" t="n">
         <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -2719,16 +2719,16 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -2751,25 +2751,25 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Priscilla</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuzo697</t>
+          <t>Priscilla#4LCAF</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -2783,30 +2783,30 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D75" t="n">
         <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Priscilla</t>
+          <t>Juliie</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Priscilla#4LCAF</t>
+          <t>Pipou931</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2815,30 +2815,30 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D76" t="n">
         <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Juliie</t>
+          <t>Selver</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pipou931</t>
+          <t>Seesee</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2847,30 +2847,30 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D77" t="n">
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Seesee</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2879,25 +2879,25 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D78" t="n">
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>C4M</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -2911,25 +2911,25 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D79" t="n">
         <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>C4M</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -2943,30 +2943,30 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D80" t="n">
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>Elisewiss</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2975,30 +2975,30 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C81" t="n">
         <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Elise</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Elisewiss</t>
+          <t>SabC1</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3007,30 +3007,30 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SabC1</t>
+          <t>Fuzo697</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3039,16 +3039,16 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3071,16 +3071,16 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -3103,16 +3103,16 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3135,16 +3135,16 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -3167,16 +3167,16 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -3199,16 +3199,16 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D88" t="n">
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -3231,16 +3231,16 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -3263,16 +3263,16 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -3295,16 +3295,16 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -3327,16 +3327,16 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -3359,25 +3359,25 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D93" t="n">
         <v>2</v>
       </c>
       <c r="E93" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3400,16 +3400,16 @@
         <v>2</v>
       </c>
       <c r="E94" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -3423,16 +3423,16 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -3455,16 +3455,16 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="C96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D96" t="n">
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3483,16 +3483,16 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="C97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D97" t="n">
         <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -3515,16 +3515,16 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="C98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D98" t="n">
         <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -3547,16 +3547,16 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="C99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -3579,16 +3579,16 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="C100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -3611,16 +3611,16 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="C101" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -3643,16 +3643,16 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="C102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -3671,16 +3671,16 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="C103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -3699,16 +3699,16 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="C104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D104" t="n">
         <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -3731,30 +3731,30 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mélissa</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>PavelMel</t>
+          <t>MxKnight</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3763,30 +3763,30 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="C106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>romain</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>MxKnight</t>
+          <t>RomainLect</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3795,30 +3795,30 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="C107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>romain</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>RomainLect</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3827,10 +3827,10 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="C108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
@@ -3840,12 +3840,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>Sab_M45</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -3868,21 +3868,21 @@
         <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Mélissa</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sab_M45</t>
+          <t>PavelMel</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3891,16 +3891,16 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>

--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -463,30 +463,30 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>611</v>
+        <v>903</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -495,30 +495,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>601</v>
+        <v>859</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>557</v>
+        <v>741</v>
       </c>
       <c r="C4" t="n">
         <v>7</v>
@@ -536,16 +536,16 @@
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>556</v>
+        <v>726</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>516</v>
+        <v>710</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Panaf</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Panaff</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>511</v>
+        <v>693</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>503</v>
+        <v>691</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -687,25 +687,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>500</v>
+        <v>683</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>498</v>
+        <v>668</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>466</v>
+        <v>665</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -783,30 +783,30 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>461</v>
+        <v>664</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -815,30 +815,30 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>455</v>
+        <v>645</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -847,30 +847,30 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>450</v>
+        <v>639</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -879,25 +879,25 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>440</v>
+        <v>631</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t>Panaf</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>Panaff</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -911,30 +911,30 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>440</v>
+        <v>612</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -943,62 +943,58 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>440</v>
+        <v>603</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>goat</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>440</v>
+        <v>601</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
         <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>EmyEnzo</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1007,30 +1003,30 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>435</v>
+        <v>594</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1039,30 +1035,30 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>435</v>
+        <v>580</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1071,30 +1067,30 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>426</v>
+        <v>568</v>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1103,30 +1099,30 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>425</v>
+        <v>555</v>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Marion1822</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1135,30 +1131,30 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>422</v>
+        <v>551</v>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Timy</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1167,30 +1163,30 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>416</v>
+        <v>548</v>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1199,30 +1195,30 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>400</v>
+        <v>545</v>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1231,30 +1227,30 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>391</v>
+        <v>538</v>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>AudreyB225</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1263,30 +1259,30 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>382</v>
+        <v>531</v>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Brieuc</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>Yebri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1295,25 +1291,25 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>381</v>
+        <v>524</v>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1327,30 +1323,30 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>376</v>
+        <v>519</v>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D29" t="n">
         <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1359,25 +1355,25 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>376</v>
+        <v>512</v>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Maruyama</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1391,30 +1387,30 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>371</v>
+        <v>512</v>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>chaychaychay</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1423,30 +1419,30 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>358</v>
+        <v>510</v>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D32" t="n">
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1455,25 +1451,25 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>344</v>
+        <v>507</v>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D33" t="n">
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1487,58 +1483,62 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>344</v>
+        <v>505</v>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Francisco93</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>YassineZ95</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>341</v>
+        <v>498</v>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1547,30 +1547,30 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>339</v>
+        <v>498</v>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D36" t="n">
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1579,30 +1579,30 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>339</v>
+        <v>496</v>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1611,25 +1611,25 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>339</v>
+        <v>494</v>
       </c>
       <c r="C38" t="n">
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>Timy</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1643,30 +1643,30 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>328</v>
+        <v>490</v>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D39" t="n">
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>EmyEnzo</t>
+          <t>C4M</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1675,30 +1675,30 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>324</v>
+        <v>488</v>
       </c>
       <c r="C40" t="n">
         <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brieuc</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Yebri</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1707,25 +1707,25 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>324</v>
+        <v>484</v>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D41" t="n">
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Kolas</t>
+          <t>Maruyama</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1739,30 +1739,30 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>324</v>
+        <v>483</v>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>Valentine___</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1771,30 +1771,30 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>323</v>
+        <v>478</v>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D43" t="n">
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1803,30 +1803,30 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>318</v>
+        <v>477</v>
       </c>
       <c r="C44" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
+          <t>Marie__92</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1835,30 +1835,30 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>318</v>
+        <v>474</v>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1867,30 +1867,30 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>318</v>
+        <v>463</v>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D46" t="n">
         <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>AudreyB225</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1899,30 +1899,30 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>309</v>
+        <v>463</v>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D47" t="n">
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Teddbear</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1931,86 +1931,94 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>309</v>
+        <v>460</v>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D48" t="n">
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1993ahm</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Romain_JO</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>308</v>
+        <v>451</v>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>goat</t>
+          <t>Loïc</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>goat#AD6GS</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Exia95</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>298</v>
+        <v>448</v>
       </c>
       <c r="C50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Devilrock95</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2019,25 +2027,25 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>298</v>
+        <v>436</v>
       </c>
       <c r="C51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D51" t="n">
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2051,30 +2059,30 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>295</v>
+        <v>436</v>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D52" t="n">
         <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2083,30 +2091,30 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>292</v>
+        <v>433</v>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Cindie</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>WIL1610</t>
+          <t>Cindie_JJA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2115,62 +2123,58 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>280</v>
+        <v>430</v>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Soraya</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Soraya-Y</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>compta</t>
-        </is>
-      </c>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>278</v>
+        <v>418</v>
       </c>
       <c r="C55" t="n">
         <v>5</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Erwan</t>
+          <t>Soraya</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Erwan#4G91X</t>
+          <t>Soraya-Y</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2179,30 +2183,30 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>277</v>
+        <v>411</v>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2211,30 +2215,30 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>271</v>
+        <v>405</v>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Loïc</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Exia95</t>
+          <t>Camillewbl</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2243,30 +2247,30 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>270</v>
+        <v>404</v>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Damien</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>PANENKANY</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2275,25 +2279,25 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>265</v>
+        <v>396</v>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2307,30 +2311,30 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>265</v>
+        <v>393</v>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liliane </t>
+          <t>Erwan</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>LilianeB</t>
+          <t>Erwan#4G91X</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2339,30 +2343,30 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>250</v>
+        <v>389</v>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Romain J</t>
+          <t>Juliie</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
+          <t>Pipou931</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2371,30 +2375,30 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>250</v>
+        <v>382</v>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Jérémy</t>
+          <t>Selver</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>JeremFZ</t>
+          <t>Seesee</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2403,58 +2407,62 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>250</v>
+        <v>382</v>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>lenaaik</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>249</v>
+        <v>382</v>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>Elisewiss</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2463,30 +2471,30 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>240</v>
+        <v>382</v>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D65" t="n">
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2495,62 +2503,58 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>234</v>
+        <v>381</v>
       </c>
       <c r="C66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>GLR_PRIME</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>232</v>
+        <v>370</v>
       </c>
       <c r="C67" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D67" t="n">
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Emma_Noel</t>
+          <t>Devilrock95</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2559,30 +2563,30 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>231</v>
+        <v>358</v>
       </c>
       <c r="C68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Antonio Moctezuma</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>abihuts</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2591,25 +2595,25 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>230</v>
+        <v>349</v>
       </c>
       <c r="C69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -2623,62 +2627,58 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>229</v>
+        <v>344</v>
       </c>
       <c r="C70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E70" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>François</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chadia__</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>226</v>
+        <v>343</v>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D71" t="n">
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>Camss</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2687,30 +2687,30 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>224</v>
+        <v>342</v>
       </c>
       <c r="C72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Marilena</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>GOAT#UE2WM8M9</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2719,25 +2719,25 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>205</v>
+        <v>337</v>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t xml:space="preserve">Liliane </t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Camss</t>
+          <t>LilianeB</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -2751,30 +2751,30 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>202</v>
+        <v>324</v>
       </c>
       <c r="C74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D74" t="n">
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Priscilla</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Priscilla#4LCAF</t>
+          <t>Kolas</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2783,25 +2783,25 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>202</v>
+        <v>322</v>
       </c>
       <c r="C75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Juliie</t>
+          <t>Jérémy</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pipou931</t>
+          <t>JeremFZ</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -2815,30 +2815,30 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>202</v>
+        <v>318</v>
       </c>
       <c r="C76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Seesee</t>
+          <t>MatuRenard</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2847,25 +2847,25 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>202</v>
+        <v>318</v>
       </c>
       <c r="C77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -2879,25 +2879,25 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>202</v>
+        <v>303</v>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Antonio Moctezuma</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>C4M</t>
+          <t>abihuts</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -2911,25 +2911,25 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>202</v>
+        <v>302</v>
       </c>
       <c r="C79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -2943,30 +2943,30 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>202</v>
+        <v>296</v>
       </c>
       <c r="C80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D80" t="n">
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Elise</t>
+          <t>Marilena</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Elisewiss</t>
+          <t>GOAT#UE2WM8M9</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2975,30 +2975,30 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>190</v>
+        <v>292</v>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>William</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SabC1</t>
+          <t>WIL1610</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3007,30 +3007,30 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>189</v>
+        <v>290</v>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Lison</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fuzo697</t>
+          <t>Lyzone</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3039,30 +3039,30 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>186</v>
+        <v>282</v>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Mathilde</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>MT35T</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3071,30 +3071,30 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>182</v>
+        <v>274</v>
       </c>
       <c r="C84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Priscilla</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>JEVAISGAGNER10</t>
+          <t>Priscilla#4LCAF</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3103,30 +3103,30 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>182</v>
+        <v>274</v>
       </c>
       <c r="C85" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Léa</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>LeaBrd</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>182</v>
+        <v>268</v>
       </c>
       <c r="C86" t="n">
         <v>4</v>
@@ -3144,16 +3144,16 @@
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lison</t>
+          <t>Cécile</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lyzone</t>
+          <t>Ceciledp</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3167,30 +3167,30 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>182</v>
+        <v>266</v>
       </c>
       <c r="C87" t="n">
         <v>4</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Ibra</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>PacoSarra</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3199,30 +3199,30 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>182</v>
+        <v>265</v>
       </c>
       <c r="C88" t="n">
         <v>4</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Marie__92</t>
+          <t>dian-bgt</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>182</v>
+        <v>258</v>
       </c>
       <c r="C89" t="n">
         <v>4</v>
@@ -3240,21 +3240,21 @@
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>K_Marp</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3263,30 +3263,30 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>182</v>
+        <v>254</v>
       </c>
       <c r="C90" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Camillewbl</t>
+          <t>JEVAISGAGNER10</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3295,30 +3295,30 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>182</v>
+        <v>254</v>
       </c>
       <c r="C91" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>Melissagzb</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3327,30 +3327,30 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>181</v>
+        <v>254</v>
       </c>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Damien</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>PANENKANY</t>
+          <t>K_Marp</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3359,30 +3359,30 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>178</v>
+        <v>254</v>
       </c>
       <c r="C93" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3391,30 +3391,30 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>163</v>
+        <v>249</v>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3423,90 +3423,90 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>160</v>
+        <v>241</v>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cécile</t>
+          <t>ousmane</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ceciledp</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>158</v>
+        <v>234</v>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fa_One</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>GLR_PRIME</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>158</v>
+        <v>232</v>
       </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D97" t="n">
         <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Killian</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>KIKS999</t>
+          <t>Emma_Noel</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3515,57 +3515,53 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>158</v>
+        <v>230</v>
       </c>
       <c r="C98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D98" t="n">
         <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Valentine___</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>Fa_One</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>138</v>
+        <v>223</v>
       </c>
       <c r="C99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Laetitia</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Laetice2020</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -3579,7 +3575,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>138</v>
+        <v>208</v>
       </c>
       <c r="C100" t="n">
         <v>3</v>
@@ -3588,21 +3584,21 @@
         <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cindie</t>
+          <t>Mélissa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cindie_JJA</t>
+          <t>PavelMel</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3611,39 +3607,35 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>138</v>
+        <v>205</v>
       </c>
       <c r="C101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>lea</t>
+          <t>Brick</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>RBTL</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>133</v>
+        <v>190</v>
       </c>
       <c r="C102" t="n">
         <v>3</v>
@@ -3652,26 +3644,30 @@
         <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>BrickXVI</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>SabC1</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>133</v>
+        <v>189</v>
       </c>
       <c r="C103" t="n">
         <v>3</v>
@@ -3680,49 +3676,53 @@
         <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ousmane</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Taylor2901</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+          <t>Fuzo697</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>128</v>
+        <v>182</v>
       </c>
       <c r="C104" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ibra</t>
+          <t>Léa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>PacoSarra</t>
+          <t>LeaBrd</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3731,16 +3731,16 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>108</v>
+        <v>180</v>
       </c>
       <c r="C105" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -3763,30 +3763,30 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>108</v>
+        <v>180</v>
       </c>
       <c r="C106" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>romain</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>RomainLect</t>
+          <t>Sab_M45</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3795,30 +3795,30 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>108</v>
+        <v>158</v>
       </c>
       <c r="C107" t="n">
         <v>3</v>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>Killian</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>KIKS999</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3827,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="C108" t="n">
         <v>3</v>
@@ -3836,16 +3836,16 @@
         <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Laetitia</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Sab_M45</t>
+          <t>Laetice2020</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -3859,10 +3859,10 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>93</v>
+        <v>138</v>
       </c>
       <c r="C109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
@@ -3872,12 +3872,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mélissa</t>
+          <t>lea</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>PavelMel</t>
+          <t>RBTL</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -3891,30 +3891,30 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>59</v>
+        <v>108</v>
       </c>
       <c r="C110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mathilde</t>
+          <t>romain</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>MT35T</t>
+          <t>RomainLect</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>

--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -463,30 +463,30 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>903</v>
+        <v>1025</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -495,30 +495,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>859</v>
+        <v>903</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -527,25 +527,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>741</v>
+        <v>859</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>726</v>
+        <v>746</v>
       </c>
       <c r="C5" t="n">
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>710</v>
+        <v>741</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>693</v>
+        <v>733</v>
       </c>
       <c r="C7" t="n">
         <v>7</v>
@@ -632,21 +632,21 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>AudreyB225</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>691</v>
+        <v>726</v>
       </c>
       <c r="C8" t="n">
         <v>8</v>
@@ -664,21 +664,21 @@
         <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -687,25 +687,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>683</v>
+        <v>710</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -719,7 +719,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>668</v>
+        <v>691</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
@@ -728,21 +728,21 @@
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>665</v>
+        <v>683</v>
       </c>
       <c r="C11" t="n">
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -783,30 +783,30 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>645</v>
+        <v>665</v>
       </c>
       <c r="C13" t="n">
         <v>8</v>
@@ -824,21 +824,21 @@
         <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -847,30 +847,30 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>639</v>
+        <v>664</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -879,25 +879,25 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>631</v>
+        <v>654</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Panaf</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Panaff</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -911,30 +911,30 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>612</v>
+        <v>645</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Marion1822</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -943,58 +943,62 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>603</v>
+        <v>640</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>goat</t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>goat#AD6GS</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>YassineZ95</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>601</v>
+        <v>639</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>EmyEnzo</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1007,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>594</v>
+        <v>631</v>
       </c>
       <c r="C19" t="n">
         <v>7</v>
@@ -1012,21 +1016,21 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Panaf</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>Panaff</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1035,30 +1039,30 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>580</v>
+        <v>612</v>
       </c>
       <c r="C20" t="n">
         <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1067,62 +1071,58 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>568</v>
+        <v>603</v>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>goat</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>555</v>
+        <v>601</v>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D22" t="n">
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>EmyEnzo</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1131,30 +1131,30 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>551</v>
+        <v>594</v>
       </c>
       <c r="C23" t="n">
         <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1163,30 +1163,30 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>548</v>
+        <v>568</v>
       </c>
       <c r="C24" t="n">
         <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1195,25 +1195,25 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>545</v>
+        <v>555</v>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1227,25 +1227,25 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>538</v>
+        <v>551</v>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1259,7 +1259,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>531</v>
+        <v>548</v>
       </c>
       <c r="C27" t="n">
         <v>7</v>
@@ -1268,21 +1268,21 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brieuc</t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Yebri</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1291,30 +1291,30 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>524</v>
+        <v>545</v>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1323,30 +1323,30 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="C29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>512</v>
+        <v>531</v>
       </c>
       <c r="C30" t="n">
         <v>7</v>
@@ -1364,21 +1364,21 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Brieuc</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
+          <t>Yebri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1387,30 +1387,30 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="C31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1419,30 +1419,30 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="C33" t="n">
         <v>7</v>
@@ -1460,16 +1460,16 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1483,30 +1483,30 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="C34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>chaychaychay</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1515,30 +1515,30 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1547,30 +1547,30 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D36" t="n">
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1579,30 +1579,30 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1611,30 +1611,30 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Timy</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C39" t="n">
         <v>6</v>
@@ -1652,21 +1652,21 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>C4M</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1675,30 +1675,30 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="C40" t="n">
         <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Timy</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="C41" t="n">
         <v>6</v>
@@ -1716,21 +1716,21 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Maruyama</t>
+          <t>C4M</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1739,25 +1739,25 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C42" t="n">
         <v>6</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Valentine___</t>
+          <t>Maruyama</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1771,30 +1771,30 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="C43" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
         <v>12</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>Valentine___</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1803,30 +1803,30 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C44" t="n">
         <v>7</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Marie__92</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1835,30 +1835,30 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>Camss</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1867,30 +1867,30 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>AudreyB225</t>
+          <t>Marie__92</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1899,25 +1899,25 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -1931,10 +1931,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D48" t="n">
         <v>1</v>
@@ -1944,17 +1944,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Romain J</t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
+          <t>Teddbear</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="C49" t="n">
         <v>6</v>
@@ -1972,21 +1972,21 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Loïc</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Exia95</t>
+          <t>Romain_JO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1995,25 +1995,25 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C50" t="n">
         <v>6</v>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Loïc</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Exia95</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2027,30 +2027,30 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="C51" t="n">
         <v>6</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2062,27 +2062,27 @@
         <v>436</v>
       </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2091,30 +2091,30 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cindie</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cindie_JJA</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2123,35 +2123,39 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Cindie</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Cindie_JJA</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="C55" t="n">
         <v>5</v>
@@ -2160,53 +2164,49 @@
         <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Soraya</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Soraya-Y</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>compta</t>
-        </is>
-      </c>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="C56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D56" t="n">
         <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Soraya</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
+          <t>Soraya-Y</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2215,30 +2215,30 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="C57" t="n">
         <v>6</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Camillewbl</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2247,25 +2247,25 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Damien</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>PANENKANY</t>
+          <t>Camillewbl</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2279,30 +2279,30 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Damien</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>PANENKANY</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2311,30 +2311,30 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C60" t="n">
         <v>6</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Erwan</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Erwan#4G91X</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2343,30 +2343,30 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C61" t="n">
         <v>6</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Juliie</t>
+          <t>Erwan</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pipou931</t>
+          <t>Erwan#4G91X</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="C62" t="n">
         <v>6</v>
@@ -2384,21 +2384,21 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t>Juliie</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Seesee</t>
+          <t>Pipou931</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2416,21 +2416,21 @@
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Selver</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>Seesee</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2448,21 +2448,21 @@
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Elise</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Elisewiss</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2474,27 +2474,27 @@
         <v>382</v>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D65" t="n">
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>Elisewiss</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2503,38 +2503,42 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D66" t="n">
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1993ahm</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>ChrisKr1Deg1</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="C67" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D67" t="n">
         <v>1</v>
@@ -2544,44 +2548,40 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Devilrock95</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>Devilrock95</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -2595,7 +2595,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="C69" t="n">
         <v>5</v>
@@ -2604,16 +2604,16 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>GLR_PRIME</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -2627,7 +2627,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="C70" t="n">
         <v>5</v>
@@ -2636,44 +2636,48 @@
         <v>2</v>
       </c>
       <c r="E70" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Francisco93</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>Droit_au_but7723</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Camss</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -2687,7 +2691,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C72" t="n">
         <v>5</v>
@@ -2696,30 +2700,26 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>François</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C73" t="n">
         <v>5</v>
@@ -2728,16 +2728,16 @@
         <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liliane </t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>LilianeB</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -2751,30 +2751,30 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="C74" t="n">
         <v>5</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t xml:space="preserve">Liliane </t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Kolas</t>
+          <t>LilianeB</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2783,30 +2783,30 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C75" t="n">
         <v>5</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Jérémy</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>JeremFZ</t>
+          <t>Kolas</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2815,30 +2815,30 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C76" t="n">
         <v>5</v>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>Jérémy</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
+          <t>JeremFZ</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2856,21 +2856,21 @@
         <v>2</v>
       </c>
       <c r="E77" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>MatuRenard</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2879,25 +2879,25 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="C78" t="n">
         <v>5</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Antonio Moctezuma</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>abihuts</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -2911,7 +2911,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C79" t="n">
         <v>5</v>
@@ -2920,16 +2920,16 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Antonio Moctezuma</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>abihuts</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -2943,30 +2943,30 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="C80" t="n">
         <v>5</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Marilena</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>GOAT#UE2WM8M9</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2975,30 +2975,30 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D81" t="n">
         <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Marilena</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>WIL1610</t>
+          <t>GOAT#UE2WM8M9</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3007,30 +3007,30 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C82" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lison</t>
+          <t>William</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lyzone</t>
+          <t>WIL1610</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3039,30 +3039,30 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="C83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mathilde</t>
+          <t>Lison</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>MT35T</t>
+          <t>Lyzone</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3071,30 +3071,30 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="C84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Priscilla</t>
+          <t>Mathilde</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Priscilla#4LCAF</t>
+          <t>MT35T</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3112,21 +3112,21 @@
         <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Priscilla</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>Priscilla#4LCAF</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3135,25 +3135,25 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cécile</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ceciledp</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3167,30 +3167,30 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C87" t="n">
         <v>4</v>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ibra</t>
+          <t>Cécile</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>PacoSarra</t>
+          <t>Ceciledp</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C88" t="n">
         <v>4</v>
@@ -3208,21 +3208,21 @@
         <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Ibra</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
+          <t>PacoSarra</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3231,30 +3231,30 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="C89" t="n">
         <v>4</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E89" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>dian-bgt</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3263,30 +3263,30 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>JEVAISGAGNER10</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3308,17 +3308,17 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>JEVAISGAGNER10</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3336,21 +3336,21 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>K_Marp</t>
+          <t>Melissagzb</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3368,21 +3368,21 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>K_Marp</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3391,25 +3391,25 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C94" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -3423,35 +3423,39 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="C95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>ousmane</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Taylor2901</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>davidd23</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C96" t="n">
         <v>4</v>
@@ -3460,23 +3464,19 @@
         <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>ousmane</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>GLR_PRIME</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -3492,7 +3492,7 @@
         <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>

--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -463,30 +463,30 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1025</v>
+        <v>1154</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -495,30 +495,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>903</v>
+        <v>1025</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>859</v>
+        <v>1019</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -559,16 +559,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>746</v>
+        <v>1007</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -591,25 +591,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>741</v>
+        <v>1004</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>733</v>
+        <v>915</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AudreyB225</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -655,16 +655,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>726</v>
+        <v>892</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -687,16 +687,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>710</v>
+        <v>876</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>691</v>
+        <v>839</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>683</v>
+        <v>833</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -783,16 +783,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>668</v>
+        <v>813</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -815,30 +815,30 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>665</v>
+        <v>796</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
         <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -847,30 +847,30 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>664</v>
+        <v>755</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -879,25 +879,25 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>654</v>
+        <v>747</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Panaf</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Panaff</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -911,7 +911,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>645</v>
+        <v>746</v>
       </c>
       <c r="C16" t="n">
         <v>8</v>
@@ -920,21 +920,21 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>YassineZ95</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -943,30 +943,30 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>640</v>
+        <v>728</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>639</v>
+        <v>687</v>
       </c>
       <c r="C18" t="n">
         <v>8</v>
@@ -984,21 +984,21 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1007,30 +1007,30 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>631</v>
+        <v>683</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Panaf</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Panaff</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1039,30 +1039,30 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>612</v>
+        <v>676</v>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>Brieuc</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Marion1822</t>
+          <t>Yebri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1071,58 +1071,62 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>603</v>
+        <v>665</v>
       </c>
       <c r="C21" t="n">
         <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>goat</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>goat#AD6GS</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>catherine#5FRTD</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>601</v>
+        <v>664</v>
       </c>
       <c r="C22" t="n">
         <v>7</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>EmyEnzo</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1131,25 +1135,25 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>594</v>
+        <v>655</v>
       </c>
       <c r="C23" t="n">
         <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1163,30 +1167,30 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>568</v>
+        <v>654</v>
       </c>
       <c r="C24" t="n">
         <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1195,30 +1199,30 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>555</v>
+        <v>645</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1227,30 +1231,30 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>551</v>
+        <v>643</v>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1259,30 +1263,30 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>548</v>
+        <v>640</v>
       </c>
       <c r="C27" t="n">
         <v>7</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1291,30 +1295,30 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>545</v>
+        <v>635</v>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1323,25 +1327,25 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>538</v>
+        <v>628</v>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1355,30 +1359,30 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>531</v>
+        <v>628</v>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D30" t="n">
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brieuc</t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Yebri</t>
+          <t>chaychaychay</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1387,25 +1391,25 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>524</v>
+        <v>620</v>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1419,30 +1423,30 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>519</v>
+        <v>620</v>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1451,30 +1455,30 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>512</v>
+        <v>619</v>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
+          <t>Marie__92</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1483,30 +1487,30 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>512</v>
+        <v>619</v>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>Timy</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1515,30 +1519,30 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>510</v>
+        <v>616</v>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1547,25 +1551,25 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>507</v>
+        <v>612</v>
       </c>
       <c r="C36" t="n">
         <v>7</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1579,57 +1583,53 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>498</v>
+        <v>603</v>
       </c>
       <c r="C37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>goat</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ppo28</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Reste du monde</t>
-        </is>
-      </c>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>498</v>
+        <v>601</v>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
+          <t>EmyEnzo</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1643,30 +1643,30 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>496</v>
+        <v>594</v>
       </c>
       <c r="C39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D39" t="n">
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1675,30 +1675,30 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>494</v>
+        <v>593</v>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Timy</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1707,30 +1707,30 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>490</v>
+        <v>581</v>
       </c>
       <c r="C41" t="n">
         <v>6</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>C4M</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>484</v>
+        <v>579</v>
       </c>
       <c r="C42" t="n">
         <v>6</v>
@@ -1752,17 +1752,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Maruyama</t>
+          <t>Teddbear</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1771,25 +1771,25 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>483</v>
+        <v>576</v>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Valentine___</t>
+          <t>Romain_JO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1803,30 +1803,30 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>478</v>
+        <v>569</v>
       </c>
       <c r="C44" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>Mathilde</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>MT35T</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1835,25 +1835,25 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>478</v>
+        <v>568</v>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Camss</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -1867,62 +1867,58 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>477</v>
+        <v>555</v>
       </c>
       <c r="C46" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Marie__92</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>474</v>
+        <v>551</v>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1931,30 +1927,30 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>463</v>
+        <v>550</v>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D48" t="n">
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>Camillewbl</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1963,25 +1959,25 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>460</v>
+        <v>548</v>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Romain J</t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -1995,62 +1991,58 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>451</v>
+        <v>526</v>
       </c>
       <c r="C50" t="n">
         <v>6</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
         <v>14</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Loïc</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Exia95</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>compta</t>
-        </is>
-      </c>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>448</v>
+        <v>519</v>
       </c>
       <c r="C51" t="n">
         <v>6</v>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2051,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>436</v>
+        <v>515</v>
       </c>
       <c r="C52" t="n">
         <v>6</v>
@@ -2068,16 +2060,16 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2091,30 +2083,30 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>436</v>
+        <v>512</v>
       </c>
       <c r="C53" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2123,30 +2115,30 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>433</v>
+        <v>507</v>
       </c>
       <c r="C54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cindie</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cindie_JJA</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2155,53 +2147,57 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>430</v>
+        <v>507</v>
       </c>
       <c r="C55" t="n">
         <v>5</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>davidd23</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>418</v>
+        <v>498</v>
       </c>
       <c r="C56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Soraya</t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Soraya-Y</t>
+          <t>Elisewiss</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2215,7 +2211,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>411</v>
+        <v>498</v>
       </c>
       <c r="C57" t="n">
         <v>6</v>
@@ -2224,21 +2220,21 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2247,30 +2243,30 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>405</v>
+        <v>498</v>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
         <v>14</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Camillewbl</t>
+          <t>SabC1</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2279,30 +2275,30 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>404</v>
+        <v>495</v>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Damien</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>PANENKANY</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2307,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>396</v>
+        <v>490</v>
       </c>
       <c r="C60" t="n">
         <v>6</v>
@@ -2320,16 +2316,16 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>C4M</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2343,25 +2339,25 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>393</v>
+        <v>484</v>
       </c>
       <c r="C61" t="n">
         <v>6</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Erwan</t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Erwan#4G91X</t>
+          <t>Maruyama</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2375,30 +2371,30 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>389</v>
+        <v>483</v>
       </c>
       <c r="C62" t="n">
         <v>6</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Juliie</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pipou931</t>
+          <t>Valentine___</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2407,30 +2403,30 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>382</v>
+        <v>479</v>
       </c>
       <c r="C63" t="n">
         <v>6</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t xml:space="preserve">Liliane </t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Seesee</t>
+          <t>LilianeB</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2439,30 +2435,30 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>382</v>
+        <v>463</v>
       </c>
       <c r="C64" t="n">
         <v>6</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>AudreyB225</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2471,62 +2467,58 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>382</v>
+        <v>460</v>
       </c>
       <c r="C65" t="n">
         <v>6</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Elise</t>
+          <t>François</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Elisewiss</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>compta</t>
-        </is>
-      </c>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>382</v>
+        <v>451</v>
       </c>
       <c r="C66" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D66" t="n">
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Loïc</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>Exia95</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2535,58 +2527,62 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>381</v>
+        <v>445</v>
       </c>
       <c r="C67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D67" t="n">
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Antonio Moctezuma</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1993ahm</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>abihuts</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>370</v>
+        <v>444</v>
       </c>
       <c r="C68" t="n">
         <v>6</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Jérémy</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Devilrock95</t>
+          <t>JeremFZ</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2595,62 +2591,58 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>369</v>
+        <v>443</v>
       </c>
       <c r="C69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Brick</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>GLR_PRIME</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>358</v>
+        <v>434</v>
       </c>
       <c r="C70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D70" t="n">
         <v>2</v>
       </c>
       <c r="E70" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>MatuRenard</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2659,25 +2651,25 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>349</v>
+        <v>434</v>
       </c>
       <c r="C71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E71" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -2691,35 +2683,39 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>344</v>
+        <v>433</v>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Cindie</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Francisco93</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>Cindie_JJA</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>342</v>
+        <v>418</v>
       </c>
       <c r="C73" t="n">
         <v>5</v>
@@ -2728,21 +2724,21 @@
         <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Soraya</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>Soraya-Y</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2751,30 +2747,30 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>337</v>
+        <v>411</v>
       </c>
       <c r="C74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D74" t="n">
         <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liliane </t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>LilianeB</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2779,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>324</v>
+        <v>408</v>
       </c>
       <c r="C75" t="n">
         <v>5</v>
@@ -2792,21 +2788,21 @@
         <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>William</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Kolas</t>
+          <t>WIL1610</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2815,25 +2811,25 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>322</v>
+        <v>406</v>
       </c>
       <c r="C76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Jérémy</t>
+          <t>Lison</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>JeremFZ</t>
+          <t>Lyzone</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -2847,30 +2843,30 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>318</v>
+        <v>404</v>
       </c>
       <c r="C77" t="n">
         <v>5</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>Damien</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
+          <t>PANENKANY</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2879,25 +2875,25 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>318</v>
+        <v>400</v>
       </c>
       <c r="C78" t="n">
         <v>5</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>GLR_PRIME</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -2911,30 +2907,30 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>303</v>
+        <v>399</v>
       </c>
       <c r="C79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Antonio Moctezuma</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>abihuts</t>
+          <t>Melissagzb</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2943,30 +2939,30 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>302</v>
+        <v>393</v>
       </c>
       <c r="C80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Erwan</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>Erwan#4G91X</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2975,30 +2971,30 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>296</v>
+        <v>390</v>
       </c>
       <c r="C81" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D81" t="n">
         <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Marilena</t>
+          <t>Priscilla</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>GOAT#UE2WM8M9</t>
+          <t>Priscilla#4LCAF</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3007,10 +3003,10 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>292</v>
+        <v>389</v>
       </c>
       <c r="C82" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D82" t="n">
         <v>1</v>
@@ -3020,17 +3016,17 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Juliie</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>WIL1610</t>
+          <t>Pipou931</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3039,30 +3035,30 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>290</v>
+        <v>382</v>
       </c>
       <c r="C83" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lison</t>
+          <t>Selver</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lyzone</t>
+          <t>Seesee</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3071,30 +3067,30 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>282</v>
+        <v>382</v>
       </c>
       <c r="C84" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mathilde</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>MT35T</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3103,30 +3099,30 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>274</v>
+        <v>370</v>
       </c>
       <c r="C85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D85" t="n">
         <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Priscilla</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Priscilla#4LCAF</t>
+          <t>Devilrock95</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3131,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>274</v>
+        <v>365</v>
       </c>
       <c r="C86" t="n">
         <v>5</v>
@@ -3148,12 +3144,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3167,30 +3163,30 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>268</v>
+        <v>358</v>
       </c>
       <c r="C87" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cécile</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ceciledp</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3199,30 +3195,30 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>266</v>
+        <v>350</v>
       </c>
       <c r="C88" t="n">
         <v>4</v>
       </c>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ibra</t>
+          <t>Mélissa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>PacoSarra</t>
+          <t>PavelMel</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3231,25 +3227,25 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>265</v>
+        <v>343</v>
       </c>
       <c r="C89" t="n">
         <v>4</v>
       </c>
       <c r="D89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
+          <t>Camss</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3263,30 +3259,30 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>258</v>
+        <v>342</v>
       </c>
       <c r="C90" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E90" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3295,30 +3291,30 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>254</v>
+        <v>324</v>
       </c>
       <c r="C91" t="n">
         <v>5</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>JEVAISGAGNER10</t>
+          <t>Kolas</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3327,7 +3323,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>254</v>
+        <v>302</v>
       </c>
       <c r="C92" t="n">
         <v>5</v>
@@ -3336,21 +3332,21 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3355,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>254</v>
+        <v>298</v>
       </c>
       <c r="C93" t="n">
         <v>5</v>
@@ -3368,21 +3364,21 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Léa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>K_Marp</t>
+          <t>LeaBrd</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3391,30 +3387,30 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>254</v>
+        <v>296</v>
       </c>
       <c r="C94" t="n">
         <v>5</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Marilena</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>GOAT#UE2WM8M9</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3423,25 +3419,25 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>249</v>
+        <v>296</v>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>Sab_M45</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -3455,58 +3451,62 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>241</v>
+        <v>274</v>
       </c>
       <c r="C96" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ousmane</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Taylor2901</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>Rosa_1009</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>232</v>
+        <v>268</v>
       </c>
       <c r="C97" t="n">
         <v>4</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Cécile</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Emma_Noel</t>
+          <t>Ceciledp</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3515,53 +3515,57 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>230</v>
+        <v>266</v>
       </c>
       <c r="C98" t="n">
         <v>4</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E98" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>Ibra</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fa_One</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>PacoSarra</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>223</v>
+        <v>265</v>
       </c>
       <c r="C99" t="n">
         <v>4</v>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E99" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>dian-bgt</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -3575,10 +3579,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>208</v>
+        <v>254</v>
       </c>
       <c r="C100" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -3588,17 +3592,17 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mélissa</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>PavelMel</t>
+          <t>JEVAISGAGNER10</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3607,85 +3611,85 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>205</v>
+        <v>254</v>
       </c>
       <c r="C101" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>BrickXVI</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>K_Marp</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>190</v>
+        <v>241</v>
       </c>
       <c r="C102" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>ousmane</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SabC1</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>189</v>
+        <v>232</v>
       </c>
       <c r="C103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Fuzo697</t>
+          <t>Emma_Noel</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -3699,39 +3703,35 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>182</v>
+        <v>230</v>
       </c>
       <c r="C104" t="n">
         <v>4</v>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Léa</t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>LeaBrd</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>Fa_One</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>180</v>
+        <v>224</v>
       </c>
       <c r="C105" t="n">
         <v>4</v>
@@ -3740,21 +3740,21 @@
         <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>romain</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>MxKnight</t>
+          <t>RomainLect</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3763,30 +3763,30 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="C106" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sab_M45</t>
+          <t>Fuzo697</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3795,30 +3795,30 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="C107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Killian</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>KIKS999</t>
+          <t>MxKnight</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3827,30 +3827,30 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="C108" t="n">
         <v>3</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Laetitia</t>
+          <t>Killian</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Laetice2020</t>
+          <t>KIKS999</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3868,21 +3868,21 @@
         <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>lea</t>
+          <t>Laetitia</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>RBTL</t>
+          <t>Laetice2020</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="C110" t="n">
         <v>3</v>
@@ -3900,21 +3900,21 @@
         <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>romain</t>
+          <t>lea</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>RomainLect</t>
+          <t>RBTL</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>

--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -472,7 +472,7 @@
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,30 +495,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1025</v>
+        <v>1080</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -527,16 +527,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1019</v>
+        <v>1065</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -559,25 +559,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1007</v>
+        <v>1025</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>915</v>
+        <v>938</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>892</v>
+        <v>922</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
         <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>876</v>
+        <v>915</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>839</v>
+        <v>879</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>833</v>
+        <v>859</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
         <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -783,30 +783,30 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>813</v>
+        <v>839</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -815,30 +815,30 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -847,30 +847,30 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>755</v>
+        <v>796</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -879,16 +879,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>747</v>
+        <v>793</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -911,16 +911,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>746</v>
+        <v>792</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -943,16 +943,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>728</v>
+        <v>774</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -975,30 +975,30 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>687</v>
+        <v>741</v>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1007,25 +1007,25 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>683</v>
+        <v>740</v>
       </c>
       <c r="C19" t="n">
         <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1039,30 +1039,30 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>676</v>
+        <v>733</v>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brieuc</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Yebri</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1071,30 +1071,30 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>665</v>
+        <v>729</v>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1103,30 +1103,30 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>664</v>
+        <v>722</v>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Brieuc</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>Yebri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1135,30 +1135,30 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>655</v>
+        <v>721</v>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1167,30 +1167,30 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>654</v>
+        <v>689</v>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1199,30 +1199,30 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>645</v>
+        <v>674</v>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1231,30 +1231,30 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>643</v>
+        <v>669</v>
       </c>
       <c r="C26" t="n">
         <v>8</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1263,25 +1263,25 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>640</v>
+        <v>666</v>
       </c>
       <c r="C27" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1295,30 +1295,30 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>635</v>
+        <v>666</v>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1327,30 +1327,30 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>628</v>
+        <v>665</v>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>16</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
+          <t>Marie__92</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1359,30 +1359,30 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>628</v>
+        <v>665</v>
       </c>
       <c r="C30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>Timy</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1391,30 +1391,30 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>620</v>
+        <v>658</v>
       </c>
       <c r="C31" t="n">
         <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1423,30 +1423,30 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>620</v>
+        <v>655</v>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1455,30 +1455,30 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>619</v>
+        <v>654</v>
       </c>
       <c r="C33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D33" t="n">
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Marie__92</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1487,62 +1487,58 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>619</v>
+        <v>649</v>
       </c>
       <c r="C34" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>goat</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Timy</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>616</v>
+        <v>647</v>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>EmyEnzo</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1551,30 +1547,30 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>612</v>
+        <v>640</v>
       </c>
       <c r="C36" t="n">
         <v>7</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1583,35 +1579,39 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>603</v>
+        <v>635</v>
       </c>
       <c r="C37" t="n">
         <v>8</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>goat</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>goat#AD6GS</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Ouiouiausoleil</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>601</v>
+        <v>631</v>
       </c>
       <c r="C38" t="n">
         <v>7</v>
@@ -1624,49 +1624,45 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>EmyEnzo</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>594</v>
+        <v>628</v>
       </c>
       <c r="C39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
         <v>16</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>chaychaychay</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1675,30 +1671,30 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>593</v>
+        <v>625</v>
       </c>
       <c r="C40" t="n">
         <v>7</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Teddbear</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1707,25 +1703,25 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>581</v>
+        <v>624</v>
       </c>
       <c r="C41" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D41" t="n">
         <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1739,30 +1735,30 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>579</v>
+        <v>622</v>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D42" t="n">
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>Romain_JO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1771,30 +1767,30 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>576</v>
+        <v>616</v>
       </c>
       <c r="C43" t="n">
         <v>7</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Romain J</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1803,16 +1799,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>569</v>
+        <v>615</v>
       </c>
       <c r="C44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D44" t="n">
         <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1835,7 +1831,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>568</v>
+        <v>602</v>
       </c>
       <c r="C45" t="n">
         <v>7</v>
@@ -1844,81 +1840,81 @@
         <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>555</v>
+        <v>597</v>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D46" t="n">
         <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>FRHTCTD10</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>551</v>
+        <v>596</v>
       </c>
       <c r="C47" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>Camillewbl</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1923,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>550</v>
+        <v>594</v>
       </c>
       <c r="C48" t="n">
         <v>7</v>
@@ -1936,21 +1932,21 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Camillewbl</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1959,25 +1955,25 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>548</v>
+        <v>581</v>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -1991,58 +1987,62 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>526</v>
+        <v>574</v>
       </c>
       <c r="C50" t="n">
         <v>6</v>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1993ahm</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>SabC1</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>519</v>
+        <v>568</v>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2051,25 +2051,25 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>515</v>
+        <v>566</v>
       </c>
       <c r="C52" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>C4M</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2083,7 +2083,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>512</v>
+        <v>565</v>
       </c>
       <c r="C53" t="n">
         <v>7</v>
@@ -2092,21 +2092,21 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2115,30 +2115,30 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>507</v>
+        <v>561</v>
       </c>
       <c r="C54" t="n">
         <v>7</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2147,30 +2147,30 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>507</v>
+        <v>559</v>
       </c>
       <c r="C55" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>Valentine___</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2179,30 +2179,30 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>498</v>
+        <v>558</v>
       </c>
       <c r="C56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D56" t="n">
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Elise</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Elisewiss</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2211,30 +2211,30 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>498</v>
+        <v>555</v>
       </c>
       <c r="C57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E57" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t xml:space="preserve">Liliane </t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
+          <t>LilianeB</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2243,30 +2243,30 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>498</v>
+        <v>553</v>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D58" t="n">
         <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SabC1</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2275,25 +2275,25 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>495</v>
+        <v>553</v>
       </c>
       <c r="C59" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2307,30 +2307,30 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>490</v>
+        <v>544</v>
       </c>
       <c r="C60" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D60" t="n">
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>C4M</t>
+          <t>Elisewiss</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2339,30 +2339,30 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>484</v>
+        <v>544</v>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" t="n">
         <v>16</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Maruyama</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2371,30 +2371,30 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>483</v>
+        <v>541</v>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Valentine___</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2403,30 +2403,30 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>479</v>
+        <v>534</v>
       </c>
       <c r="C63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liliane </t>
+          <t>Selver</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>LilianeB</t>
+          <t>Seesee</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2435,30 +2435,30 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>463</v>
+        <v>521</v>
       </c>
       <c r="C64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D64" t="n">
         <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Antonio Moctezuma</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>AudreyB225</t>
+          <t>abihuts</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2467,90 +2467,90 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>460</v>
+        <v>520</v>
       </c>
       <c r="C65" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Jérémy</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Francisco93</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>JeremFZ</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>451</v>
+        <v>519</v>
       </c>
       <c r="C66" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D66" t="n">
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Loïc</t>
+          <t>Brick</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Exia95</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>compta</t>
-        </is>
-      </c>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>445</v>
+        <v>509</v>
       </c>
       <c r="C67" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Antonio Moctezuma</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>abihuts</t>
+          <t>AudreyB225</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2559,90 +2559,90 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>444</v>
+        <v>506</v>
       </c>
       <c r="C68" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Jérémy</t>
+          <t>François</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>JeremFZ</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>443</v>
+        <v>497</v>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Loïc</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>BrickXVI</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>Exia95</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>434</v>
+        <v>487</v>
       </c>
       <c r="C70" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>434</v>
+        <v>484</v>
       </c>
       <c r="C71" t="n">
         <v>6</v>
@@ -2660,21 +2660,21 @@
         <v>2</v>
       </c>
       <c r="E71" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>William</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>WIL1610</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2683,30 +2683,30 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>433</v>
+        <v>484</v>
       </c>
       <c r="C72" t="n">
         <v>6</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Cindie</t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cindie_JJA</t>
+          <t>Maruyama</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2715,30 +2715,30 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>418</v>
+        <v>480</v>
       </c>
       <c r="C73" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D73" t="n">
         <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Soraya</t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Soraya-Y</t>
+          <t>MatuRenard</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2747,30 +2747,30 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>411</v>
+        <v>479</v>
       </c>
       <c r="C74" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Cindie</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
+          <t>Cindie_JJA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2779,30 +2779,30 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>408</v>
+        <v>476</v>
       </c>
       <c r="C75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>WIL1610</t>
+          <t>GLR_PRIME</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2811,25 +2811,25 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>406</v>
+        <v>465</v>
       </c>
       <c r="C76" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E76" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lison</t>
+          <t>Juliie</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lyzone</t>
+          <t>Pipou931</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -2843,30 +2843,30 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>404</v>
+        <v>458</v>
       </c>
       <c r="C77" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E77" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Damien</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>PANENKANY</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2875,25 +2875,25 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>400</v>
+        <v>454</v>
       </c>
       <c r="C78" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D78" t="n">
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>GLR_PRIME</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -2907,30 +2907,30 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>399</v>
+        <v>452</v>
       </c>
       <c r="C79" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Lison</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>Lyzone</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>393</v>
+        <v>450</v>
       </c>
       <c r="C80" t="n">
         <v>6</v>
@@ -2948,21 +2948,21 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Erwan</t>
+          <t>Damien</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Erwan#4G91X</t>
+          <t>PANENKANY</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2971,25 +2971,25 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>390</v>
+        <v>445</v>
       </c>
       <c r="C81" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D81" t="n">
         <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Priscilla</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Priscilla#4LCAF</t>
+          <t>Melissagzb</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3003,30 +3003,30 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>389</v>
+        <v>439</v>
       </c>
       <c r="C82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Juliie</t>
+          <t>Erwan</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pipou931</t>
+          <t>Erwan#4G91X</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3035,30 +3035,30 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>382</v>
+        <v>436</v>
       </c>
       <c r="C83" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D83" t="n">
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t>Priscilla</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Seesee</t>
+          <t>Priscilla#4LCAF</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3067,30 +3067,30 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>382</v>
+        <v>434</v>
       </c>
       <c r="C84" t="n">
         <v>6</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E84" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3099,30 +3099,30 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>370</v>
+        <v>434</v>
       </c>
       <c r="C85" t="n">
         <v>6</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Devilrock95</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3131,30 +3131,30 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>365</v>
+        <v>418</v>
       </c>
       <c r="C86" t="n">
         <v>5</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>Soraya</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>Soraya-Y</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3163,25 +3163,25 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>358</v>
+        <v>416</v>
       </c>
       <c r="C87" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>Devilrock95</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3195,30 +3195,30 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>350</v>
+        <v>411</v>
       </c>
       <c r="C88" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D88" t="n">
         <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mélissa</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>PavelMel</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3227,30 +3227,30 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>343</v>
+        <v>396</v>
       </c>
       <c r="C89" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D89" t="n">
         <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Mélissa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Camss</t>
+          <t>PavelMel</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3259,25 +3259,25 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>342</v>
+        <v>389</v>
       </c>
       <c r="C90" t="n">
         <v>5</v>
       </c>
       <c r="D90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>Camss</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3291,30 +3291,30 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>324</v>
+        <v>388</v>
       </c>
       <c r="C91" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Kolas</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3323,25 +3323,25 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>302</v>
+        <v>372</v>
       </c>
       <c r="C92" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
         <v>16</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>Sab_M45</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3355,30 +3355,30 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>298</v>
+        <v>370</v>
       </c>
       <c r="C93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Léa</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>LeaBrd</t>
+          <t>Kolas</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3387,30 +3387,30 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>296</v>
+        <v>344</v>
       </c>
       <c r="C94" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Marilena</t>
+          <t>Léa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>GOAT#UE2WM8M9</t>
+          <t>LeaBrd</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3419,25 +3419,25 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>296</v>
+        <v>341</v>
       </c>
       <c r="C95" t="n">
         <v>5</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E95" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Sab_M45</t>
+          <t>dian-bgt</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -3451,16 +3451,16 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>274</v>
+        <v>320</v>
       </c>
       <c r="C96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D96" t="n">
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3483,16 +3483,16 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>268</v>
+        <v>314</v>
       </c>
       <c r="C97" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -3515,30 +3515,30 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>266</v>
+        <v>308</v>
       </c>
       <c r="C98" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D98" t="n">
         <v>2</v>
       </c>
       <c r="E98" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ibra</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>PacoSarra</t>
+          <t>Emma_Noel</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3547,62 +3547,58 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>265</v>
+        <v>306</v>
       </c>
       <c r="C99" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D99" t="n">
         <v>2</v>
       </c>
       <c r="E99" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Fa_One</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>254</v>
+        <v>300</v>
       </c>
       <c r="C100" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>JEVAISGAGNER10</t>
+          <t>K_Marp</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3611,30 +3607,30 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>254</v>
+        <v>296</v>
       </c>
       <c r="C101" t="n">
         <v>5</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Marilena</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>K_Marp</t>
+          <t>GOAT#UE2WM8M9</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3643,58 +3639,62 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="C102" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>ousmane</t>
+          <t>romain</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Taylor2901</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>RomainLect</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>232</v>
+        <v>266</v>
       </c>
       <c r="C103" t="n">
         <v>4</v>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Ibra</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Emma_Noel</t>
+          <t>PacoSarra</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3703,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>230</v>
+        <v>265</v>
       </c>
       <c r="C104" t="n">
         <v>4</v>
@@ -3712,44 +3712,48 @@
         <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Fa_One</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr"/>
+          <t>Fuzo697</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="C105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>romain</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>RomainLect</t>
+          <t>JEVAISGAGNER10</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -3763,48 +3767,44 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>189</v>
+        <v>241</v>
       </c>
       <c r="C106" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>ousmane</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Fuzo697</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>180</v>
+        <v>226</v>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -3827,16 +3827,16 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>158</v>
+        <v>204</v>
       </c>
       <c r="C108" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D108" t="n">
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -3859,16 +3859,16 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>138</v>
+        <v>184</v>
       </c>
       <c r="C109" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>138</v>
+        <v>184</v>
       </c>
       <c r="C110" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>

--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -463,25 +463,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1154</v>
+        <v>1427</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -495,25 +495,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1080</v>
+        <v>1358</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -527,25 +527,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1065</v>
+        <v>1347</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1025</v>
+        <v>1249</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -591,25 +591,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>1007</v>
+        <v>1220</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>938</v>
+        <v>1201</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>922</v>
+        <v>1190</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -687,25 +687,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>915</v>
+        <v>1166</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D9" t="n">
         <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>879</v>
+        <v>1148</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>859</v>
+        <v>1125</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -783,25 +783,25 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>839</v>
+        <v>1115</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -815,30 +815,30 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>801</v>
+        <v>1102</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -847,25 +847,25 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>796</v>
+        <v>1085</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -879,30 +879,30 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>793</v>
+        <v>1066</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Panaf</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Panaff</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -911,30 +911,30 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>792</v>
+        <v>1058</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -943,16 +943,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>774</v>
+        <v>1054</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -975,30 +975,30 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>741</v>
+        <v>1043</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Teddbear</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1007,16 +1007,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>740</v>
+        <v>1030</v>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1039,30 +1039,30 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>733</v>
+        <v>1023</v>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1071,30 +1071,30 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>729</v>
+        <v>1021</v>
       </c>
       <c r="C21" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>Panaf</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>Panaff</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1103,30 +1103,30 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>722</v>
+        <v>1011</v>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brieuc</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Yebri</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1135,30 +1135,30 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>721</v>
+        <v>1009</v>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1167,62 +1167,58 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>689</v>
+        <v>1000</v>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ppo28</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Reste du monde</t>
-        </is>
-      </c>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>674</v>
+        <v>999</v>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1231,30 +1227,30 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>669</v>
+        <v>995</v>
       </c>
       <c r="C26" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D26" t="n">
         <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1263,30 +1259,30 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>666</v>
+        <v>979</v>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1295,25 +1291,25 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>666</v>
+        <v>974</v>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1327,30 +1323,30 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>665</v>
+        <v>967</v>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E29" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Marie__92</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1359,30 +1355,30 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>665</v>
+        <v>962</v>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Timy</t>
+          <t>Romain_JO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1391,30 +1387,30 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>658</v>
+        <v>956</v>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1423,30 +1419,30 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>655</v>
+        <v>956</v>
       </c>
       <c r="C32" t="n">
         <v>7</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E32" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1455,25 +1451,25 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>654</v>
+        <v>954</v>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1487,58 +1483,62 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>649</v>
+        <v>954</v>
       </c>
       <c r="C34" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E34" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>goat</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>goat#AD6GS</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Ilan_260_</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>647</v>
+        <v>929</v>
       </c>
       <c r="C35" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>EmyEnzo</t>
+          <t>YassineZ95</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1547,30 +1547,30 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>640</v>
+        <v>921</v>
       </c>
       <c r="C36" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1579,30 +1579,30 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>635</v>
+        <v>915</v>
       </c>
       <c r="C37" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D37" t="n">
         <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>chaychaychay</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1611,58 +1611,62 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>631</v>
+        <v>909</v>
       </c>
       <c r="C38" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Emilay</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>628</v>
+        <v>909</v>
       </c>
       <c r="C39" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>SabC1</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1671,30 +1675,30 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>625</v>
+        <v>893</v>
       </c>
       <c r="C40" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t>Brieuc</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>Yebri</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1703,25 +1707,25 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>624</v>
+        <v>892</v>
       </c>
       <c r="C41" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D41" t="n">
         <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1735,30 +1739,30 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>622</v>
+        <v>890</v>
       </c>
       <c r="C42" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Romain J</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1767,30 +1771,30 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>616</v>
+        <v>886</v>
       </c>
       <c r="C43" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E43" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1799,90 +1803,90 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>615</v>
+        <v>886</v>
       </c>
       <c r="C44" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mathilde</t>
+          <t>goat</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>MT35T</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>compta</t>
-        </is>
-      </c>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>602</v>
+        <v>880</v>
       </c>
       <c r="C45" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D45" t="n">
         <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1993ahm</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>EmyEnzo</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>597</v>
+        <v>878</v>
       </c>
       <c r="C46" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E46" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1891,25 +1895,25 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>596</v>
+        <v>870</v>
       </c>
       <c r="C47" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Camillewbl</t>
+          <t>Marie__92</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -1923,30 +1927,30 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>594</v>
+        <v>861</v>
       </c>
       <c r="C48" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1955,62 +1959,58 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>581</v>
+        <v>861</v>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D49" t="n">
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Brick</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>574</v>
+        <v>857</v>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SabC1</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2019,25 +2019,25 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>568</v>
+        <v>848</v>
       </c>
       <c r="C51" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2051,30 +2051,30 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>566</v>
+        <v>846</v>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Loïc</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>C4M</t>
+          <t>Exia95</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2083,30 +2083,30 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>565</v>
+        <v>845</v>
       </c>
       <c r="C53" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E53" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t xml:space="preserve">Liliane </t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>LilianeB</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2115,25 +2115,25 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>561</v>
+        <v>836</v>
       </c>
       <c r="C54" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D54" t="n">
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>Timy</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2147,30 +2147,30 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>559</v>
+        <v>832</v>
       </c>
       <c r="C55" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D55" t="n">
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Valentine___</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2179,30 +2179,30 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>558</v>
+        <v>828</v>
       </c>
       <c r="C56" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2211,30 +2211,30 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>555</v>
+        <v>824</v>
       </c>
       <c r="C57" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D57" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liliane </t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>LilianeB</t>
+          <t>Camillewbl</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2243,30 +2243,30 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>553</v>
+        <v>799</v>
       </c>
       <c r="C58" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D58" t="n">
         <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>C4M</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2275,25 +2275,25 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>553</v>
+        <v>785</v>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E59" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Juliie</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>Pipou931</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2307,30 +2307,30 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>544</v>
+        <v>774</v>
       </c>
       <c r="C60" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Elise</t>
+          <t>Selver</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Elisewiss</t>
+          <t>Seesee</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2339,30 +2339,30 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>544</v>
+        <v>770</v>
       </c>
       <c r="C61" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2371,30 +2371,30 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>541</v>
+        <v>765</v>
       </c>
       <c r="C62" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>Devilrock95</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2403,30 +2403,30 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>534</v>
+        <v>765</v>
       </c>
       <c r="C63" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Seesee</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2435,25 +2435,25 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>521</v>
+        <v>763</v>
       </c>
       <c r="C64" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D64" t="n">
         <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Antonio Moctezuma</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>abihuts</t>
+          <t>GLR_PRIME</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2467,30 +2467,30 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>520</v>
+        <v>761</v>
       </c>
       <c r="C65" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D65" t="n">
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Jérémy</t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>JeremFZ</t>
+          <t>Elisewiss</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2499,58 +2499,62 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>519</v>
+        <v>751</v>
       </c>
       <c r="C66" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E66" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>BrickXVI</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>Daviddesco1</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>509</v>
+        <v>745</v>
       </c>
       <c r="C67" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>AudreyB225</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2559,58 +2563,62 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>506</v>
+        <v>744</v>
       </c>
       <c r="C68" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E68" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Soraya</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Francisco93</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>Soraya-Y</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>497</v>
+        <v>738</v>
       </c>
       <c r="C69" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Loïc</t>
+          <t>Antonio Moctezuma</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Exia95</t>
+          <t>abihuts</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2619,25 +2627,25 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>487</v>
+        <v>738</v>
       </c>
       <c r="C70" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D70" t="n">
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
+          <t>Valentine___</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -2651,30 +2659,30 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>484</v>
+        <v>737</v>
       </c>
       <c r="C71" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Jérémy</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>WIL1610</t>
+          <t>JeremFZ</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2683,30 +2691,30 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>484</v>
+        <v>731</v>
       </c>
       <c r="C72" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E72" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Maruyama</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2715,30 +2723,30 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>480</v>
+        <v>731</v>
       </c>
       <c r="C73" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D73" t="n">
         <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
+          <t>AudreyB225</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2747,57 +2755,53 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>479</v>
+        <v>720</v>
       </c>
       <c r="C74" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Cindie</t>
+          <t>François</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cindie_JJA</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>compta</t>
-        </is>
-      </c>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>476</v>
+        <v>719</v>
       </c>
       <c r="C75" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E75" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>GLR_PRIME</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -2811,30 +2815,30 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>465</v>
+        <v>719</v>
       </c>
       <c r="C76" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Juliie</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pipou931</t>
+          <t>Kolas</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2843,30 +2847,30 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>458</v>
+        <v>718</v>
       </c>
       <c r="C77" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D77" t="n">
         <v>2</v>
       </c>
       <c r="E77" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Mathilde</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>MT35T</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2875,30 +2879,30 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>454</v>
+        <v>708</v>
       </c>
       <c r="C78" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D78" t="n">
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Cindie</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>Cindie_JJA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2907,30 +2911,30 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>452</v>
+        <v>703</v>
       </c>
       <c r="C79" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lison</t>
+          <t>Priscilla</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lyzone</t>
+          <t>Priscilla#4LCAF</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2939,30 +2943,30 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>450</v>
+        <v>701</v>
       </c>
       <c r="C80" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Damien</t>
+          <t>William</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>PANENKANY</t>
+          <t>WIL1610</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2971,30 +2975,30 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>445</v>
+        <v>696</v>
       </c>
       <c r="C81" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3003,25 +3007,25 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>439</v>
+        <v>690</v>
       </c>
       <c r="C82" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Erwan</t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Erwan#4G91X</t>
+          <t>Maruyama</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3035,25 +3039,25 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>436</v>
+        <v>682</v>
       </c>
       <c r="C83" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D83" t="n">
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Priscilla</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Priscilla#4LCAF</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3067,30 +3071,30 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>434</v>
+        <v>678</v>
       </c>
       <c r="C84" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3099,30 +3103,30 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>434</v>
+        <v>667</v>
       </c>
       <c r="C85" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>Damien</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>PANENKANY</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3131,30 +3135,30 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>418</v>
+        <v>661</v>
       </c>
       <c r="C86" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E86" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Soraya</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Soraya-Y</t>
+          <t>dian-bgt</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3163,62 +3167,58 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>416</v>
+        <v>655</v>
       </c>
       <c r="C87" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Devilrock95</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>Fa_One</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>411</v>
+        <v>651</v>
       </c>
       <c r="C88" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>MatuRenard</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3227,30 +3227,30 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>396</v>
+        <v>638</v>
       </c>
       <c r="C89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D89" t="n">
         <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mélissa</t>
+          <t>Erwan</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>PavelMel</t>
+          <t>Erwan#4G91X</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3259,16 +3259,16 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>389</v>
+        <v>636</v>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -3291,16 +3291,16 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>388</v>
+        <v>635</v>
       </c>
       <c r="C91" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E91" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -3323,30 +3323,30 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>372</v>
+        <v>616</v>
       </c>
       <c r="C92" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Marilena</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sab_M45</t>
+          <t>GOAT#UE2WM8M9</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3355,94 +3355,86 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>370</v>
+        <v>602</v>
       </c>
       <c r="C93" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E93" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Kolas</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>344</v>
+        <v>578</v>
       </c>
       <c r="C94" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Léa</t>
+          <t>ousmane</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>LeaBrd</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>341</v>
+        <v>572</v>
       </c>
       <c r="C95" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D95" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Léa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
+          <t>LeaBrd</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3451,25 +3443,25 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>320</v>
+        <v>564</v>
       </c>
       <c r="C96" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Lison</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>Lyzone</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -3483,16 +3475,16 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>314</v>
+        <v>563</v>
       </c>
       <c r="C97" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -3515,25 +3507,25 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>308</v>
+        <v>541</v>
       </c>
       <c r="C98" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Emma_Noel</t>
+          <t>Fuzo697</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -3547,58 +3539,62 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>306</v>
+        <v>534</v>
       </c>
       <c r="C99" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Fa_One</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>Melissagzb</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>300</v>
+        <v>530</v>
       </c>
       <c r="C100" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E100" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Ibra</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>K_Marp</t>
+          <t>PacoSarra</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3607,30 +3603,30 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>296</v>
+        <v>491</v>
       </c>
       <c r="C101" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D101" t="n">
         <v>1</v>
       </c>
       <c r="E101" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Marilena</t>
+          <t>Laetitia</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>GOAT#UE2WM8M9</t>
+          <t>Laetice2020</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3639,30 +3635,30 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>270</v>
+        <v>487</v>
       </c>
       <c r="C102" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E102" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>romain</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>RomainLect</t>
+          <t>Emma_Noel</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3671,30 +3667,30 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>266</v>
+        <v>464</v>
       </c>
       <c r="C103" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ibra</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>PacoSarra</t>
+          <t>Sab_M45</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3703,25 +3699,25 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>265</v>
+        <v>440</v>
       </c>
       <c r="C104" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D104" t="n">
         <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Mélissa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Fuzo697</t>
+          <t>PavelMel</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -3735,25 +3731,25 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="C105" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>romain</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>JEVAISGAGNER10</t>
+          <t>RomainLect</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -3767,58 +3763,62 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>241</v>
+        <v>421</v>
       </c>
       <c r="C106" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>ousmane</t>
+          <t>Killian</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Taylor2901</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr"/>
+          <t>KIKS999</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>226</v>
+        <v>419</v>
       </c>
       <c r="C107" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>MxKnight</t>
+          <t>JEVAISGAGNER10</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3827,30 +3827,30 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>204</v>
+        <v>405</v>
       </c>
       <c r="C108" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Killian</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>KIKS999</t>
+          <t>K_Marp</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3859,30 +3859,30 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>184</v>
+        <v>398</v>
       </c>
       <c r="C109" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Laetitia</t>
+          <t>lea</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Laetice2020</t>
+          <t>RBTL</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3891,30 +3891,30 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>184</v>
+        <v>396</v>
       </c>
       <c r="C110" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>lea</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>RBTL</t>
+          <t>MxKnight</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>

--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -463,30 +463,30 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1427</v>
+        <v>1458</v>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -495,25 +495,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1358</v>
+        <v>1441</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1347</v>
+        <v>1427</v>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1249</v>
+        <v>1356</v>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>1220</v>
+        <v>1335</v>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>1201</v>
+        <v>1333</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1190</v>
+        <v>1331</v>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>1166</v>
+        <v>1249</v>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -719,25 +719,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>1148</v>
+        <v>1244</v>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D10" t="n">
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -751,25 +751,25 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>1125</v>
+        <v>1242</v>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -783,25 +783,25 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>1115</v>
+        <v>1234</v>
       </c>
       <c r="C12" t="n">
         <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -815,25 +815,25 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>1102</v>
+        <v>1204</v>
       </c>
       <c r="C13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -847,30 +847,30 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>1085</v>
+        <v>1204</v>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -879,30 +879,30 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>1066</v>
+        <v>1186</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -911,30 +911,30 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>1058</v>
+        <v>1167</v>
       </c>
       <c r="C16" t="n">
         <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -943,30 +943,30 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>1054</v>
+        <v>1162</v>
       </c>
       <c r="C17" t="n">
         <v>14</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Marion1822</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -975,25 +975,25 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>1043</v>
+        <v>1138</v>
       </c>
       <c r="C18" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1007,30 +1007,30 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>1030</v>
+        <v>1131</v>
       </c>
       <c r="C19" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1039,30 +1039,30 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>1023</v>
+        <v>1129</v>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1071,30 +1071,30 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>1021</v>
+        <v>1088</v>
       </c>
       <c r="C21" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Panaf</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Panaff</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1103,16 +1103,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>1011</v>
+        <v>1080</v>
       </c>
       <c r="C22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D22" t="n">
         <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1135,30 +1135,30 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>1009</v>
+        <v>1074</v>
       </c>
       <c r="C23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>YassineZ95</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1167,58 +1167,62 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>1000</v>
+        <v>1066</v>
       </c>
       <c r="C24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>WalidSiuuuuu</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>999</v>
+        <v>1062</v>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1227,30 +1231,30 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>995</v>
+        <v>1061</v>
       </c>
       <c r="C26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1259,25 +1263,25 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>979</v>
+        <v>1057</v>
       </c>
       <c r="C27" t="n">
         <v>14</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1291,25 +1295,25 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>974</v>
+        <v>1045</v>
       </c>
       <c r="C28" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D28" t="n">
         <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>Romain_JO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1323,25 +1327,25 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>967</v>
+        <v>1044</v>
       </c>
       <c r="C29" t="n">
         <v>14</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1355,30 +1359,30 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>962</v>
+        <v>1042</v>
       </c>
       <c r="C30" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Romain J</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1387,30 +1391,30 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>956</v>
+        <v>1035</v>
       </c>
       <c r="C31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Panaf</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Panaff</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1419,30 +1423,30 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>956</v>
+        <v>1032</v>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>Camillewbl</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1451,25 +1455,25 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>954</v>
+        <v>1023</v>
       </c>
       <c r="C33" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1483,25 +1487,25 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>954</v>
+        <v>1011</v>
       </c>
       <c r="C34" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E34" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1515,30 +1519,30 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>929</v>
+        <v>995</v>
       </c>
       <c r="C35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Mathilde</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>MT35T</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1547,30 +1551,30 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>921</v>
+        <v>992</v>
       </c>
       <c r="C36" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
         <v>25</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
+          <t>SabC1</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1579,30 +1583,30 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>915</v>
+        <v>981</v>
       </c>
       <c r="C37" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>Teddbear</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1611,30 +1615,30 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>909</v>
+        <v>973</v>
       </c>
       <c r="C38" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1643,30 +1647,30 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>909</v>
+        <v>970</v>
       </c>
       <c r="C39" t="n">
         <v>12</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SabC1</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1675,16 +1679,16 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>893</v>
+        <v>969</v>
       </c>
       <c r="C40" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D40" t="n">
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1707,62 +1711,58 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>892</v>
+        <v>969</v>
       </c>
       <c r="C41" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>goat</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>890</v>
+        <v>963</v>
       </c>
       <c r="C42" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>EmyEnzo</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1771,25 +1771,25 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>886</v>
+        <v>962</v>
       </c>
       <c r="C43" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Selver</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
+          <t>Seesee</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1803,58 +1803,62 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>886</v>
+        <v>961</v>
       </c>
       <c r="C44" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>goat</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>goat#AD6GS</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>BadrLeo</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>880</v>
+        <v>960</v>
       </c>
       <c r="C45" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D45" t="n">
         <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>EmyEnzo</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1863,25 +1867,25 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>878</v>
+        <v>958</v>
       </c>
       <c r="C46" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>GLR_PRIME</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -1895,30 +1899,30 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>870</v>
+        <v>958</v>
       </c>
       <c r="C47" t="n">
         <v>13</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Marie__92</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1927,30 +1931,30 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>861</v>
+        <v>939</v>
       </c>
       <c r="C48" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>Marie__92</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1959,25 +1963,25 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>861</v>
+        <v>938</v>
       </c>
       <c r="C49" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E49" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>BrickXVI</t>
+          <t>Julie_Romao</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -1987,30 +1991,30 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>857</v>
+        <v>933</v>
       </c>
       <c r="C50" t="n">
         <v>12</v>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E50" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2019,16 +2023,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>848</v>
+        <v>931</v>
       </c>
       <c r="C51" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D51" t="n">
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2051,16 +2055,16 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>846</v>
+        <v>929</v>
       </c>
       <c r="C52" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D52" t="n">
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2083,30 +2087,30 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>845</v>
+        <v>928</v>
       </c>
       <c r="C53" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liliane </t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>LilianeB</t>
+          <t>MatuRenard</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2115,30 +2119,30 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>836</v>
+        <v>915</v>
       </c>
       <c r="C54" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Timy</t>
+          <t>chaychaychay</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2147,16 +2151,16 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>832</v>
+        <v>915</v>
       </c>
       <c r="C55" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D55" t="n">
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2179,30 +2183,30 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>828</v>
+        <v>904</v>
       </c>
       <c r="C56" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2211,25 +2215,25 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>824</v>
+        <v>890</v>
       </c>
       <c r="C57" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Camillewbl</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2243,30 +2247,30 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>799</v>
+        <v>859</v>
       </c>
       <c r="C58" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D58" t="n">
         <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>C4M</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2275,62 +2279,58 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>785</v>
+        <v>845</v>
       </c>
       <c r="C59" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Juliie</t>
+          <t>Brick</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pipou931</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>774</v>
+        <v>844</v>
       </c>
       <c r="C60" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Seesee</t>
+          <t>Elisewiss</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>770</v>
+        <v>836</v>
       </c>
       <c r="C61" t="n">
         <v>11</v>
@@ -2352,12 +2352,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>Timy</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2371,25 +2371,25 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>765</v>
+        <v>830</v>
       </c>
       <c r="C62" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E62" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Devilrock95</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2403,30 +2403,30 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>765</v>
+        <v>827</v>
       </c>
       <c r="C63" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D63" t="n">
         <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Soraya</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>Soraya-Y</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2435,25 +2435,25 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>763</v>
+        <v>822</v>
       </c>
       <c r="C64" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>GLR_PRIME</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2467,30 +2467,30 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>761</v>
+        <v>821</v>
       </c>
       <c r="C65" t="n">
         <v>13</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Elise</t>
+          <t>Antonio Moctezuma</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Elisewiss</t>
+          <t>abihuts</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2499,16 +2499,16 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>751</v>
+        <v>804</v>
       </c>
       <c r="C66" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2531,30 +2531,30 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>745</v>
+        <v>800</v>
       </c>
       <c r="C67" t="n">
         <v>12</v>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Damien</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>PANENKANY</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2563,62 +2563,58 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>744</v>
+        <v>796</v>
       </c>
       <c r="C68" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Soraya</t>
+          <t>François</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Soraya-Y</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>compta</t>
-        </is>
-      </c>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>738</v>
+        <v>794</v>
       </c>
       <c r="C69" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E69" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Antonio Moctezuma</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>abihuts</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2627,30 +2623,30 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>738</v>
+        <v>786</v>
       </c>
       <c r="C70" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E70" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>Priscilla</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Valentine___</t>
+          <t>Priscilla#4LCAF</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2659,25 +2655,25 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>737</v>
+        <v>784</v>
       </c>
       <c r="C71" t="n">
         <v>12</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E71" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Jérémy</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>JeremFZ</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -2691,30 +2687,30 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>731</v>
+        <v>784</v>
       </c>
       <c r="C72" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D72" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>William</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>WIL1610</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2723,30 +2719,30 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>731</v>
+        <v>784</v>
       </c>
       <c r="C73" t="n">
         <v>11</v>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>AudreyB225</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2755,58 +2751,62 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>720</v>
+        <v>783</v>
       </c>
       <c r="C74" t="n">
         <v>12</v>
       </c>
       <c r="D74" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E74" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>François</t>
+          <t xml:space="preserve">Liliane </t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Francisco93</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>LilianeB</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>719</v>
+        <v>779</v>
       </c>
       <c r="C75" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>Devilrock95</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2815,30 +2815,30 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>719</v>
+        <v>769</v>
       </c>
       <c r="C76" t="n">
         <v>13</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76" t="n">
         <v>25</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Juliie</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Kolas</t>
+          <t>Pipou931</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2847,30 +2847,30 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>718</v>
+        <v>766</v>
       </c>
       <c r="C77" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mathilde</t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>MT35T</t>
+          <t>Maruyama</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>708</v>
+        <v>765</v>
       </c>
       <c r="C78" t="n">
         <v>11</v>
@@ -2888,16 +2888,16 @@
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cindie</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cindie_JJA</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -2911,30 +2911,30 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>703</v>
+        <v>752</v>
       </c>
       <c r="C79" t="n">
         <v>12</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Priscilla</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Priscilla#4LCAF</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2943,30 +2943,30 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>701</v>
+        <v>752</v>
       </c>
       <c r="C80" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Lison</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>WIL1610</t>
+          <t>Lyzone</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2975,30 +2975,30 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>696</v>
+        <v>752</v>
       </c>
       <c r="C81" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E81" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>Valentine___</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3007,30 +3007,30 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>690</v>
+        <v>745</v>
       </c>
       <c r="C82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Maruyama</t>
+          <t>AudreyB225</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3039,39 +3039,35 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>682</v>
+        <v>738</v>
       </c>
       <c r="C83" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E83" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>Fa_One</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>678</v>
+        <v>737</v>
       </c>
       <c r="C84" t="n">
         <v>11</v>
@@ -3080,16 +3076,16 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>C4M</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3103,30 +3099,30 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>667</v>
+        <v>733</v>
       </c>
       <c r="C85" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Damien</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>PANENKANY</t>
+          <t>Kolas</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3135,30 +3131,30 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>661</v>
+        <v>722</v>
       </c>
       <c r="C86" t="n">
         <v>11</v>
       </c>
       <c r="D86" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Cindie</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
+          <t>Cindie_JJA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3167,53 +3163,57 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>655</v>
+        <v>708</v>
       </c>
       <c r="C87" t="n">
         <v>12</v>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>Cécile</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fa_One</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>Ceciledp</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>651</v>
+        <v>702</v>
       </c>
       <c r="C88" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>romain</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
+          <t>RomainLect</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3227,30 +3227,30 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>638</v>
+        <v>686</v>
       </c>
       <c r="C89" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E89" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Erwan</t>
+          <t>Laetitia</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Erwan#4G91X</t>
+          <t>Laetice2020</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3259,30 +3259,30 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>636</v>
+        <v>679</v>
       </c>
       <c r="C90" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Camss</t>
+          <t>Melissagzb</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3291,25 +3291,25 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>635</v>
+        <v>675</v>
       </c>
       <c r="C91" t="n">
         <v>11</v>
       </c>
       <c r="D91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Jérémy</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>JeremFZ</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3323,16 +3323,16 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>616</v>
+        <v>669</v>
       </c>
       <c r="C92" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -3355,25 +3355,25 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>602</v>
+        <v>654</v>
       </c>
       <c r="C93" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>ousmane</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>1993ahm</t>
+          <t>Taylor2901</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -3383,7 +3383,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>578</v>
+        <v>652</v>
       </c>
       <c r="C94" t="n">
         <v>10</v>
@@ -3392,49 +3392,53 @@
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ousmane</t>
+          <t>Erwan</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Taylor2901</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>Erwan#4G91X</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>572</v>
+        <v>638</v>
       </c>
       <c r="C95" t="n">
         <v>11</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E95" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Léa</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>LeaBrd</t>
+          <t>dian-bgt</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3443,25 +3447,25 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>564</v>
+        <v>619</v>
       </c>
       <c r="C96" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E96" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lison</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lyzone</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -3475,25 +3479,25 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>563</v>
+        <v>616</v>
       </c>
       <c r="C97" t="n">
         <v>10</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Cécile</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ceciledp</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -3507,62 +3511,58 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>541</v>
+        <v>602</v>
       </c>
       <c r="C98" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E98" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fuzo697</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>534</v>
+        <v>597</v>
       </c>
       <c r="C99" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D99" t="n">
         <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>MxKnight</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3571,30 +3571,30 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>530</v>
+        <v>572</v>
       </c>
       <c r="C100" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ibra</t>
+          <t>Léa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>PacoSarra</t>
+          <t>LeaBrd</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3603,30 +3603,30 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>491</v>
+        <v>570</v>
       </c>
       <c r="C101" t="n">
         <v>10</v>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E101" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Laetitia</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Laetice2020</t>
+          <t>Emma_Noel</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3635,25 +3635,25 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>487</v>
+        <v>555</v>
       </c>
       <c r="C102" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Emma_Noel</t>
+          <t>Fuzo697</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -3667,16 +3667,16 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>464</v>
+        <v>547</v>
       </c>
       <c r="C103" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D103" t="n">
         <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -3699,30 +3699,30 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>440</v>
+        <v>544</v>
       </c>
       <c r="C104" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D104" t="n">
         <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mélissa</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>PavelMel</t>
+          <t>Camss</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3731,30 +3731,30 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>425</v>
+        <v>543</v>
       </c>
       <c r="C105" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>romain</t>
+          <t>lea</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>RomainLect</t>
+          <t>RBTL</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3763,25 +3763,25 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>421</v>
+        <v>530</v>
       </c>
       <c r="C106" t="n">
         <v>9</v>
       </c>
       <c r="D106" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E106" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Killian</t>
+          <t>Ibra</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>KIKS999</t>
+          <t>PacoSarra</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -3795,30 +3795,30 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>419</v>
+        <v>516</v>
       </c>
       <c r="C107" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Mélissa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>JEVAISGAGNER10</t>
+          <t>PavelMel</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3827,30 +3827,30 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>405</v>
+        <v>504</v>
       </c>
       <c r="C108" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Killian</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>K_Marp</t>
+          <t>KIKS999</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3859,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>398</v>
+        <v>488</v>
       </c>
       <c r="C109" t="n">
         <v>9</v>
@@ -3868,21 +3868,21 @@
         <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>lea</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>RBTL</t>
+          <t>K_Marp</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3891,10 +3891,10 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>396</v>
+        <v>433</v>
       </c>
       <c r="C110" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
@@ -3904,17 +3904,17 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>MxKnight</t>
+          <t>JEVAISGAGNER10</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>

--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -463,30 +463,30 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1458</v>
+        <v>1682</v>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -495,30 +495,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1441</v>
+        <v>1667</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1427</v>
+        <v>1641</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1356</v>
+        <v>1574</v>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>1335</v>
+        <v>1533</v>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>1333</v>
+        <v>1525</v>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -655,16 +655,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1331</v>
+        <v>1521</v>
       </c>
       <c r="C8" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>1249</v>
+        <v>1518</v>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>1244</v>
+        <v>1509</v>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D10" t="n">
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>1242</v>
+        <v>1485</v>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -783,30 +783,30 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>1234</v>
+        <v>1475</v>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -815,30 +815,30 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>1204</v>
+        <v>1448</v>
       </c>
       <c r="C13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D13" t="n">
         <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -847,30 +847,30 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>1204</v>
+        <v>1445</v>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D14" t="n">
         <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -879,30 +879,30 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>1186</v>
+        <v>1445</v>
       </c>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -911,16 +911,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>1167</v>
+        <v>1438</v>
       </c>
       <c r="C16" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -943,30 +943,30 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>1162</v>
+        <v>1432</v>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -975,30 +975,30 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>1138</v>
+        <v>1412</v>
       </c>
       <c r="C18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1007,30 +1007,30 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>1131</v>
+        <v>1402</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>Mathilde</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>MT35T</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1039,30 +1039,30 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>1129</v>
+        <v>1389</v>
       </c>
       <c r="C20" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1071,25 +1071,25 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>1088</v>
+        <v>1321</v>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1103,25 +1103,25 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>1080</v>
+        <v>1312</v>
       </c>
       <c r="C22" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>YassineZ95</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1135,25 +1135,25 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>1074</v>
+        <v>1308</v>
       </c>
       <c r="C23" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1167,25 +1167,25 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>1066</v>
+        <v>1303</v>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1199,16 +1199,16 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>1062</v>
+        <v>1303</v>
       </c>
       <c r="C25" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1231,30 +1231,30 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>1061</v>
+        <v>1302</v>
       </c>
       <c r="C26" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E26" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Marion1822</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1263,30 +1263,30 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>1057</v>
+        <v>1285</v>
       </c>
       <c r="C27" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Camillewbl</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1295,30 +1295,30 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>1045</v>
+        <v>1261</v>
       </c>
       <c r="C28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E28" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Romain J</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1327,30 +1327,30 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>1044</v>
+        <v>1254</v>
       </c>
       <c r="C29" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1359,30 +1359,30 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>1042</v>
+        <v>1251</v>
       </c>
       <c r="C30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D30" t="n">
         <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1391,30 +1391,30 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>1035</v>
+        <v>1236</v>
       </c>
       <c r="C31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D31" t="n">
         <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Panaf</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Panaff</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1423,30 +1423,30 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>1032</v>
+        <v>1229</v>
       </c>
       <c r="C32" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E32" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Camillewbl</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1455,30 +1455,30 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>1023</v>
+        <v>1221</v>
       </c>
       <c r="C33" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E33" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1487,25 +1487,25 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>1011</v>
+        <v>1215</v>
       </c>
       <c r="C34" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1519,30 +1519,30 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>995</v>
+        <v>1215</v>
       </c>
       <c r="C35" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mathilde</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>MT35T</t>
+          <t>Romain_JO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1551,30 +1551,30 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>992</v>
+        <v>1214</v>
       </c>
       <c r="C36" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D36" t="n">
         <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SabC1</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1583,30 +1583,30 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>981</v>
+        <v>1211</v>
       </c>
       <c r="C37" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D37" t="n">
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1615,30 +1615,30 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>973</v>
+        <v>1210</v>
       </c>
       <c r="C38" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D38" t="n">
         <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Brieuc</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>Yebri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1647,30 +1647,30 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>970</v>
+        <v>1205</v>
       </c>
       <c r="C39" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Panaf</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Panaff</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1679,76 +1679,76 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>969</v>
+        <v>1199</v>
       </c>
       <c r="C40" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brieuc</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Yebri</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>969</v>
+        <v>1191</v>
       </c>
       <c r="C41" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>goat</t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>goat#AD6GS</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>chaychaychay</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>963</v>
+        <v>1183</v>
       </c>
       <c r="C42" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D42" t="n">
         <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1771,30 +1771,30 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>962</v>
+        <v>1180</v>
       </c>
       <c r="C43" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Seesee</t>
+          <t>Marie__92</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1803,25 +1803,25 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>961</v>
+        <v>1170</v>
       </c>
       <c r="C44" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>Loïc</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>Exia95</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1835,25 +1835,25 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>960</v>
+        <v>1144</v>
       </c>
       <c r="C45" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E45" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Selver</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>Seesee</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -1867,25 +1867,25 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>958</v>
+        <v>1142</v>
       </c>
       <c r="C46" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D46" t="n">
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>GLR_PRIME</t>
+          <t>SabC1</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -1899,30 +1899,30 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>958</v>
+        <v>1140</v>
       </c>
       <c r="C47" t="n">
         <v>13</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E47" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1931,90 +1931,90 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>939</v>
+        <v>1139</v>
       </c>
       <c r="C48" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>goat</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Marie__92</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>938</v>
+        <v>1131</v>
       </c>
       <c r="C49" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Teddbear</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>933</v>
+        <v>1114</v>
       </c>
       <c r="C50" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2023,30 +2023,30 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>931</v>
+        <v>1111</v>
       </c>
       <c r="C51" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>MatuRenard</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2055,30 +2055,30 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>929</v>
+        <v>1104</v>
       </c>
       <c r="C52" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E52" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Loïc</t>
+          <t xml:space="preserve">Liliane </t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Exia95</t>
+          <t>LilianeB</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2087,30 +2087,30 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>928</v>
+        <v>1103</v>
       </c>
       <c r="C53" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E53" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2119,30 +2119,30 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>915</v>
+        <v>1100</v>
       </c>
       <c r="C54" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D54" t="n">
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2151,30 +2151,30 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>915</v>
+        <v>1095</v>
       </c>
       <c r="C55" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
+          <t>Maruyama</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2183,25 +2183,25 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>904</v>
+        <v>1087</v>
       </c>
       <c r="C56" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E56" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>GLR_PRIME</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2215,30 +2215,30 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>890</v>
+        <v>1083</v>
       </c>
       <c r="C57" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E57" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2247,25 +2247,25 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>859</v>
+        <v>1071</v>
       </c>
       <c r="C58" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2279,58 +2279,62 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>845</v>
+        <v>1068</v>
       </c>
       <c r="C59" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E59" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Soraya</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>BrickXVI</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>Soraya-Y</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>844</v>
+        <v>1062</v>
       </c>
       <c r="C60" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Elise</t>
+          <t>Antonio Moctezuma</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Elisewiss</t>
+          <t>abihuts</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2339,62 +2343,58 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>836</v>
+        <v>1057</v>
       </c>
       <c r="C61" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>François</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Timy</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>830</v>
+        <v>1055</v>
       </c>
       <c r="C62" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2403,30 +2403,30 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>827</v>
+        <v>1045</v>
       </c>
       <c r="C63" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D63" t="n">
         <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Soraya</t>
+          <t>William</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Soraya-Y</t>
+          <t>WIL1610</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2435,25 +2435,25 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>822</v>
+        <v>1045</v>
       </c>
       <c r="C64" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2467,30 +2467,30 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>821</v>
+        <v>1040</v>
       </c>
       <c r="C65" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D65" t="n">
         <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Antonio Moctezuma</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>abihuts</t>
+          <t>Devilrock95</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2499,30 +2499,30 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>804</v>
+        <v>1035</v>
       </c>
       <c r="C66" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E66" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2531,57 +2531,53 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>800</v>
+        <v>1035</v>
       </c>
       <c r="C67" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Damien</t>
+          <t>Brick</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>PANENKANY</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>796</v>
+        <v>1029</v>
       </c>
       <c r="C68" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E68" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Francisco93</t>
+          <t>Fa_One</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -2591,30 +2587,30 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>794</v>
+        <v>1025</v>
       </c>
       <c r="C69" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D69" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E69" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2623,25 +2619,25 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>786</v>
+        <v>1022</v>
       </c>
       <c r="C70" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Priscilla</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Priscilla#4LCAF</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -2655,30 +2651,30 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>784</v>
+        <v>1015</v>
       </c>
       <c r="C71" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D71" t="n">
         <v>3</v>
       </c>
       <c r="E71" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2687,30 +2683,30 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>784</v>
+        <v>1010</v>
       </c>
       <c r="C72" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D72" t="n">
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Juliie</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>WIL1610</t>
+          <t>Pipou931</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2719,30 +2715,30 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>784</v>
+        <v>1003</v>
       </c>
       <c r="C73" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Damien</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>PANENKANY</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2751,30 +2747,30 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>783</v>
+        <v>994</v>
       </c>
       <c r="C74" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D74" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E74" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liliane </t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>LilianeB</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2783,30 +2779,30 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>779</v>
+        <v>993</v>
       </c>
       <c r="C75" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Lison</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Devilrock95</t>
+          <t>Lyzone</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2815,30 +2811,30 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>769</v>
+        <v>986</v>
       </c>
       <c r="C76" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D76" t="n">
         <v>2</v>
       </c>
       <c r="E76" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Juliie</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pipou931</t>
+          <t>AudreyB225</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2847,30 +2843,30 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>766</v>
+        <v>986</v>
       </c>
       <c r="C77" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E77" t="n">
         <v>27</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Maruyama</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2879,30 +2875,30 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>765</v>
+        <v>981</v>
       </c>
       <c r="C78" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E78" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2911,30 +2907,30 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>752</v>
+        <v>978</v>
       </c>
       <c r="C79" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>C4M</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2943,30 +2939,30 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>752</v>
+        <v>976</v>
       </c>
       <c r="C80" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E80" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lison</t>
+          <t>Priscilla</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lyzone</t>
+          <t>Priscilla#4LCAF</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2975,30 +2971,30 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>752</v>
+        <v>973</v>
       </c>
       <c r="C81" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Valentine___</t>
+          <t>Elisewiss</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3007,30 +3003,30 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>745</v>
+        <v>965</v>
       </c>
       <c r="C82" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E82" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>AudreyB225</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3039,53 +3035,57 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>738</v>
+        <v>960</v>
       </c>
       <c r="C83" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D83" t="n">
         <v>2</v>
       </c>
       <c r="E83" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>Marilena</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fa_One</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>GOAT#UE2WM8M9</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>737</v>
+        <v>949</v>
       </c>
       <c r="C84" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Cécile</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>C4M</t>
+          <t>Ceciledp</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3099,16 +3099,16 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>733</v>
+        <v>913</v>
       </c>
       <c r="C85" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3131,30 +3131,30 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>722</v>
+        <v>909</v>
       </c>
       <c r="C86" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E86" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cindie</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cindie_JJA</t>
+          <t>dian-bgt</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3163,25 +3163,25 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>708</v>
+        <v>894</v>
       </c>
       <c r="C87" t="n">
         <v>12</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cécile</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ceciledp</t>
+          <t>Timy</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3195,30 +3195,30 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>702</v>
+        <v>892</v>
       </c>
       <c r="C88" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D88" t="n">
         <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>romain</t>
+          <t>Cindie</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>RomainLect</t>
+          <t>Cindie_JJA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3227,30 +3227,30 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>686</v>
+        <v>885</v>
       </c>
       <c r="C89" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Laetitia</t>
+          <t>romain</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Laetice2020</t>
+          <t>RomainLect</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3259,30 +3259,30 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>679</v>
+        <v>865</v>
       </c>
       <c r="C90" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Jérémy</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>JeremFZ</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3291,30 +3291,30 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>675</v>
+        <v>864</v>
       </c>
       <c r="C91" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E91" t="n">
         <v>27</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Jérémy</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>JeremFZ</t>
+          <t>Valentine___</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3323,25 +3323,25 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>669</v>
+        <v>840</v>
       </c>
       <c r="C92" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E92" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Marilena</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>GOAT#UE2WM8M9</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3355,44 +3355,48 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>654</v>
+        <v>836</v>
       </c>
       <c r="C93" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E93" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ousmane</t>
+          <t>Laetitia</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Taylor2901</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+          <t>Laetice2020</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>652</v>
+        <v>822</v>
       </c>
       <c r="C94" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D94" t="n">
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -3415,30 +3419,30 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>638</v>
+        <v>820</v>
       </c>
       <c r="C95" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
+          <t>K_Marp</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3447,30 +3451,30 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>619</v>
+        <v>811</v>
       </c>
       <c r="C96" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D96" t="n">
         <v>2</v>
       </c>
       <c r="E96" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>Emma_Noel</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3479,90 +3483,90 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>616</v>
+        <v>804</v>
       </c>
       <c r="C97" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>ousmane</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>602</v>
+        <v>796</v>
       </c>
       <c r="C98" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>1993ahm</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>Fuzo697</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>597</v>
+        <v>786</v>
       </c>
       <c r="C99" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E99" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>MxKnight</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3571,16 +3575,16 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>572</v>
+        <v>777</v>
       </c>
       <c r="C100" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -3603,30 +3607,30 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>570</v>
+        <v>764</v>
       </c>
       <c r="C101" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D101" t="n">
         <v>2</v>
       </c>
       <c r="E101" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Emma_Noel</t>
+          <t>MxKnight</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3635,30 +3639,30 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>555</v>
+        <v>745</v>
       </c>
       <c r="C102" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D102" t="n">
         <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Killian</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Fuzo697</t>
+          <t>KIKS999</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3667,30 +3671,30 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>547</v>
+        <v>730</v>
       </c>
       <c r="C103" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E103" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Ibra</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sab_M45</t>
+          <t>PacoSarra</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3699,30 +3703,30 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>544</v>
+        <v>720</v>
       </c>
       <c r="C104" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E104" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Camss</t>
+          <t>Melissagzb</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3731,16 +3735,16 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>543</v>
+        <v>692</v>
       </c>
       <c r="C105" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -3763,30 +3767,30 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>530</v>
+        <v>676</v>
       </c>
       <c r="C106" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ibra</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>PacoSarra</t>
+          <t>Sab_M45</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3795,16 +3799,16 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>516</v>
+        <v>648</v>
       </c>
       <c r="C107" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -3827,30 +3831,30 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>504</v>
+        <v>636</v>
       </c>
       <c r="C108" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D108" t="n">
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Killian</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>KIKS999</t>
+          <t>Camss</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3859,30 +3863,30 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>488</v>
+        <v>613</v>
       </c>
       <c r="C109" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>K_Marp</t>
+          <t>JEVAISGAGNER10</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3891,32 +3895,28 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>433</v>
+        <v>602</v>
       </c>
       <c r="C110" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E110" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>JEVAISGAGNER10</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Reste du monde</t>
-        </is>
-      </c>
+          <t>1993ahm</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -463,30 +463,30 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1682</v>
+        <v>1863</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -495,30 +495,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1667</v>
+        <v>1853</v>
       </c>
       <c r="C3" t="n">
         <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1641</v>
+        <v>1840</v>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1574</v>
+        <v>1758</v>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>1533</v>
+        <v>1751</v>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>1525</v>
+        <v>1732</v>
       </c>
       <c r="C7" t="n">
         <v>20</v>
@@ -632,21 +632,21 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -655,16 +655,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1521</v>
+        <v>1717</v>
       </c>
       <c r="C8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>1518</v>
+        <v>1708</v>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -719,16 +719,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>1509</v>
+        <v>1705</v>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D10" t="n">
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>1485</v>
+        <v>1671</v>
       </c>
       <c r="C11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -783,30 +783,30 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>1475</v>
+        <v>1644</v>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -815,30 +815,30 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>1448</v>
+        <v>1638</v>
       </c>
       <c r="C13" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D13" t="n">
         <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -847,30 +847,30 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>1445</v>
+        <v>1628</v>
       </c>
       <c r="C14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -879,30 +879,30 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>1445</v>
+        <v>1577</v>
       </c>
       <c r="C15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>1438</v>
+        <v>1566</v>
       </c>
       <c r="C16" t="n">
         <v>19</v>
@@ -920,21 +920,21 @@
         <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -943,30 +943,30 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>1432</v>
+        <v>1560</v>
       </c>
       <c r="C17" t="n">
         <v>18</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Mathilde</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>MT35T</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -975,30 +975,30 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>1412</v>
+        <v>1536</v>
       </c>
       <c r="C18" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1007,25 +1007,25 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>1402</v>
+        <v>1518</v>
       </c>
       <c r="C19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D19" t="n">
         <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mathilde</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MT35T</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1039,30 +1039,30 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>1389</v>
+        <v>1503</v>
       </c>
       <c r="C20" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1071,30 +1071,30 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>1321</v>
+        <v>1499</v>
       </c>
       <c r="C21" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1103,30 +1103,30 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>1312</v>
+        <v>1499</v>
       </c>
       <c r="C22" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D22" t="n">
         <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1135,30 +1135,30 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>1308</v>
+        <v>1498</v>
       </c>
       <c r="C23" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E23" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1167,30 +1167,30 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>1303</v>
+        <v>1481</v>
       </c>
       <c r="C24" t="n">
         <v>20</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>Camillewbl</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1199,25 +1199,25 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>1303</v>
+        <v>1477</v>
       </c>
       <c r="C25" t="n">
         <v>19</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t>Panaf</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>Panaff</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1231,25 +1231,25 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>1302</v>
+        <v>1471</v>
       </c>
       <c r="C26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1263,30 +1263,30 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>1285</v>
+        <v>1450</v>
       </c>
       <c r="C27" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Camillewbl</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1295,25 +1295,25 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>1261</v>
+        <v>1447</v>
       </c>
       <c r="C28" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1327,30 +1327,30 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>1254</v>
+        <v>1410</v>
       </c>
       <c r="C29" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1359,30 +1359,30 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>1251</v>
+        <v>1394</v>
       </c>
       <c r="C30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Marion1822</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1391,30 +1391,30 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>1236</v>
+        <v>1388</v>
       </c>
       <c r="C31" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1423,25 +1423,25 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>1229</v>
+        <v>1379</v>
       </c>
       <c r="C32" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E32" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>YassineZ95</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1455,30 +1455,30 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>1221</v>
+        <v>1376</v>
       </c>
       <c r="C33" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>Marie__92</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1487,30 +1487,30 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>1215</v>
+        <v>1372</v>
       </c>
       <c r="C34" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E34" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1519,30 +1519,30 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>1215</v>
+        <v>1366</v>
       </c>
       <c r="C35" t="n">
         <v>18</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E35" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Romain J</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1551,25 +1551,25 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>1214</v>
+        <v>1359</v>
       </c>
       <c r="C36" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D36" t="n">
         <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>MatuRenard</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1583,30 +1583,30 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>1211</v>
+        <v>1354</v>
       </c>
       <c r="C37" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E37" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t xml:space="preserve">Liliane </t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>LilianeB</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1615,30 +1615,30 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>1210</v>
+        <v>1352</v>
       </c>
       <c r="C38" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brieuc</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Yebri</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1647,30 +1647,30 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>1205</v>
+        <v>1350</v>
       </c>
       <c r="C39" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Panaf</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Panaff</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1679,53 +1679,57 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>1199</v>
+        <v>1349</v>
       </c>
       <c r="C40" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>chaychaychay</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>1191</v>
+        <v>1342</v>
       </c>
       <c r="C41" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E41" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>EmyEnzo</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1739,30 +1743,30 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>1183</v>
+        <v>1340</v>
       </c>
       <c r="C42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E42" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Selver</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>EmyEnzo</t>
+          <t>Seesee</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1771,30 +1775,30 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>1180</v>
+        <v>1340</v>
       </c>
       <c r="C43" t="n">
         <v>18</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Marie__92</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1803,30 +1807,30 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>1170</v>
+        <v>1339</v>
       </c>
       <c r="C44" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Loïc</t>
+          <t>Brieuc</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Exia95</t>
+          <t>Yebri</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1835,30 +1839,30 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>1144</v>
+        <v>1338</v>
       </c>
       <c r="C45" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Seesee</t>
+          <t>SabC1</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1867,30 +1871,30 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>1142</v>
+        <v>1320</v>
       </c>
       <c r="C46" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SabC1</t>
+          <t>Romain_JO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1899,30 +1903,30 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>1140</v>
+        <v>1308</v>
       </c>
       <c r="C47" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1931,58 +1935,62 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>1139</v>
+        <v>1298</v>
       </c>
       <c r="C48" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E48" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>goat</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>goat#AD6GS</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>BadrLeo</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>1131</v>
+        <v>1296</v>
       </c>
       <c r="C49" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1991,30 +1999,30 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>1114</v>
+        <v>1291</v>
       </c>
       <c r="C50" t="n">
         <v>18</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>Maruyama</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2023,94 +2031,86 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>1111</v>
+        <v>1290</v>
       </c>
       <c r="C51" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E51" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Reste du monde</t>
-        </is>
-      </c>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>1104</v>
+        <v>1283</v>
       </c>
       <c r="C52" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D52" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E52" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liliane </t>
+          <t>François</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>LilianeB</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>1103</v>
+        <v>1283</v>
       </c>
       <c r="C53" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E53" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>GLR_PRIME</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2119,30 +2119,30 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>1100</v>
+        <v>1281</v>
       </c>
       <c r="C54" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2151,30 +2151,30 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>1095</v>
+        <v>1279</v>
       </c>
       <c r="C55" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E55" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Maruyama</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2183,30 +2183,30 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>1087</v>
+        <v>1275</v>
       </c>
       <c r="C56" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Loïc</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>GLR_PRIME</t>
+          <t>Exia95</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2215,25 +2215,25 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>1083</v>
+        <v>1271</v>
       </c>
       <c r="C57" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2247,62 +2247,58 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>1071</v>
+        <v>1255</v>
       </c>
       <c r="C58" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E58" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>Fa_One</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>1068</v>
+        <v>1254</v>
       </c>
       <c r="C59" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Soraya</t>
+          <t>romain</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Soraya-Y</t>
+          <t>RomainLect</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2311,25 +2307,25 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>1062</v>
+        <v>1252</v>
       </c>
       <c r="C60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E60" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Antonio Moctezuma</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>abihuts</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2343,58 +2339,62 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>1057</v>
+        <v>1236</v>
       </c>
       <c r="C61" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Francisco93</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>Devilrock95</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>1055</v>
+        <v>1231</v>
       </c>
       <c r="C62" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E62" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2403,62 +2403,58 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>1045</v>
+        <v>1231</v>
       </c>
       <c r="C63" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D63" t="n">
         <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Brick</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>WIL1610</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Reste du monde</t>
-        </is>
-      </c>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>1045</v>
+        <v>1222</v>
       </c>
       <c r="C64" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>Teddbear</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2467,30 +2463,30 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>1040</v>
+        <v>1218</v>
       </c>
       <c r="C65" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E65" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Devilrock95</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2499,25 +2495,25 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>1035</v>
+        <v>1215</v>
       </c>
       <c r="C66" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E66" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
+          <t>Kolas</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2531,81 +2527,89 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>1035</v>
+        <v>1202</v>
       </c>
       <c r="C67" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E67" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Priscilla</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>BrickXVI</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>Priscilla#4LCAF</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>1029</v>
+        <v>1197</v>
       </c>
       <c r="C68" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E68" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>Antonio Moctezuma</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fa_One</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>abihuts</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>1025</v>
+        <v>1191</v>
       </c>
       <c r="C69" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>Juliie</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>Pipou931</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -2619,30 +2623,30 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>1022</v>
+        <v>1191</v>
       </c>
       <c r="C70" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E70" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Erwan</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>Erwan#4G91X</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2651,30 +2655,30 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>1015</v>
+        <v>1184</v>
       </c>
       <c r="C71" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E71" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2683,30 +2687,30 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>1010</v>
+        <v>1182</v>
       </c>
       <c r="C72" t="n">
         <v>17</v>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E72" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Juliie</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pipou931</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2715,30 +2719,30 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>1003</v>
+        <v>1181</v>
       </c>
       <c r="C73" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Damien</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>PANENKANY</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2747,25 +2751,25 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>994</v>
+        <v>1162</v>
       </c>
       <c r="C74" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D74" t="n">
         <v>3</v>
       </c>
       <c r="E74" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -2779,30 +2783,30 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>993</v>
+        <v>1150</v>
       </c>
       <c r="C75" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E75" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lison</t>
+          <t>William</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lyzone</t>
+          <t>WIL1610</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2811,16 +2815,16 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>986</v>
+        <v>1144</v>
       </c>
       <c r="C76" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D76" t="n">
         <v>2</v>
       </c>
       <c r="E76" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -2843,62 +2847,58 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>986</v>
+        <v>1139</v>
       </c>
       <c r="C77" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>goat</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>981</v>
+        <v>1128</v>
       </c>
       <c r="C78" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>Timy</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2907,25 +2907,25 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>978</v>
+        <v>1122</v>
       </c>
       <c r="C79" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Lison</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>C4M</t>
+          <t>Lyzone</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -2939,30 +2939,30 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>976</v>
+        <v>1107</v>
       </c>
       <c r="C80" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Priscilla</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Priscilla#4LCAF</t>
+          <t>C4M</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2971,30 +2971,30 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>973</v>
+        <v>1105</v>
       </c>
       <c r="C81" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E81" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Elise</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Elisewiss</t>
+          <t>dian-bgt</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3003,30 +3003,30 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>965</v>
+        <v>1089</v>
       </c>
       <c r="C82" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D82" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E82" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Marilena</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>GOAT#UE2WM8M9</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3035,30 +3035,30 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>960</v>
+        <v>1088</v>
       </c>
       <c r="C83" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Marilena</t>
+          <t>Cindie</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>GOAT#UE2WM8M9</t>
+          <t>Cindie_JJA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3067,30 +3067,30 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>949</v>
+        <v>1068</v>
       </c>
       <c r="C84" t="n">
         <v>16</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E84" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cécile</t>
+          <t>Soraya</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ceciledp</t>
+          <t>Soraya-Y</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3099,30 +3099,30 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>913</v>
+        <v>1061</v>
       </c>
       <c r="C85" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D85" t="n">
         <v>2</v>
       </c>
       <c r="E85" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Jérémy</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Kolas</t>
+          <t>JeremFZ</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3131,25 +3131,25 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>909</v>
+        <v>1054</v>
       </c>
       <c r="C86" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D86" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Cécile</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
+          <t>Ceciledp</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3163,30 +3163,30 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>894</v>
+        <v>1053</v>
       </c>
       <c r="C87" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E87" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Timy</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3195,30 +3195,30 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>892</v>
+        <v>1041</v>
       </c>
       <c r="C88" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cindie</t>
+          <t>Damien</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cindie_JJA</t>
+          <t>PANENKANY</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3227,30 +3227,30 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>885</v>
+        <v>1032</v>
       </c>
       <c r="C89" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E89" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>romain</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>RomainLect</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3259,30 +3259,30 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>865</v>
+        <v>1007</v>
       </c>
       <c r="C90" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D90" t="n">
         <v>2</v>
       </c>
       <c r="E90" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Jérémy</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>JeremFZ</t>
+          <t>Emma_Noel</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3291,30 +3291,30 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>864</v>
+        <v>998</v>
       </c>
       <c r="C91" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D91" t="n">
         <v>3</v>
       </c>
       <c r="E91" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Valentine___</t>
+          <t>Melissagzb</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3323,25 +3323,25 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>840</v>
+        <v>981</v>
       </c>
       <c r="C92" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E92" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3355,30 +3355,30 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>836</v>
+        <v>978</v>
       </c>
       <c r="C93" t="n">
         <v>15</v>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Laetitia</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Laetice2020</t>
+          <t>K_Marp</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3387,30 +3387,30 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>822</v>
+        <v>973</v>
       </c>
       <c r="C94" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D94" t="n">
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Erwan</t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Erwan#4G91X</t>
+          <t>Elisewiss</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3419,30 +3419,30 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>820</v>
+        <v>969</v>
       </c>
       <c r="C95" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E95" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>K_Marp</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3451,30 +3451,30 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>811</v>
+        <v>932</v>
       </c>
       <c r="C96" t="n">
         <v>14</v>
       </c>
       <c r="D96" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E96" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Emma_Noel</t>
+          <t>Valentine___</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3483,58 +3483,62 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>804</v>
+        <v>926</v>
       </c>
       <c r="C97" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E97" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>ousmane</t>
+          <t>Ibra</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Taylor2901</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>PacoSarra</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>796</v>
+        <v>915</v>
       </c>
       <c r="C98" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E98" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fuzo697</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3543,30 +3547,30 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>786</v>
+        <v>869</v>
       </c>
       <c r="C99" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D99" t="n">
         <v>2</v>
       </c>
       <c r="E99" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>MxKnight</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3575,62 +3579,58 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>777</v>
+        <v>842</v>
       </c>
       <c r="C100" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Léa</t>
+          <t>ousmane</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>LeaBrd</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>764</v>
+        <v>836</v>
       </c>
       <c r="C101" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D101" t="n">
         <v>2</v>
       </c>
       <c r="E101" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Laetitia</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>MxKnight</t>
+          <t>Laetice2020</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3639,30 +3639,30 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>745</v>
+        <v>834</v>
       </c>
       <c r="C102" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D102" t="n">
         <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Killian</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>KIKS999</t>
+          <t>Fuzo697</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3671,30 +3671,30 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>730</v>
+        <v>821</v>
       </c>
       <c r="C103" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D103" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ibra</t>
+          <t>lea</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>PacoSarra</t>
+          <t>RBTL</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3703,30 +3703,30 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>720</v>
+        <v>809</v>
       </c>
       <c r="C104" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>JEVAISGAGNER10</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3735,30 +3735,30 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>692</v>
+        <v>783</v>
       </c>
       <c r="C105" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>lea</t>
+          <t>Killian</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>RBTL</t>
+          <t>KIKS999</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3767,16 +3767,16 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>676</v>
+        <v>781</v>
       </c>
       <c r="C106" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D106" t="n">
         <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -3799,25 +3799,25 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>648</v>
+        <v>777</v>
       </c>
       <c r="C107" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mélissa</t>
+          <t>Léa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>PavelMel</t>
+          <t>LeaBrd</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -3831,16 +3831,16 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>636</v>
+        <v>674</v>
       </c>
       <c r="C108" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D108" t="n">
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -3863,30 +3863,30 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>613</v>
+        <v>648</v>
       </c>
       <c r="C109" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E109" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Mélissa</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>JEVAISGAGNER10</t>
+          <t>PavelMel</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>

--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -463,30 +463,30 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2209</v>
+        <v>2292</v>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>2162</v>
+        <v>2275</v>
       </c>
       <c r="C3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>2155</v>
+        <v>2269</v>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>2125</v>
+        <v>2265</v>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
         <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>2078</v>
+        <v>2228</v>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>2066</v>
+        <v>2185</v>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>2041</v>
+        <v>2179</v>
       </c>
       <c r="C8" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -687,16 +687,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>2026</v>
+        <v>2163</v>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -719,16 +719,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>2010</v>
+        <v>2147</v>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -751,16 +751,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>2007</v>
+        <v>2144</v>
       </c>
       <c r="C11" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -783,25 +783,25 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>1996</v>
+        <v>2126</v>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -815,30 +815,30 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>1989</v>
+        <v>2126</v>
       </c>
       <c r="C13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -847,30 +847,30 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>1980</v>
+        <v>2109</v>
       </c>
       <c r="C14" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -879,25 +879,25 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>1968</v>
+        <v>2040</v>
       </c>
       <c r="C15" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -911,30 +911,30 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>1942</v>
+        <v>2028</v>
       </c>
       <c r="C16" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -943,25 +943,25 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>1932</v>
+        <v>2004</v>
       </c>
       <c r="C17" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -975,30 +975,30 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>1886</v>
+        <v>1995</v>
       </c>
       <c r="C18" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>Marie__92</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1007,30 +1007,30 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>1885</v>
+        <v>1992</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Marie__92</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1039,16 +1039,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>1882</v>
+        <v>1992</v>
       </c>
       <c r="C20" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1071,30 +1071,30 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>1869</v>
+        <v>1963</v>
       </c>
       <c r="C21" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1103,30 +1103,30 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>1867</v>
+        <v>1955</v>
       </c>
       <c r="C22" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1135,25 +1135,25 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>1852</v>
+        <v>1946</v>
       </c>
       <c r="C23" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E23" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1167,30 +1167,30 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>1794</v>
+        <v>1939</v>
       </c>
       <c r="C24" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E24" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1199,25 +1199,25 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>1785</v>
+        <v>1931</v>
       </c>
       <c r="C25" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Camillewbl</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1231,30 +1231,30 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>1771</v>
+        <v>1929</v>
       </c>
       <c r="C26" t="n">
         <v>27</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1263,30 +1263,30 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>1769</v>
+        <v>1912</v>
       </c>
       <c r="C27" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1295,48 +1295,44 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>1768</v>
+        <v>1896</v>
       </c>
       <c r="C28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E28" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Kaliced</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>compta</t>
-        </is>
-      </c>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>1753</v>
+        <v>1890</v>
       </c>
       <c r="C29" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D29" t="n">
         <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1359,16 +1355,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>1746</v>
+        <v>1883</v>
       </c>
       <c r="C30" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D30" t="n">
         <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1391,16 +1387,16 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>1735</v>
+        <v>1872</v>
       </c>
       <c r="C31" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D31" t="n">
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1423,30 +1419,30 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>1735</v>
+        <v>1869</v>
       </c>
       <c r="C32" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1455,25 +1451,25 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>1730</v>
+        <v>1858</v>
       </c>
       <c r="C33" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>MatuRenard</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1487,30 +1483,30 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>1722</v>
+        <v>1845</v>
       </c>
       <c r="C34" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mathilde</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>MT35T</t>
+          <t>Camillewbl</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1519,30 +1515,30 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>1712</v>
+        <v>1840</v>
       </c>
       <c r="C35" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E35" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>EmyEnzo</t>
+          <t>YassineZ95</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1551,30 +1547,30 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>1682</v>
+        <v>1831</v>
       </c>
       <c r="C36" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1583,30 +1579,30 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>1675</v>
+        <v>1829</v>
       </c>
       <c r="C37" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D37" t="n">
         <v>7</v>
       </c>
       <c r="E37" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1615,30 +1611,30 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>1672</v>
+        <v>1813</v>
       </c>
       <c r="C38" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E38" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>EmyEnzo</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1647,30 +1643,30 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>1671</v>
+        <v>1804</v>
       </c>
       <c r="C39" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D39" t="n">
         <v>5</v>
       </c>
       <c r="E39" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
+          <t>Romain_JO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1679,16 +1675,16 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>1660</v>
+        <v>1797</v>
       </c>
       <c r="C40" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D40" t="n">
         <v>7</v>
       </c>
       <c r="E40" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1711,30 +1707,30 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>1659</v>
+        <v>1782</v>
       </c>
       <c r="C41" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E41" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brieuc</t>
+          <t>Mathilde</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Yebri</t>
+          <t>MT35T</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1743,30 +1739,30 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>1658</v>
+        <v>1781</v>
       </c>
       <c r="C42" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D42" t="n">
         <v>6</v>
       </c>
       <c r="E42" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1775,30 +1771,30 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>1644</v>
+        <v>1779</v>
       </c>
       <c r="C43" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1807,30 +1803,30 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>1642</v>
+        <v>1764</v>
       </c>
       <c r="C44" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D44" t="n">
         <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Loïc</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>Exia95</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1839,16 +1835,16 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>1632</v>
+        <v>1762</v>
       </c>
       <c r="C45" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E45" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1871,58 +1867,62 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>1632</v>
+        <v>1738</v>
       </c>
       <c r="C46" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D46" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E46" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Rosa_1009</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>1627</v>
+        <v>1732</v>
       </c>
       <c r="C47" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E47" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Loïc</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Exia95</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1931,30 +1931,30 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>1621</v>
+        <v>1718</v>
       </c>
       <c r="C48" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E48" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Kolas</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1963,30 +1963,30 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>1617</v>
+        <v>1709</v>
       </c>
       <c r="C49" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E49" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Romain J</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1995,30 +1995,30 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>1612</v>
+        <v>1699</v>
       </c>
       <c r="C50" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D50" t="n">
         <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>Devilrock95</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2027,30 +2027,30 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>1582</v>
+        <v>1687</v>
       </c>
       <c r="C51" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2059,30 +2059,30 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>1579</v>
+        <v>1672</v>
       </c>
       <c r="C52" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D52" t="n">
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>AudreyB225</t>
+          <t>chaychaychay</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2091,30 +2091,30 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>1573</v>
+        <v>1660</v>
       </c>
       <c r="C53" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D53" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E53" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t>Antonio Moctezuma</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Seesee</t>
+          <t>abihuts</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2123,30 +2123,30 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>1573</v>
+        <v>1659</v>
       </c>
       <c r="C54" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>romain</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>RomainLect</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2155,58 +2155,62 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>1567</v>
+        <v>1659</v>
       </c>
       <c r="C55" t="n">
         <v>25</v>
       </c>
       <c r="D55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Brieuc</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Francisco93</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>Yebri</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>1562</v>
+        <v>1650</v>
       </c>
       <c r="C56" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E56" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Devilrock95</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2215,30 +2219,30 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>1556</v>
+        <v>1645</v>
       </c>
       <c r="C57" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D57" t="n">
         <v>5</v>
       </c>
       <c r="E57" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>Kolas</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2247,30 +2251,30 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>1551</v>
+        <v>1640</v>
       </c>
       <c r="C58" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D58" t="n">
         <v>5</v>
       </c>
       <c r="E58" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2279,30 +2283,30 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>1540</v>
+        <v>1639</v>
       </c>
       <c r="C59" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D59" t="n">
         <v>3</v>
       </c>
       <c r="E59" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Erwan</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Erwan#4G91X</t>
+          <t>AudreyB225</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2311,62 +2315,58 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>1523</v>
+        <v>1634</v>
       </c>
       <c r="C60" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E60" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Antonio Moctezuma</t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>abihuts</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Fa_One</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>1523</v>
+        <v>1633</v>
       </c>
       <c r="C61" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D61" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E61" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2375,62 +2375,58 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>1517</v>
+        <v>1627</v>
       </c>
       <c r="C62" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E62" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>François</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Reste du monde</t>
-        </is>
-      </c>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>1503</v>
+        <v>1611</v>
       </c>
       <c r="C63" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D63" t="n">
         <v>5</v>
       </c>
       <c r="E63" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Priscilla</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
+          <t>Priscilla#4LCAF</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2439,25 +2435,25 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>1497</v>
+        <v>1603</v>
       </c>
       <c r="C64" t="n">
         <v>25</v>
       </c>
       <c r="D64" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E64" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>Brick</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fa_One</t>
+          <t>BrickXVI</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -2467,30 +2463,30 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>1496</v>
+        <v>1600</v>
       </c>
       <c r="C65" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E65" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>romain</t>
+          <t>Erwan</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>RomainLect</t>
+          <t>Erwan#4G91X</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2499,25 +2495,25 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>1474</v>
+        <v>1597</v>
       </c>
       <c r="C66" t="n">
         <v>24</v>
       </c>
       <c r="D66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E66" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Priscilla</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Priscilla#4LCAF</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2531,58 +2527,62 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>1473</v>
+        <v>1597</v>
       </c>
       <c r="C67" t="n">
         <v>23</v>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E67" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Selver</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>BrickXVI</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>Seesee</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>1461</v>
+        <v>1580</v>
       </c>
       <c r="C68" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E68" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Maruyama</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2591,30 +2591,30 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>1460</v>
+        <v>1577</v>
       </c>
       <c r="C69" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D69" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E69" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2623,25 +2623,25 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>1458</v>
+        <v>1571</v>
       </c>
       <c r="C70" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>GLR_PRIME</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -2655,30 +2655,30 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>1444</v>
+        <v>1534</v>
       </c>
       <c r="C71" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E71" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>dian-bgt</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2687,25 +2687,25 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>1434</v>
+        <v>1524</v>
       </c>
       <c r="C72" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D72" t="n">
         <v>3</v>
       </c>
       <c r="E72" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>Jérémy</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>JeremFZ</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -2719,30 +2719,30 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>1433</v>
+        <v>1521</v>
       </c>
       <c r="C73" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D73" t="n">
         <v>4</v>
       </c>
       <c r="E73" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>Maruyama</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2751,30 +2751,30 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>1423</v>
+        <v>1521</v>
       </c>
       <c r="C74" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E74" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2783,30 +2783,30 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>1422</v>
+        <v>1516</v>
       </c>
       <c r="C75" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D75" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>Elisewiss</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2815,25 +2815,25 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>1416</v>
+        <v>1503</v>
       </c>
       <c r="C76" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Juliie</t>
+          <t>Cécile</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pipou931</t>
+          <t>Ceciledp</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -2847,25 +2847,25 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>1397</v>
+        <v>1495</v>
       </c>
       <c r="C77" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D77" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Lison</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
+          <t>Lyzone</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -2879,30 +2879,30 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>1392</v>
+        <v>1493</v>
       </c>
       <c r="C78" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E78" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cindie</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cindie_JJA</t>
+          <t>Melissagzb</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2911,30 +2911,30 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>1389</v>
+        <v>1490</v>
       </c>
       <c r="C79" t="n">
         <v>23</v>
       </c>
       <c r="D79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E79" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>William</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>WIL1610</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2943,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>1389</v>
+        <v>1482</v>
       </c>
       <c r="C80" t="n">
         <v>21</v>
@@ -2952,21 +2952,21 @@
         <v>4</v>
       </c>
       <c r="E80" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>Teddbear</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2975,25 +2975,25 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>1387</v>
+        <v>1458</v>
       </c>
       <c r="C81" t="n">
         <v>23</v>
       </c>
       <c r="D81" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E81" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Jérémy</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>JeremFZ</t>
+          <t>GLR_PRIME</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3007,30 +3007,30 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>1358</v>
+        <v>1452</v>
       </c>
       <c r="C82" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lison</t>
+          <t>Cindie</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lyzone</t>
+          <t>Cindie_JJA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3039,30 +3039,30 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>1354</v>
+        <v>1449</v>
       </c>
       <c r="C83" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D83" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E83" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>William</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>WIL1610</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3071,30 +3071,30 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>1349</v>
+        <v>1447</v>
       </c>
       <c r="C84" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E84" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Soraya</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>C4M</t>
+          <t>Soraya-Y</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3103,30 +3103,30 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>1329</v>
+        <v>1440</v>
       </c>
       <c r="C85" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Elise</t>
+          <t>Juliie</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Elisewiss</t>
+          <t>Pipou931</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3135,30 +3135,30 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>1329</v>
+        <v>1422</v>
       </c>
       <c r="C86" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E86" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>K_Marp</t>
+          <t>Fuzo697</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3167,30 +3167,30 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>1310</v>
+        <v>1414</v>
       </c>
       <c r="C87" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E87" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Soraya</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Soraya-Y</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3199,30 +3199,30 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>1296</v>
+        <v>1407</v>
       </c>
       <c r="C88" t="n">
         <v>23</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cécile</t>
+          <t>Damien</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ceciledp</t>
+          <t>PANENKANY</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3231,25 +3231,25 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>1277</v>
+        <v>1402</v>
       </c>
       <c r="C89" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D89" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E89" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ibra</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>PacoSarra</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3263,30 +3263,30 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>1276</v>
+        <v>1390</v>
       </c>
       <c r="C90" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E90" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Timy</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>1272</v>
+        <v>1389</v>
       </c>
       <c r="C91" t="n">
         <v>22</v>
@@ -3304,21 +3304,21 @@
         <v>2</v>
       </c>
       <c r="E91" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Marilena</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>GOAT#UE2WM8M9</t>
+          <t>K_Marp</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3327,30 +3327,30 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>1261</v>
+        <v>1389</v>
       </c>
       <c r="C92" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D92" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>Timy</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3359,25 +3359,25 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>1253</v>
+        <v>1387</v>
       </c>
       <c r="C93" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D93" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E93" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Ibra</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>PacoSarra</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3391,30 +3391,30 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>1247</v>
+        <v>1373</v>
       </c>
       <c r="C94" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E94" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>MxKnight</t>
+          <t>C4M</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3423,30 +3423,30 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>1235</v>
+        <v>1307</v>
       </c>
       <c r="C95" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D95" t="n">
         <v>3</v>
       </c>
       <c r="E95" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fuzo697</t>
+          <t>MxKnight</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3455,30 +3455,30 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>1220</v>
+        <v>1296</v>
       </c>
       <c r="C96" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D96" t="n">
         <v>2</v>
       </c>
       <c r="E96" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Damien</t>
+          <t>Marilena</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>PANENKANY</t>
+          <t>GOAT#UE2WM8M9</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3487,25 +3487,25 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>1215</v>
+        <v>1285</v>
       </c>
       <c r="C97" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D97" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E97" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -3519,16 +3519,16 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>1212</v>
+        <v>1272</v>
       </c>
       <c r="C98" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D98" t="n">
         <v>4</v>
       </c>
       <c r="E98" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -3551,25 +3551,25 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>1190</v>
+        <v>1271</v>
       </c>
       <c r="C99" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>lea</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Emma_Noel</t>
+          <t>RBTL</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -3583,53 +3583,57 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>1139</v>
+        <v>1258</v>
       </c>
       <c r="C100" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E100" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>goat#AD6GS</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>JEVAISGAGNER10</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>1134</v>
+        <v>1250</v>
       </c>
       <c r="C101" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E101" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>lea</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>RBTL</t>
+          <t>Emma_Noel</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -3643,48 +3647,44 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>1121</v>
+        <v>1240</v>
       </c>
       <c r="C102" t="n">
         <v>19</v>
       </c>
       <c r="D102" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>JEVAISGAGNER10</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Reste du monde</t>
-        </is>
-      </c>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>1084</v>
+        <v>1221</v>
       </c>
       <c r="C103" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D103" t="n">
         <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -3703,30 +3703,30 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>1010</v>
+        <v>1121</v>
       </c>
       <c r="C104" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D104" t="n">
         <v>2</v>
       </c>
       <c r="E104" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Léa</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>LeaBrd</t>
+          <t>Sab_M45</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3735,30 +3735,30 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>984</v>
+        <v>1073</v>
       </c>
       <c r="C105" t="n">
         <v>17</v>
       </c>
       <c r="D105" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E105" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Sab_M45</t>
+          <t>Valentine___</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3767,30 +3767,30 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>963</v>
+        <v>1070</v>
       </c>
       <c r="C106" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D106" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E106" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>Léa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Valentine___</t>
+          <t>LeaBrd</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3799,16 +3799,16 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>946</v>
+        <v>1056</v>
       </c>
       <c r="C107" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E107" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -3831,30 +3831,30 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>899</v>
+        <v>935</v>
       </c>
       <c r="C108" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E108" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Killian</t>
+          <t>Mélissa</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>KIKS999</t>
+          <t>PavelMel</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3863,30 +3863,30 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>808</v>
+        <v>899</v>
       </c>
       <c r="C109" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mélissa</t>
+          <t>Killian</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>PavelMel</t>
+          <t>KIKS999</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>

--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2292</v>
+        <v>2635</v>
       </c>
       <c r="C2" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>2275</v>
+        <v>2618</v>
       </c>
       <c r="C3" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>2269</v>
+        <v>2551</v>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>2265</v>
+        <v>2524</v>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>2228</v>
+        <v>2499</v>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>2185</v>
+        <v>2472</v>
       </c>
       <c r="C7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>2179</v>
+        <v>2431</v>
       </c>
       <c r="C8" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>2163</v>
+        <v>2431</v>
       </c>
       <c r="C9" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -719,16 +719,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>2147</v>
+        <v>2402</v>
       </c>
       <c r="C10" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>2144</v>
+        <v>2364</v>
       </c>
       <c r="C11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -783,30 +783,30 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>2126</v>
+        <v>2347</v>
       </c>
       <c r="C12" t="n">
         <v>32</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -815,25 +815,25 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>2126</v>
+        <v>2338</v>
       </c>
       <c r="C13" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -847,25 +847,25 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>2109</v>
+        <v>2298</v>
       </c>
       <c r="C14" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -879,25 +879,25 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>2040</v>
+        <v>2283</v>
       </c>
       <c r="C15" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -911,30 +911,30 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>2028</v>
+        <v>2262</v>
       </c>
       <c r="C16" t="n">
         <v>29</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -943,16 +943,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>2004</v>
+        <v>2259</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -975,16 +975,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>1995</v>
+        <v>2250</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1007,30 +1007,30 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>1992</v>
+        <v>2247</v>
       </c>
       <c r="C19" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1039,16 +1039,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>1992</v>
+        <v>2247</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D20" t="n">
         <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1071,30 +1071,30 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>1963</v>
+        <v>2210</v>
       </c>
       <c r="C21" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1103,30 +1103,30 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>1955</v>
+        <v>2186</v>
       </c>
       <c r="C22" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1135,25 +1135,25 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>1946</v>
+        <v>2171</v>
       </c>
       <c r="C23" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>SabC1</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1167,25 +1167,25 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>1939</v>
+        <v>2164</v>
       </c>
       <c r="C24" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D24" t="n">
         <v>7</v>
       </c>
       <c r="E24" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1199,30 +1199,30 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>1931</v>
+        <v>2161</v>
       </c>
       <c r="C25" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1231,30 +1231,30 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>1929</v>
+        <v>2139</v>
       </c>
       <c r="C26" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1263,25 +1263,25 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>1912</v>
+        <v>2129</v>
       </c>
       <c r="C27" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1295,7 +1295,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>1896</v>
+        <v>2114</v>
       </c>
       <c r="C28" t="n">
         <v>25</v>
@@ -1304,49 +1304,53 @@
         <v>7</v>
       </c>
       <c r="E28" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Chadia__</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>1890</v>
+        <v>2108</v>
       </c>
       <c r="C29" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D29" t="n">
         <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Panaf</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SabC1</t>
+          <t>Panaff</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1355,25 +1359,25 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>1883</v>
+        <v>2104</v>
       </c>
       <c r="C30" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1387,30 +1391,30 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>1872</v>
+        <v>2084</v>
       </c>
       <c r="C31" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E31" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Panaf</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Panaff</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1419,30 +1423,30 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>1869</v>
+        <v>2067</v>
       </c>
       <c r="C32" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D32" t="n">
         <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1451,30 +1455,30 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>1858</v>
+        <v>2055</v>
       </c>
       <c r="C33" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E33" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1483,30 +1487,30 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>1845</v>
+        <v>2054</v>
       </c>
       <c r="C34" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E34" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Camillewbl</t>
+          <t>YassineZ95</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1515,30 +1519,30 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>1840</v>
+        <v>2020</v>
       </c>
       <c r="C35" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D35" t="n">
         <v>5</v>
       </c>
       <c r="E35" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Loïc</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>Exia95</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1547,30 +1551,30 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>1831</v>
+        <v>2020</v>
       </c>
       <c r="C36" t="n">
         <v>29</v>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>EmyEnzo</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1579,30 +1583,30 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>1829</v>
+        <v>2018</v>
       </c>
       <c r="C37" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D37" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Mathilde</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>MT35T</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1611,25 +1615,25 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>1813</v>
+        <v>2013</v>
       </c>
       <c r="C38" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D38" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>EmyEnzo</t>
+          <t>Camillewbl</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1643,30 +1647,30 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>1804</v>
+        <v>2003</v>
       </c>
       <c r="C39" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D39" t="n">
         <v>5</v>
       </c>
       <c r="E39" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Romain J</t>
+          <t>Antonio Moctezuma</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
+          <t>abihuts</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1675,25 +1679,25 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>1797</v>
+        <v>1993</v>
       </c>
       <c r="C40" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D40" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liliane </t>
+          <t>David</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>LilianeB</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1707,30 +1711,30 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>1782</v>
+        <v>1988</v>
       </c>
       <c r="C41" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E41" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mathilde</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>MT35T</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1739,30 +1743,30 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>1781</v>
+        <v>1985</v>
       </c>
       <c r="C42" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E42" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1771,30 +1775,30 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>1779</v>
+        <v>1972</v>
       </c>
       <c r="C43" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E43" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>Romain_JO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1803,30 +1807,30 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>1764</v>
+        <v>1961</v>
       </c>
       <c r="C44" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E44" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Loïc</t>
+          <t xml:space="preserve">Liliane </t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Exia95</t>
+          <t>LilianeB</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1835,25 +1839,25 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>1762</v>
+        <v>1958</v>
       </c>
       <c r="C45" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E45" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -1867,25 +1871,25 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>1738</v>
+        <v>1954</v>
       </c>
       <c r="C46" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D46" t="n">
         <v>6</v>
       </c>
       <c r="E46" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -1899,30 +1903,30 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>1732</v>
+        <v>1951</v>
       </c>
       <c r="C47" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D47" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E47" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>Devilrock95</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1931,62 +1935,58 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>1718</v>
+        <v>1950</v>
       </c>
       <c r="C48" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D48" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E48" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>François</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>1709</v>
+        <v>1943</v>
       </c>
       <c r="C49" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D49" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>Cécile</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>Ceciledp</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1995,30 +1995,30 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>1699</v>
+        <v>1935</v>
       </c>
       <c r="C50" t="n">
         <v>30</v>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E50" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Devilrock95</t>
+          <t>MatuRenard</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2027,62 +2027,58 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>1687</v>
+        <v>1925</v>
       </c>
       <c r="C51" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E51" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>JKInternational</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>1672</v>
+        <v>1919</v>
       </c>
       <c r="C52" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2091,62 +2087,58 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>1660</v>
+        <v>1908</v>
       </c>
       <c r="C53" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E53" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Antonio Moctezuma</t>
+          <t>Brick</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>abihuts</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>1659</v>
+        <v>1906</v>
       </c>
       <c r="C54" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E54" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>romain</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>RomainLect</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2155,30 +2147,30 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>1659</v>
+        <v>1895</v>
       </c>
       <c r="C55" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E55" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brieuc</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Yebri</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2187,62 +2179,58 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>1650</v>
+        <v>1889</v>
       </c>
       <c r="C56" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D56" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E56" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Reste du monde</t>
-        </is>
-      </c>
+          <t>Fa_One</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>1645</v>
+        <v>1889</v>
       </c>
       <c r="C57" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Kolas</t>
+          <t>Elisewiss</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2251,30 +2239,30 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>1640</v>
+        <v>1866</v>
       </c>
       <c r="C58" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D58" t="n">
         <v>5</v>
       </c>
       <c r="E58" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Priscilla</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
+          <t>Priscilla#4LCAF</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2283,30 +2271,30 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>1639</v>
+        <v>1836</v>
       </c>
       <c r="C59" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D59" t="n">
         <v>3</v>
       </c>
       <c r="E59" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>AudreyB225</t>
+          <t>chaychaychay</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2315,58 +2303,62 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>1634</v>
+        <v>1836</v>
       </c>
       <c r="C60" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>Erwan</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fa_One</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Erwan#4G91X</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>1633</v>
+        <v>1834</v>
       </c>
       <c r="C61" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E61" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Brieuc</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>Yebri</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2375,58 +2367,62 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>1627</v>
+        <v>1832</v>
       </c>
       <c r="C62" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E62" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Francisco93</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>Filipinho95</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>1611</v>
+        <v>1826</v>
       </c>
       <c r="C63" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Priscilla</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Priscilla#4LCAF</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2435,53 +2431,57 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>1603</v>
+        <v>1825</v>
       </c>
       <c r="C64" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E64" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>BrickXVI</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>BadrLeo</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>1600</v>
+        <v>1813</v>
       </c>
       <c r="C65" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E65" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Erwan</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Erwan#4G91X</t>
+          <t>Kolas</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2495,30 +2495,30 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>1597</v>
+        <v>1812</v>
       </c>
       <c r="C66" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E66" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2527,30 +2527,30 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>1597</v>
+        <v>1807</v>
       </c>
       <c r="C67" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D67" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Seesee</t>
+          <t>AudreyB225</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2559,25 +2559,25 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>1580</v>
+        <v>1789</v>
       </c>
       <c r="C68" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D68" t="n">
         <v>5</v>
       </c>
       <c r="E68" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>dian-bgt</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -2591,30 +2591,30 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>1577</v>
+        <v>1788</v>
       </c>
       <c r="C69" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E69" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>Marilena</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>GOAT#UE2WM8M9</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2623,30 +2623,30 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>1571</v>
+        <v>1787</v>
       </c>
       <c r="C70" t="n">
         <v>25</v>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E70" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>Teddbear</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2655,30 +2655,30 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>1534</v>
+        <v>1778</v>
       </c>
       <c r="C71" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D71" t="n">
         <v>5</v>
       </c>
       <c r="E71" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2687,30 +2687,30 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>1524</v>
+        <v>1745</v>
       </c>
       <c r="C72" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E72" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Jérémy</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>JeremFZ</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2719,30 +2719,30 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>1521</v>
+        <v>1736</v>
       </c>
       <c r="C73" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>romain</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Maruyama</t>
+          <t>RomainLect</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2751,25 +2751,25 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>1521</v>
+        <v>1727</v>
       </c>
       <c r="C74" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D74" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E74" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -2783,30 +2783,30 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>1516</v>
+        <v>1724</v>
       </c>
       <c r="C75" t="n">
         <v>25</v>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E75" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Elise</t>
+          <t>Selver</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Elisewiss</t>
+          <t>Seesee</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2815,30 +2815,30 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>1503</v>
+        <v>1705</v>
       </c>
       <c r="C76" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E76" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Cécile</t>
+          <t>William</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ceciledp</t>
+          <t>WIL1610</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2847,30 +2847,30 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>1495</v>
+        <v>1702</v>
       </c>
       <c r="C77" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E77" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lison</t>
+          <t>Soraya</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lyzone</t>
+          <t>Soraya-Y</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2879,25 +2879,25 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>1493</v>
+        <v>1692</v>
       </c>
       <c r="C78" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E78" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Damien</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>PANENKANY</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -2911,30 +2911,30 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>1490</v>
+        <v>1685</v>
       </c>
       <c r="C79" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D79" t="n">
         <v>4</v>
       </c>
       <c r="E79" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>Maruyama</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2943,25 +2943,25 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>1482</v>
+        <v>1679</v>
       </c>
       <c r="C80" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D80" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E80" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -2975,30 +2975,30 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>1458</v>
+        <v>1665</v>
       </c>
       <c r="C81" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D81" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E81" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>GLR_PRIME</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3007,30 +3007,30 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>1452</v>
+        <v>1663</v>
       </c>
       <c r="C82" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cindie</t>
+          <t>Lison</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cindie_JJA</t>
+          <t>Lyzone</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>1449</v>
+        <v>1646</v>
       </c>
       <c r="C83" t="n">
         <v>25</v>
@@ -3048,21 +3048,21 @@
         <v>3</v>
       </c>
       <c r="E83" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>WIL1610</t>
+          <t>K_Marp</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3071,30 +3071,30 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>1447</v>
+        <v>1645</v>
       </c>
       <c r="C84" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E84" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Soraya</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Soraya-Y</t>
+          <t>Fuzo697</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3103,30 +3103,30 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>1440</v>
+        <v>1641</v>
       </c>
       <c r="C85" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Juliie</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pipou931</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3135,25 +3135,25 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>1422</v>
+        <v>1638</v>
       </c>
       <c r="C86" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D86" t="n">
         <v>4</v>
       </c>
       <c r="E86" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fuzo697</t>
+          <t>Melissagzb</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3167,30 +3167,30 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>1414</v>
+        <v>1623</v>
       </c>
       <c r="C87" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D87" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E87" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Ibra</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>PacoSarra</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3199,30 +3199,30 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>1407</v>
+        <v>1616</v>
       </c>
       <c r="C88" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Damien</t>
+          <t>Cindie</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>PANENKANY</t>
+          <t>Cindie_JJA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3231,30 +3231,30 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>1402</v>
+        <v>1612</v>
       </c>
       <c r="C89" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D89" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E89" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>Timy</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3263,30 +3263,30 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>1390</v>
+        <v>1611</v>
       </c>
       <c r="C90" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E90" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Jérémy</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>JeremFZ</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3295,30 +3295,30 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>1389</v>
+        <v>1595</v>
       </c>
       <c r="C91" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D91" t="n">
         <v>2</v>
       </c>
       <c r="E91" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Juliie</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>K_Marp</t>
+          <t>Pipou931</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3327,30 +3327,30 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>1389</v>
+        <v>1582</v>
       </c>
       <c r="C92" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E92" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Timy</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3359,25 +3359,25 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>1387</v>
+        <v>1555</v>
       </c>
       <c r="C93" t="n">
         <v>23</v>
       </c>
       <c r="D93" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E93" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ibra</t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>PacoSarra</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3391,30 +3391,30 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>1373</v>
+        <v>1540</v>
       </c>
       <c r="C94" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E94" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>C4M</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3423,30 +3423,30 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>1307</v>
+        <v>1537</v>
       </c>
       <c r="C95" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E95" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>MxKnight</t>
+          <t>C4M</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3455,30 +3455,30 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>1296</v>
+        <v>1508</v>
       </c>
       <c r="C96" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D96" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E96" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Marilena</t>
+          <t>Laetitia</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>GOAT#UE2WM8M9</t>
+          <t>Laetice2020</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3487,30 +3487,30 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>1285</v>
+        <v>1486</v>
       </c>
       <c r="C97" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D97" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>Emma_Noel</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3519,62 +3519,58 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>1272</v>
+        <v>1473</v>
       </c>
       <c r="C98" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D98" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E98" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Laetitia</t>
+          <t>ousmane</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Laetice2020</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>1271</v>
+        <v>1472</v>
       </c>
       <c r="C99" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E99" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>lea</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>RBTL</t>
+          <t>MxKnight</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3583,16 +3579,16 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>1258</v>
+        <v>1472</v>
       </c>
       <c r="C100" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E100" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -3615,30 +3611,30 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>1250</v>
+        <v>1458</v>
       </c>
       <c r="C101" t="n">
         <v>23</v>
       </c>
       <c r="D101" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E101" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Emma_Noel</t>
+          <t>GLR_PRIME</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3647,53 +3643,57 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>1240</v>
+        <v>1439</v>
       </c>
       <c r="C102" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>lea</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>goat#AD6GS</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>RBTL</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>1221</v>
+        <v>1404</v>
       </c>
       <c r="C103" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D103" t="n">
         <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ousmane</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Taylor2901</t>
+          <t>goat#AD6GS</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
@@ -3703,30 +3703,30 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>1121</v>
+        <v>1316</v>
       </c>
       <c r="C104" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D104" t="n">
         <v>2</v>
       </c>
       <c r="E104" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Léa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sab_M45</t>
+          <t>LeaBrd</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3735,30 +3735,30 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>1073</v>
+        <v>1296</v>
       </c>
       <c r="C105" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D105" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E105" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Valentine___</t>
+          <t>Sab_M45</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3767,30 +3767,30 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>1070</v>
+        <v>1270</v>
       </c>
       <c r="C106" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D106" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E106" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Léa</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>LeaBrd</t>
+          <t>Camss</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3799,30 +3799,30 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>1056</v>
+        <v>1237</v>
       </c>
       <c r="C107" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D107" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E107" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Camss</t>
+          <t>Valentine___</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3831,30 +3831,30 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>935</v>
+        <v>1184</v>
       </c>
       <c r="C108" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mélissa</t>
+          <t>Killian</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>PavelMel</t>
+          <t>KIKS999</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3863,30 +3863,30 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>899</v>
+        <v>983</v>
       </c>
       <c r="C109" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E109" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Killian</t>
+          <t>Mélissa</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>KIKS999</t>
+          <t>PavelMel</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>

--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,30 +463,30 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2635</v>
+        <v>2940</v>
       </c>
       <c r="C2" t="n">
         <v>38</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -495,30 +495,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>2618</v>
+        <v>2892</v>
       </c>
       <c r="C3" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -527,16 +527,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>2551</v>
+        <v>2789</v>
       </c>
       <c r="C4" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>2524</v>
+        <v>2772</v>
       </c>
       <c r="C5" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -591,25 +591,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>2499</v>
+        <v>2761</v>
       </c>
       <c r="C6" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>2472</v>
+        <v>2664</v>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>2431</v>
+        <v>2608</v>
       </c>
       <c r="C8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>2431</v>
+        <v>2588</v>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>2402</v>
+        <v>2581</v>
       </c>
       <c r="C10" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>2364</v>
+        <v>2581</v>
       </c>
       <c r="C11" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -783,30 +783,30 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>2347</v>
+        <v>2580</v>
       </c>
       <c r="C12" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -815,30 +815,30 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>2338</v>
+        <v>2577</v>
       </c>
       <c r="C13" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -847,30 +847,30 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>2298</v>
+        <v>2531</v>
       </c>
       <c r="C14" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -879,16 +879,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>2283</v>
+        <v>2520</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -911,30 +911,30 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>2262</v>
+        <v>2517</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>SabC1</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -943,30 +943,30 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>2259</v>
+        <v>2499</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -975,30 +975,30 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>2250</v>
+        <v>2460</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Marie__92</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1007,30 +1007,30 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>2247</v>
+        <v>2456</v>
       </c>
       <c r="C19" t="n">
         <v>34</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1039,30 +1039,30 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>2247</v>
+        <v>2449</v>
       </c>
       <c r="C20" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>Panaf</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Marion1822</t>
+          <t>Panaff</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1071,30 +1071,30 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>2210</v>
+        <v>2447</v>
       </c>
       <c r="C21" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1103,30 +1103,30 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>2186</v>
+        <v>2443</v>
       </c>
       <c r="C22" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1135,25 +1135,25 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>2171</v>
+        <v>2423</v>
       </c>
       <c r="C23" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SabC1</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1167,25 +1167,25 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>2164</v>
+        <v>2415</v>
       </c>
       <c r="C24" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1199,25 +1199,25 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>2161</v>
+        <v>2405</v>
       </c>
       <c r="C25" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E25" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1231,25 +1231,25 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>2139</v>
+        <v>2401</v>
       </c>
       <c r="C26" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1263,30 +1263,30 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>2129</v>
+        <v>2379</v>
       </c>
       <c r="C27" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>Marie__92</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1295,25 +1295,25 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>2114</v>
+        <v>2376</v>
       </c>
       <c r="C28" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D28" t="n">
         <v>7</v>
       </c>
       <c r="E28" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1327,30 +1327,30 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>2108</v>
+        <v>2374</v>
       </c>
       <c r="C29" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Panaf</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Panaff</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1359,30 +1359,30 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>2104</v>
+        <v>2365</v>
       </c>
       <c r="C30" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1391,30 +1391,30 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>2084</v>
+        <v>2364</v>
       </c>
       <c r="C31" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D31" t="n">
         <v>7</v>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Antonio Moctezuma</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>abihuts</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1423,30 +1423,30 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>2067</v>
+        <v>2345</v>
       </c>
       <c r="C32" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E32" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1455,30 +1455,30 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>2055</v>
+        <v>2342</v>
       </c>
       <c r="C33" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Loïc</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>Exia95</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1487,30 +1487,30 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>2054</v>
+        <v>2342</v>
       </c>
       <c r="C34" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D34" t="n">
         <v>6</v>
       </c>
       <c r="E34" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1519,30 +1519,30 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>2020</v>
+        <v>2341</v>
       </c>
       <c r="C35" t="n">
         <v>33</v>
       </c>
       <c r="D35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Loïc</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Exia95</t>
+          <t>EmyEnzo</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1551,30 +1551,30 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>2020</v>
+        <v>2326</v>
       </c>
       <c r="C36" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D36" t="n">
         <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>EmyEnzo</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1583,30 +1583,30 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>2018</v>
+        <v>2315</v>
       </c>
       <c r="C37" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mathilde</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>MT35T</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1615,30 +1615,30 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>2013</v>
+        <v>2314</v>
       </c>
       <c r="C38" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E38" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Camillewbl</t>
+          <t>Romain_JO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1647,25 +1647,25 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>2003</v>
+        <v>2312</v>
       </c>
       <c r="C39" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D39" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E39" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Antonio Moctezuma</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>abihuts</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1679,62 +1679,58 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>1993</v>
+        <v>2299</v>
       </c>
       <c r="C40" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E40" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Brick</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>1988</v>
+        <v>2294</v>
       </c>
       <c r="C41" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1743,30 +1739,30 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>1985</v>
+        <v>2286</v>
       </c>
       <c r="C42" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E42" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1775,30 +1771,30 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>1972</v>
+        <v>2270</v>
       </c>
       <c r="C43" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D43" t="n">
         <v>5</v>
       </c>
       <c r="E43" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Romain J</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
+          <t>Camillewbl</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1807,30 +1803,30 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>1961</v>
+        <v>2251</v>
       </c>
       <c r="C44" t="n">
         <v>30</v>
       </c>
       <c r="D44" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E44" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liliane </t>
+          <t>Mathilde</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>LilianeB</t>
+          <t>MT35T</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1839,30 +1835,30 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>1958</v>
+        <v>2198</v>
       </c>
       <c r="C45" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D45" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E45" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t xml:space="preserve">Liliane </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>LilianeB</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1871,30 +1867,30 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>1954</v>
+        <v>2189</v>
       </c>
       <c r="C46" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>Devilrock95</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1903,90 +1899,90 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>1951</v>
+        <v>2187</v>
       </c>
       <c r="C47" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E47" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>François</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Devilrock95</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>1950</v>
+        <v>2187</v>
       </c>
       <c r="C48" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E48" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Francisco93</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Chadia__</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>1943</v>
+        <v>2176</v>
       </c>
       <c r="C49" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E49" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cécile</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ceciledp</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1995,30 +1991,30 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>1935</v>
+        <v>2173</v>
       </c>
       <c r="C50" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E50" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2027,58 +2023,62 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>1925</v>
+        <v>2165</v>
       </c>
       <c r="C51" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E51" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>MyriamAmr</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>1919</v>
+        <v>2158</v>
       </c>
       <c r="C52" t="n">
         <v>32</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E52" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>Melissagzb</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2087,44 +2087,48 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>1908</v>
+        <v>2158</v>
       </c>
       <c r="C53" t="n">
         <v>29</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E53" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>BrickXVI</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>YassineZ95</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>1906</v>
+        <v>2143</v>
       </c>
       <c r="C54" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E54" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2147,76 +2151,76 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>1895</v>
+        <v>2143</v>
       </c>
       <c r="C55" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E55" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>1889</v>
+        <v>2128</v>
       </c>
       <c r="C56" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E56" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fa_One</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Teddbear</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>1889</v>
+        <v>2126</v>
       </c>
       <c r="C57" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E57" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2239,30 +2243,30 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>1866</v>
+        <v>2124</v>
       </c>
       <c r="C58" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Priscilla</t>
+          <t>Cécile</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Priscilla#4LCAF</t>
+          <t>Ceciledp</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2271,25 +2275,25 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>1836</v>
+        <v>2120</v>
       </c>
       <c r="C59" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E59" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>Priscilla</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>Priscilla#4LCAF</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2303,30 +2307,30 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>1836</v>
+        <v>2089</v>
       </c>
       <c r="C60" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E60" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Erwan</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Erwan#4G91X</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2335,30 +2339,30 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>1834</v>
+        <v>2073</v>
       </c>
       <c r="C61" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D61" t="n">
         <v>4</v>
       </c>
       <c r="E61" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Brieuc</t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Yebri</t>
+          <t>chaychaychay</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2367,30 +2371,30 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>1832</v>
+        <v>2067</v>
       </c>
       <c r="C62" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D62" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E62" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2399,30 +2403,30 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>1826</v>
+        <v>2062</v>
       </c>
       <c r="C63" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D63" t="n">
         <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>romain</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>RomainLect</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2431,30 +2435,30 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>1825</v>
+        <v>2050</v>
       </c>
       <c r="C64" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E64" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>Kolas</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2467,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>1813</v>
+        <v>2049</v>
       </c>
       <c r="C65" t="n">
         <v>29</v>
@@ -2472,21 +2476,21 @@
         <v>5</v>
       </c>
       <c r="E65" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Kolas</t>
+          <t>K_Marp</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2495,30 +2499,30 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>1812</v>
+        <v>2044</v>
       </c>
       <c r="C66" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E66" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>MatuRenard</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2527,16 +2531,16 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>1807</v>
+        <v>2044</v>
       </c>
       <c r="C67" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E67" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2559,25 +2563,25 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>1789</v>
+        <v>2028</v>
       </c>
       <c r="C68" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D68" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -2591,30 +2595,30 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>1788</v>
+        <v>2026</v>
       </c>
       <c r="C69" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D69" t="n">
         <v>4</v>
       </c>
       <c r="E69" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Marilena</t>
+          <t>William</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>GOAT#UE2WM8M9</t>
+          <t>WIL1610</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2623,30 +2627,30 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>1787</v>
+        <v>2023</v>
       </c>
       <c r="C70" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t>Soraya</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>Soraya-Y</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2655,62 +2659,58 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>1778</v>
+        <v>2018</v>
       </c>
       <c r="C71" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E71" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>HamzaG</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>Fa_One</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>1745</v>
+        <v>2005</v>
       </c>
       <c r="C72" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E72" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2719,30 +2719,30 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>1736</v>
+        <v>1999</v>
       </c>
       <c r="C73" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E73" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>romain</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>RomainLect</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2751,30 +2751,30 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>1727</v>
+        <v>1978</v>
       </c>
       <c r="C74" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D74" t="n">
         <v>5</v>
       </c>
       <c r="E74" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2783,30 +2783,30 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>1724</v>
+        <v>1966</v>
       </c>
       <c r="C75" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D75" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E75" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t>Juliie</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Seesee</t>
+          <t>Pipou931</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>1705</v>
+        <v>1965</v>
       </c>
       <c r="C76" t="n">
         <v>29</v>
@@ -2824,21 +2824,21 @@
         <v>4</v>
       </c>
       <c r="E76" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Erwan</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>WIL1610</t>
+          <t>Erwan#4G91X</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2847,30 +2847,30 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>1702</v>
+        <v>1951</v>
       </c>
       <c r="C77" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E77" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Soraya</t>
+          <t>Lison</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Soraya-Y</t>
+          <t>Lyzone</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2879,30 +2879,30 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>1692</v>
+        <v>1940</v>
       </c>
       <c r="C78" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D78" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E78" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Damien</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>PANENKANY</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2911,30 +2911,30 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>1685</v>
+        <v>1898</v>
       </c>
       <c r="C79" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E79" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Maruyama</t>
+          <t>dian-bgt</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2943,30 +2943,30 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>1679</v>
+        <v>1890</v>
       </c>
       <c r="C80" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D80" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E80" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Brieuc</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>Yebri</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2975,30 +2975,30 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>1665</v>
+        <v>1873</v>
       </c>
       <c r="C81" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D81" t="n">
         <v>4</v>
       </c>
       <c r="E81" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>Cindie</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
+          <t>Cindie_JJA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3007,25 +3007,25 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>1663</v>
+        <v>1869</v>
       </c>
       <c r="C82" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E82" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lison</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lyzone</t>
+          <t>Timy</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3039,30 +3039,30 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>1646</v>
+        <v>1853</v>
       </c>
       <c r="C83" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D83" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E83" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Selver</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>K_Marp</t>
+          <t>Seesee</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3071,30 +3071,30 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>1645</v>
+        <v>1841</v>
       </c>
       <c r="C84" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D84" t="n">
         <v>4</v>
       </c>
       <c r="E84" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Marilena</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fuzo697</t>
+          <t>GOAT#UE2WM8M9</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3103,30 +3103,30 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>1641</v>
+        <v>1833</v>
       </c>
       <c r="C85" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D85" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E85" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>MxKnight</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3135,30 +3135,30 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>1638</v>
+        <v>1831</v>
       </c>
       <c r="C86" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D86" t="n">
         <v>4</v>
       </c>
       <c r="E86" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>C4M</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3167,25 +3167,25 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>1623</v>
+        <v>1800</v>
       </c>
       <c r="C87" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D87" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E87" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ibra</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>PacoSarra</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3199,30 +3199,30 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>1616</v>
+        <v>1795</v>
       </c>
       <c r="C88" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E88" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cindie</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cindie_JJA</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3231,30 +3231,30 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>1612</v>
+        <v>1791</v>
       </c>
       <c r="C89" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D89" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E89" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Timy</t>
+          <t>Maruyama</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3263,30 +3263,30 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>1611</v>
+        <v>1769</v>
       </c>
       <c r="C90" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E90" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Jérémy</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>JeremFZ</t>
+          <t>Emma_Noel</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3295,30 +3295,30 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>1595</v>
+        <v>1765</v>
       </c>
       <c r="C91" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D91" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E91" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Juliie</t>
+          <t>Damien</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pipou931</t>
+          <t>PANENKANY</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3327,30 +3327,30 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>1582</v>
+        <v>1752</v>
       </c>
       <c r="C92" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D92" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E92" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Ibra</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>PacoSarra</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3359,30 +3359,30 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>1555</v>
+        <v>1745</v>
       </c>
       <c r="C93" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D93" t="n">
         <v>5</v>
       </c>
       <c r="E93" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Laetitia</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>Laetice2020</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3391,30 +3391,30 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>1540</v>
+        <v>1721</v>
       </c>
       <c r="C94" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D94" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E94" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3423,30 +3423,30 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>1537</v>
+        <v>1712</v>
       </c>
       <c r="C95" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D95" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E95" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>C4M</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3455,30 +3455,30 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>1508</v>
+        <v>1698</v>
       </c>
       <c r="C96" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D96" t="n">
         <v>4</v>
       </c>
       <c r="E96" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Laetitia</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Laetice2020</t>
+          <t>Fuzo697</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3487,30 +3487,30 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>1486</v>
+        <v>1669</v>
       </c>
       <c r="C97" t="n">
         <v>27</v>
       </c>
       <c r="D97" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E97" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Emma_Noel</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3519,58 +3519,62 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>1473</v>
+        <v>1640</v>
       </c>
       <c r="C98" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D98" t="n">
         <v>2</v>
       </c>
       <c r="E98" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>ousmane</t>
+          <t>lea</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Taylor2901</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>RBTL</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>1472</v>
+        <v>1611</v>
       </c>
       <c r="C99" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D99" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E99" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Jérémy</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>MxKnight</t>
+          <t>JeremFZ</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3579,30 +3583,30 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>1472</v>
+        <v>1611</v>
       </c>
       <c r="C100" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E100" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>JEVAISGAGNER10</t>
+          <t>Camss</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3611,30 +3615,30 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>1458</v>
+        <v>1601</v>
       </c>
       <c r="C101" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D101" t="n">
         <v>5</v>
       </c>
       <c r="E101" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>GLR_PRIME</t>
+          <t>JEVAISGAGNER10</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3643,90 +3647,90 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>1439</v>
+        <v>1582</v>
       </c>
       <c r="C102" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E102" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>lea</t>
+          <t>ousmane</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>RBTL</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>1404</v>
+        <v>1507</v>
       </c>
       <c r="C103" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Killian</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>goat#AD6GS</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+          <t>KIKS999</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>1316</v>
+        <v>1458</v>
       </c>
       <c r="C104" t="n">
         <v>23</v>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E104" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Léa</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>LeaBrd</t>
+          <t>GLR_PRIME</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3735,16 +3739,16 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>1296</v>
+        <v>1405</v>
       </c>
       <c r="C105" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D105" t="n">
         <v>3</v>
       </c>
       <c r="E105" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -3767,62 +3771,58 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>1270</v>
+        <v>1404</v>
       </c>
       <c r="C106" t="n">
         <v>22</v>
       </c>
       <c r="D106" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Camss</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>1237</v>
+        <v>1369</v>
       </c>
       <c r="C107" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E107" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>Léa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Valentine___</t>
+          <t>LeaBrd</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3831,25 +3831,25 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>1184</v>
+        <v>1310</v>
       </c>
       <c r="C108" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D108" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E108" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Killian</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>KIKS999</t>
+          <t>Valentine___</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -3872,7 +3872,7 @@
         <v>2</v>
       </c>
       <c r="E109" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2940</v>
+        <v>3242</v>
       </c>
       <c r="C2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,30 +495,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>2892</v>
+        <v>3209</v>
       </c>
       <c r="C3" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -527,25 +527,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>2789</v>
+        <v>3106</v>
       </c>
       <c r="C4" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>2772</v>
+        <v>3103</v>
       </c>
       <c r="C5" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>2761</v>
+        <v>3029</v>
       </c>
       <c r="C6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>2664</v>
+        <v>3000</v>
       </c>
       <c r="C7" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -655,25 +655,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>2608</v>
+        <v>2914</v>
       </c>
       <c r="C8" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>2588</v>
+        <v>2902</v>
       </c>
       <c r="C9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>2581</v>
+        <v>2875</v>
       </c>
       <c r="C10" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>2581</v>
+        <v>2864</v>
       </c>
       <c r="C11" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -783,30 +783,30 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>2580</v>
+        <v>2853</v>
       </c>
       <c r="C12" t="n">
         <v>40</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -815,30 +815,30 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>2577</v>
+        <v>2851</v>
       </c>
       <c r="C13" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>SabC1</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -847,25 +847,25 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>2531</v>
+        <v>2819</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -879,25 +879,25 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>2520</v>
+        <v>2799</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -911,25 +911,25 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>2517</v>
+        <v>2797</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SabC1</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -943,25 +943,25 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>2499</v>
+        <v>2792</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -975,30 +975,30 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>2460</v>
+        <v>2783</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Marion1822</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1007,30 +1007,30 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>2456</v>
+        <v>2783</v>
       </c>
       <c r="C19" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Panaf</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>Panaff</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1039,30 +1039,30 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>2449</v>
+        <v>2777</v>
       </c>
       <c r="C20" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Panaf</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Panaff</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1071,25 +1071,25 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>2447</v>
+        <v>2757</v>
       </c>
       <c r="C21" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1103,30 +1103,30 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>2443</v>
+        <v>2754</v>
       </c>
       <c r="C22" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D22" t="n">
         <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1135,30 +1135,30 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>2423</v>
+        <v>2737</v>
       </c>
       <c r="C23" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1167,25 +1167,25 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>2415</v>
+        <v>2734</v>
       </c>
       <c r="C24" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E24" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1199,25 +1199,25 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>2405</v>
+        <v>2731</v>
       </c>
       <c r="C25" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D25" t="n">
         <v>7</v>
       </c>
       <c r="E25" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1231,30 +1231,30 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>2401</v>
+        <v>2708</v>
       </c>
       <c r="C26" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D26" t="n">
         <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1263,25 +1263,25 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>2379</v>
+        <v>2699</v>
       </c>
       <c r="C27" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Marie__92</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1295,30 +1295,30 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>2376</v>
+        <v>2687</v>
       </c>
       <c r="C28" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D28" t="n">
         <v>7</v>
       </c>
       <c r="E28" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1327,30 +1327,30 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>2374</v>
+        <v>2681</v>
       </c>
       <c r="C29" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D29" t="n">
         <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1359,30 +1359,30 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>2365</v>
+        <v>2678</v>
       </c>
       <c r="C30" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E30" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1391,30 +1391,30 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>2364</v>
+        <v>2675</v>
       </c>
       <c r="C31" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Antonio Moctezuma</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>abihuts</t>
+          <t>EmyEnzo</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1423,30 +1423,30 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>2345</v>
+        <v>2658</v>
       </c>
       <c r="C32" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E32" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1455,30 +1455,30 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>2342</v>
+        <v>2652</v>
       </c>
       <c r="C33" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Loïc</t>
+          <t>Antonio Moctezuma</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Exia95</t>
+          <t>abihuts</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1487,30 +1487,30 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>2342</v>
+        <v>2646</v>
       </c>
       <c r="C34" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1519,25 +1519,25 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>2341</v>
+        <v>2635</v>
       </c>
       <c r="C35" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E35" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>EmyEnzo</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1551,30 +1551,30 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>2326</v>
+        <v>2590</v>
       </c>
       <c r="C36" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>Marie__92</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1583,30 +1583,30 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>2315</v>
+        <v>2585</v>
       </c>
       <c r="C37" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D37" t="n">
         <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>Romain_JO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1615,25 +1615,25 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>2314</v>
+        <v>2585</v>
       </c>
       <c r="C38" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D38" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E38" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Romain J</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1647,30 +1647,30 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>2312</v>
+        <v>2584</v>
       </c>
       <c r="C39" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D39" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>Devilrock95</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1679,58 +1679,62 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>2299</v>
+        <v>2562</v>
       </c>
       <c r="C40" t="n">
         <v>33</v>
       </c>
       <c r="D40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Mathilde</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>BrickXVI</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>MT35T</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>2294</v>
+        <v>2558</v>
       </c>
       <c r="C41" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D41" t="n">
         <v>5</v>
       </c>
       <c r="E41" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1739,30 +1743,30 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>2286</v>
+        <v>2557</v>
       </c>
       <c r="C42" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D42" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E42" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1771,30 +1775,30 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>2270</v>
+        <v>2553</v>
       </c>
       <c r="C43" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D43" t="n">
         <v>5</v>
       </c>
       <c r="E43" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Loïc</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Camillewbl</t>
+          <t>Exia95</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1803,94 +1807,86 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>2251</v>
+        <v>2521</v>
       </c>
       <c r="C44" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D44" t="n">
         <v>5</v>
       </c>
       <c r="E44" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mathilde</t>
+          <t>François</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>MT35T</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>compta</t>
-        </is>
-      </c>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>2198</v>
+        <v>2510</v>
       </c>
       <c r="C45" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D45" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E45" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liliane </t>
+          <t>Brick</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>LilianeB</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>2189</v>
+        <v>2507</v>
       </c>
       <c r="C46" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E46" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Devilrock95</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1899,58 +1895,62 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>2187</v>
+        <v>2492</v>
       </c>
       <c r="C47" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E47" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Francisco93</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Melissagzb</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>2187</v>
+        <v>2481</v>
       </c>
       <c r="C48" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="D48" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E48" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>Camillewbl</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1959,30 +1959,30 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>2176</v>
+        <v>2477</v>
       </c>
       <c r="C49" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D49" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E49" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1991,25 +1991,25 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>2173</v>
+        <v>2431</v>
       </c>
       <c r="C50" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E50" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2023,25 +2023,25 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>2165</v>
+        <v>2423</v>
       </c>
       <c r="C51" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="D51" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E51" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2055,30 +2055,30 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>2158</v>
+        <v>2412</v>
       </c>
       <c r="C52" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D52" t="n">
         <v>7</v>
       </c>
       <c r="E52" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2087,30 +2087,30 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>2158</v>
+        <v>2411</v>
       </c>
       <c r="C53" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E53" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Erwan</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>Erwan#4G91X</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2119,30 +2119,30 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>2143</v>
+        <v>2410</v>
       </c>
       <c r="C54" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D54" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E54" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2151,58 +2151,62 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>2143</v>
+        <v>2394</v>
       </c>
       <c r="C55" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D55" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E55" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>romain</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>RomainLect</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>2128</v>
+        <v>2384</v>
       </c>
       <c r="C56" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D56" t="n">
         <v>6</v>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>Kolas</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2211,30 +2215,30 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>2126</v>
+        <v>2378</v>
       </c>
       <c r="C57" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D57" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E57" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Elise</t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Elisewiss</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2243,25 +2247,25 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>2124</v>
+        <v>2369</v>
       </c>
       <c r="C58" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E58" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cécile</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ceciledp</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2275,30 +2279,30 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>2120</v>
+        <v>2362</v>
       </c>
       <c r="C59" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Priscilla</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Priscilla#4LCAF</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2307,25 +2311,25 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>2089</v>
+        <v>2360</v>
       </c>
       <c r="C60" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E60" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>William</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>WIL1610</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2339,62 +2343,58 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>2073</v>
+        <v>2354</v>
       </c>
       <c r="C61" t="n">
         <v>33</v>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E61" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>2067</v>
+        <v>2352</v>
       </c>
       <c r="C62" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D62" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E62" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t xml:space="preserve">Liliane </t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>LilianeB</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2403,25 +2403,25 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>2062</v>
+        <v>2339</v>
       </c>
       <c r="C63" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D63" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E63" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>romain</t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>RomainLect</t>
+          <t>Teddbear</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2435,30 +2435,30 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>2050</v>
+        <v>2335</v>
       </c>
       <c r="C64" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D64" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Cécile</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Kolas</t>
+          <t>Ceciledp</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2467,25 +2467,25 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>2049</v>
+        <v>2332</v>
       </c>
       <c r="C65" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D65" t="n">
         <v>5</v>
       </c>
       <c r="E65" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>K_Marp</t>
+          <t>AudreyB225</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2499,62 +2499,58 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>2044</v>
+        <v>2320</v>
       </c>
       <c r="C66" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D66" t="n">
         <v>6</v>
       </c>
       <c r="E66" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Reste du monde</t>
-        </is>
-      </c>
+          <t>Fa_One</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>2044</v>
+        <v>2309</v>
       </c>
       <c r="C67" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E67" t="n">
         <v>60</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Marilena</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>AudreyB225</t>
+          <t>GOAT#UE2WM8M9</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2563,30 +2559,30 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>2028</v>
+        <v>2304</v>
       </c>
       <c r="C68" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E68" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2595,30 +2591,30 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>2026</v>
+        <v>2285</v>
       </c>
       <c r="C69" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Lison</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>WIL1610</t>
+          <t>Lyzone</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2627,30 +2623,30 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>2023</v>
+        <v>2284</v>
       </c>
       <c r="C70" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E70" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Soraya</t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Soraya-Y</t>
+          <t>chaychaychay</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2655,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>2018</v>
+        <v>2266</v>
       </c>
       <c r="C71" t="n">
         <v>34</v>
@@ -2668,49 +2664,53 @@
         <v>6</v>
       </c>
       <c r="E71" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fa_One</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>DJOSWA</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>2005</v>
+        <v>2263</v>
       </c>
       <c r="C72" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D72" t="n">
         <v>5</v>
       </c>
       <c r="E72" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>Priscilla</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>Priscilla#4LCAF</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2719,30 +2719,30 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>1999</v>
+        <v>2260</v>
       </c>
       <c r="C73" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E73" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>K_Marp</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2751,30 +2751,30 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>1978</v>
+        <v>2255</v>
       </c>
       <c r="C74" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E74" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>MatuRenard</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2783,30 +2783,30 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>1966</v>
+        <v>2248</v>
       </c>
       <c r="C75" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E75" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Juliie</t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pipou931</t>
+          <t>Elisewiss</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2815,30 +2815,30 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>1965</v>
+        <v>2247</v>
       </c>
       <c r="C76" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D76" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E76" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Erwan</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Erwan#4G91X</t>
+          <t>MxKnight</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2847,30 +2847,30 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>1951</v>
+        <v>2233</v>
       </c>
       <c r="C77" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E77" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lison</t>
+          <t>Damien</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lyzone</t>
+          <t>PANENKANY</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2879,30 +2879,30 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>1940</v>
+        <v>2200</v>
       </c>
       <c r="C78" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E78" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Juliie</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>Pipou931</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2911,30 +2911,30 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>1898</v>
+        <v>2190</v>
       </c>
       <c r="C79" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E79" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
+          <t>YassineZ95</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2943,25 +2943,25 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>1890</v>
+        <v>2179</v>
       </c>
       <c r="C80" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D80" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E80" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Brieuc</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Yebri</t>
+          <t>dian-bgt</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -2975,30 +2975,30 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>1873</v>
+        <v>2176</v>
       </c>
       <c r="C81" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E81" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cindie</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cindie_JJA</t>
+          <t>Timy</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3007,30 +3007,30 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>1869</v>
+        <v>2136</v>
       </c>
       <c r="C82" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D82" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E82" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Timy</t>
+          <t>Maruyama</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3039,16 +3039,16 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>1853</v>
+        <v>2134</v>
       </c>
       <c r="C83" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D83" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E83" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3071,25 +3071,25 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>1841</v>
+        <v>2123</v>
       </c>
       <c r="C84" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D84" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E84" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Marilena</t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>GOAT#UE2WM8M9</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3103,7 +3103,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>1833</v>
+        <v>2122</v>
       </c>
       <c r="C85" t="n">
         <v>30</v>
@@ -3112,21 +3112,21 @@
         <v>6</v>
       </c>
       <c r="E85" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>MxKnight</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3135,62 +3135,58 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>1831</v>
+        <v>2080</v>
       </c>
       <c r="C86" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D86" t="n">
         <v>4</v>
       </c>
       <c r="E86" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>ousmane</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>C4M</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>1800</v>
+        <v>2061</v>
       </c>
       <c r="C87" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D87" t="n">
         <v>4</v>
       </c>
       <c r="E87" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3199,30 +3195,30 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>1795</v>
+        <v>2055</v>
       </c>
       <c r="C88" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Soraya</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>Soraya-Y</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3231,30 +3227,30 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>1791</v>
+        <v>2052</v>
       </c>
       <c r="C89" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D89" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E89" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Cindie</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Maruyama</t>
+          <t>Cindie_JJA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3263,30 +3259,30 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>1769</v>
+        <v>2042</v>
       </c>
       <c r="C90" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D90" t="n">
         <v>4</v>
       </c>
       <c r="E90" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Emma_Noel</t>
+          <t>C4M</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3295,25 +3291,25 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>1765</v>
+        <v>2032</v>
       </c>
       <c r="C91" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D91" t="n">
         <v>4</v>
       </c>
       <c r="E91" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Damien</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>PANENKANY</t>
+          <t>Fuzo697</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3327,30 +3323,30 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>1752</v>
+        <v>2012</v>
       </c>
       <c r="C92" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D92" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E92" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ibra</t>
+          <t>Brieuc</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>PacoSarra</t>
+          <t>Yebri</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3359,30 +3355,30 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>1745</v>
+        <v>2011</v>
       </c>
       <c r="C93" t="n">
         <v>29</v>
       </c>
       <c r="D93" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E93" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Laetitia</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Laetice2020</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3391,30 +3387,30 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>1721</v>
+        <v>1963</v>
       </c>
       <c r="C94" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D94" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>Ibra</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
+          <t>PacoSarra</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3423,30 +3419,30 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>1712</v>
+        <v>1956</v>
       </c>
       <c r="C95" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D95" t="n">
         <v>5</v>
       </c>
       <c r="E95" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Laetitia</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>Laetice2020</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3455,30 +3451,30 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>1698</v>
+        <v>1948</v>
       </c>
       <c r="C96" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D96" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E96" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fuzo697</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3487,30 +3483,30 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>1669</v>
+        <v>1900</v>
       </c>
       <c r="C97" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D97" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E97" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3519,30 +3515,30 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>1640</v>
+        <v>1892</v>
       </c>
       <c r="C98" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D98" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E98" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>lea</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>RBTL</t>
+          <t>Camss</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3551,30 +3547,30 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>1611</v>
+        <v>1855</v>
       </c>
       <c r="C99" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E99" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Jérémy</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>JeremFZ</t>
+          <t>Emma_Noel</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3583,30 +3579,30 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>1611</v>
+        <v>1812</v>
       </c>
       <c r="C100" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D100" t="n">
         <v>5</v>
       </c>
       <c r="E100" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Camss</t>
+          <t>JEVAISGAGNER10</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3615,30 +3611,30 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>1601</v>
+        <v>1808</v>
       </c>
       <c r="C101" t="n">
         <v>27</v>
       </c>
       <c r="D101" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E101" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>JEVAISGAGNER10</t>
+          <t>Valentine___</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3647,58 +3643,62 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>1582</v>
+        <v>1796</v>
       </c>
       <c r="C102" t="n">
         <v>29</v>
       </c>
       <c r="D102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E102" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>ousmane</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Taylor2901</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>Sab_M45</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>1507</v>
+        <v>1733</v>
       </c>
       <c r="C103" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E103" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Killian</t>
+          <t>Jérémy</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>KIKS999</t>
+          <t>JeremFZ</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3707,30 +3707,30 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>1458</v>
+        <v>1708</v>
       </c>
       <c r="C104" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D104" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E104" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>lea</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>GLR_PRIME</t>
+          <t>RBTL</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3739,25 +3739,25 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>1405</v>
+        <v>1707</v>
       </c>
       <c r="C105" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D105" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E105" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Sab_M45</t>
+          <t>GLR_PRIME</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -3771,44 +3771,48 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>1404</v>
+        <v>1661</v>
       </c>
       <c r="C106" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E106" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Killian</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>goat#AD6GS</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr"/>
+          <t>KIKS999</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>1369</v>
+        <v>1580</v>
       </c>
       <c r="C107" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D107" t="n">
         <v>2</v>
       </c>
       <c r="E107" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -3831,32 +3835,28 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>1310</v>
+        <v>1404</v>
       </c>
       <c r="C108" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D108" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Valentine___</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>goat#AD6GS</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">

--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3242</v>
+        <v>3624</v>
       </c>
       <c r="C2" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>3209</v>
+        <v>3413</v>
       </c>
       <c r="C3" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>3106</v>
+        <v>3357</v>
       </c>
       <c r="C4" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>3103</v>
+        <v>3317</v>
       </c>
       <c r="C5" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>3029</v>
+        <v>3290</v>
       </c>
       <c r="C6" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>SabC1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -623,25 +623,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>3000</v>
+        <v>3263</v>
       </c>
       <c r="C7" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>2914</v>
+        <v>3234</v>
       </c>
       <c r="C8" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>2902</v>
+        <v>3225</v>
       </c>
       <c r="C9" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>2875</v>
+        <v>3215</v>
       </c>
       <c r="C10" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>2864</v>
+        <v>3201</v>
       </c>
       <c r="C11" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -783,25 +783,25 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>2853</v>
+        <v>3171</v>
       </c>
       <c r="C12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -815,30 +815,30 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>2851</v>
+        <v>3152</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SabC1</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -847,25 +847,25 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>2819</v>
+        <v>3134</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -879,30 +879,30 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>2799</v>
+        <v>3094</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -911,25 +911,25 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>2797</v>
+        <v>3079</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -943,25 +943,25 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>2792</v>
+        <v>3069</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Panaf</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>Panaff</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -975,30 +975,30 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>2783</v>
+        <v>3061</v>
       </c>
       <c r="C18" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Antonio Moctezuma</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>abihuts</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1007,30 +1007,30 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>2783</v>
+        <v>3048</v>
       </c>
       <c r="C19" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Panaf</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Panaff</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1039,30 +1039,30 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>2777</v>
+        <v>3025</v>
       </c>
       <c r="C20" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1071,30 +1071,30 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>2757</v>
+        <v>3021</v>
       </c>
       <c r="C21" t="n">
         <v>41</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1103,30 +1103,30 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>2754</v>
+        <v>3012</v>
       </c>
       <c r="C22" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1135,30 +1135,30 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>2737</v>
+        <v>2997</v>
       </c>
       <c r="C23" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Marion1822</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1167,25 +1167,25 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>2734</v>
+        <v>2987</v>
       </c>
       <c r="C24" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>David</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1199,30 +1199,30 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>2731</v>
+        <v>2971</v>
       </c>
       <c r="C25" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1231,25 +1231,25 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>2708</v>
+        <v>2961</v>
       </c>
       <c r="C26" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E26" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1263,30 +1263,30 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>2699</v>
+        <v>2942</v>
       </c>
       <c r="C27" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>Romain_JO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1295,30 +1295,30 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>2687</v>
+        <v>2940</v>
       </c>
       <c r="C28" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1327,30 +1327,30 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>2681</v>
+        <v>2929</v>
       </c>
       <c r="C29" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1359,16 +1359,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>2678</v>
+        <v>2912</v>
       </c>
       <c r="C30" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1391,30 +1391,30 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>2675</v>
+        <v>2911</v>
       </c>
       <c r="C31" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E31" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>EmyEnzo</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1423,30 +1423,30 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>2658</v>
+        <v>2905</v>
       </c>
       <c r="C32" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D32" t="n">
         <v>6</v>
       </c>
       <c r="E32" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
+          <t>EmyEnzo</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1455,30 +1455,30 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>2652</v>
+        <v>2894</v>
       </c>
       <c r="C33" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Antonio Moctezuma</t>
+          <t>Mathilde</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>abihuts</t>
+          <t>MT35T</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1487,25 +1487,25 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>2646</v>
+        <v>2885</v>
       </c>
       <c r="C34" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D34" t="n">
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1519,30 +1519,30 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>2635</v>
+        <v>2880</v>
       </c>
       <c r="C35" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E35" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1551,30 +1551,30 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>2590</v>
+        <v>2871</v>
       </c>
       <c r="C36" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Marie__92</t>
+          <t>Devilrock95</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1583,30 +1583,30 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>2585</v>
+        <v>2869</v>
       </c>
       <c r="C37" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E37" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Romain J</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1615,25 +1615,25 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>2585</v>
+        <v>2844</v>
       </c>
       <c r="C38" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E38" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1647,62 +1647,58 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>2584</v>
+        <v>2843</v>
       </c>
       <c r="C39" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E39" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Brick</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Devilrock95</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>2562</v>
+        <v>2826</v>
       </c>
       <c r="C40" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D40" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E40" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mathilde</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>MT35T</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1711,25 +1707,25 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>2558</v>
+        <v>2814</v>
       </c>
       <c r="C41" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D41" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E41" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1743,25 +1739,25 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>2557</v>
+        <v>2814</v>
       </c>
       <c r="C42" t="n">
         <v>38</v>
       </c>
       <c r="D42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E42" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1775,30 +1771,30 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>2553</v>
+        <v>2799</v>
       </c>
       <c r="C43" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E43" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Loïc</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Exia95</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1807,86 +1803,94 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>2521</v>
+        <v>2788</v>
       </c>
       <c r="C44" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E44" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Francisco93</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Camillewbl</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>2510</v>
+        <v>2784</v>
       </c>
       <c r="C45" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E45" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>BrickXVI</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>Rosa_1009</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>2507</v>
+        <v>2774</v>
       </c>
       <c r="C46" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D46" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>Marie__92</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1895,62 +1899,58 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>2492</v>
+        <v>2750</v>
       </c>
       <c r="C47" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D47" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E47" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>François</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>2481</v>
+        <v>2732</v>
       </c>
       <c r="C48" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E48" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Camillewbl</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1959,62 +1959,58 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>2477</v>
+        <v>2729</v>
       </c>
       <c r="C49" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D49" t="n">
         <v>7</v>
       </c>
       <c r="E49" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Fa_One</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>2431</v>
+        <v>2728</v>
       </c>
       <c r="C50" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E50" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Marilena</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>GOAT#UE2WM8M9</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2023,30 +2019,30 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>2423</v>
+        <v>2698</v>
       </c>
       <c r="C51" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D51" t="n">
         <v>5</v>
       </c>
       <c r="E51" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>Erwan</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>Erwan#4G91X</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2055,30 +2051,30 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>2412</v>
+        <v>2694</v>
       </c>
       <c r="C52" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E52" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t>Loïc</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>Exia95</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2087,30 +2083,30 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>2411</v>
+        <v>2679</v>
       </c>
       <c r="C53" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E53" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Erwan</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Erwan#4G91X</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2119,30 +2115,30 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>2410</v>
+        <v>2676</v>
       </c>
       <c r="C54" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="D54" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E54" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>Melissagzb</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2151,30 +2147,30 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>2394</v>
+        <v>2641</v>
       </c>
       <c r="C55" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D55" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E55" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>romain</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>RomainLect</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2183,30 +2179,30 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>2384</v>
+        <v>2620</v>
       </c>
       <c r="C56" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E56" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>William</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Kolas</t>
+          <t>WIL1610</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2215,62 +2211,58 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>2378</v>
+        <v>2608</v>
       </c>
       <c r="C57" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D57" t="n">
         <v>9</v>
       </c>
       <c r="E57" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chadia__</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>2369</v>
+        <v>2608</v>
       </c>
       <c r="C58" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D58" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E58" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2279,25 +2271,25 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>2362</v>
+        <v>2607</v>
       </c>
       <c r="C59" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E59" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2311,25 +2303,25 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>2360</v>
+        <v>2580</v>
       </c>
       <c r="C60" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E60" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>WIL1610</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2343,58 +2335,62 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>2354</v>
+        <v>2562</v>
       </c>
       <c r="C61" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D61" t="n">
         <v>7</v>
       </c>
       <c r="E61" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>MatuRenard</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>2352</v>
+        <v>2546</v>
       </c>
       <c r="C62" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D62" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E62" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liliane </t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>LilianeB</t>
+          <t>K_Marp</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2403,30 +2399,30 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>2339</v>
+        <v>2545</v>
       </c>
       <c r="C63" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D63" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t>Lison</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>Lyzone</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2435,30 +2431,30 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>2335</v>
+        <v>2545</v>
       </c>
       <c r="C64" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E64" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cécile</t>
+          <t>romain</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ceciledp</t>
+          <t>RomainLect</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2467,30 +2463,30 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>2332</v>
+        <v>2541</v>
       </c>
       <c r="C65" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E65" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>AudreyB225</t>
+          <t>Kolas</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2499,58 +2495,62 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>2320</v>
+        <v>2538</v>
       </c>
       <c r="C66" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D66" t="n">
         <v>6</v>
       </c>
       <c r="E66" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fa_One</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>chaychaychay</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>2309</v>
+        <v>2536</v>
       </c>
       <c r="C67" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D67" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E67" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Marilena</t>
+          <t xml:space="preserve">Liliane </t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>GOAT#UE2WM8M9</t>
+          <t>LilianeB</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2559,25 +2559,25 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>2304</v>
+        <v>2505</v>
       </c>
       <c r="C68" t="n">
         <v>35</v>
       </c>
       <c r="D68" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E68" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -2591,30 +2591,30 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>2285</v>
+        <v>2497</v>
       </c>
       <c r="C69" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E69" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lison</t>
+          <t>Priscilla</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lyzone</t>
+          <t>Priscilla#4LCAF</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2623,30 +2623,30 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>2284</v>
+        <v>2496</v>
       </c>
       <c r="C70" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D70" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E70" t="n">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2655,30 +2655,30 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>2266</v>
+        <v>2496</v>
       </c>
       <c r="C71" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D71" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E71" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>Teddbear</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2687,30 +2687,30 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>2263</v>
+        <v>2489</v>
       </c>
       <c r="C72" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D72" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Priscilla</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Priscilla#4LCAF</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2719,30 +2719,30 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>2260</v>
+        <v>2486</v>
       </c>
       <c r="C73" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D73" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Cécile</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>K_Marp</t>
+          <t>Ceciledp</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2751,30 +2751,30 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>2255</v>
+        <v>2471</v>
       </c>
       <c r="C74" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D74" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E74" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
+          <t>MxKnight</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2783,30 +2783,30 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>2248</v>
+        <v>2469</v>
       </c>
       <c r="C75" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D75" t="n">
         <v>4</v>
       </c>
       <c r="E75" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Elise</t>
+          <t>Juliie</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Elisewiss</t>
+          <t>Pipou931</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2815,25 +2815,25 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>2247</v>
+        <v>2459</v>
       </c>
       <c r="C76" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D76" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E76" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>MxKnight</t>
+          <t>AudreyB225</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -2847,30 +2847,30 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>2233</v>
+        <v>2444</v>
       </c>
       <c r="C77" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D77" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E77" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Damien</t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>PANENKANY</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2879,25 +2879,25 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>2200</v>
+        <v>2406</v>
       </c>
       <c r="C78" t="n">
         <v>33</v>
       </c>
       <c r="D78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E78" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Juliie</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pipou931</t>
+          <t>Timy</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -2911,30 +2911,30 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>2190</v>
+        <v>2393</v>
       </c>
       <c r="C79" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D79" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E79" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2943,30 +2943,30 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>2179</v>
+        <v>2387</v>
       </c>
       <c r="C80" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D80" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E80" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Soraya</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
+          <t>Soraya-Y</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2975,25 +2975,25 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>2176</v>
+        <v>2374</v>
       </c>
       <c r="C81" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D81" t="n">
         <v>5</v>
       </c>
       <c r="E81" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Brieuc</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Timy</t>
+          <t>Yebri</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3007,25 +3007,25 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>2136</v>
+        <v>2351</v>
       </c>
       <c r="C82" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D82" t="n">
         <v>6</v>
       </c>
       <c r="E82" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Maruyama</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3039,30 +3039,30 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>2134</v>
+        <v>2343</v>
       </c>
       <c r="C83" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D83" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E83" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Seesee</t>
+          <t>Elisewiss</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3071,25 +3071,25 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>2123</v>
+        <v>2343</v>
       </c>
       <c r="C84" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D84" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E84" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3103,25 +3103,25 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>2122</v>
+        <v>2320</v>
       </c>
       <c r="C85" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D85" t="n">
         <v>6</v>
       </c>
       <c r="E85" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>Maruyama</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3135,90 +3135,90 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>2080</v>
+        <v>2318</v>
       </c>
       <c r="C86" t="n">
         <v>35</v>
       </c>
       <c r="D86" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E86" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>ousmane</t>
+          <t>Selver</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Taylor2901</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>Seesee</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>2061</v>
+        <v>2310</v>
       </c>
       <c r="C87" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D87" t="n">
         <v>4</v>
       </c>
       <c r="E87" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>ousmane</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>2055</v>
+        <v>2306</v>
       </c>
       <c r="C88" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D88" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E88" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Soraya</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Soraya-Y</t>
+          <t>dian-bgt</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3227,30 +3227,30 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>2052</v>
+        <v>2297</v>
       </c>
       <c r="C89" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D89" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E89" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cindie</t>
+          <t>Damien</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cindie_JJA</t>
+          <t>PANENKANY</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3259,30 +3259,30 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>2042</v>
+        <v>2285</v>
       </c>
       <c r="C90" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D90" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E90" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>C4M</t>
+          <t>YassineZ95</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3291,30 +3291,30 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>2032</v>
+        <v>2282</v>
       </c>
       <c r="C91" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D91" t="n">
         <v>4</v>
       </c>
       <c r="E91" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Cindie</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fuzo697</t>
+          <t>Cindie_JJA</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3323,30 +3323,30 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>2012</v>
+        <v>2261</v>
       </c>
       <c r="C92" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D92" t="n">
         <v>4</v>
       </c>
       <c r="E92" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Brieuc</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Yebri</t>
+          <t>Fuzo697</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3355,30 +3355,30 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>2011</v>
+        <v>2243</v>
       </c>
       <c r="C93" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E93" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Laetitia</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>Laetice2020</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3387,16 +3387,16 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>1963</v>
+        <v>2227</v>
       </c>
       <c r="C94" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D94" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E94" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -3419,25 +3419,25 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>1956</v>
+        <v>2199</v>
       </c>
       <c r="C95" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D95" t="n">
         <v>5</v>
       </c>
       <c r="E95" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Laetitia</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Laetice2020</t>
+          <t>C4M</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -3451,16 +3451,16 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>1948</v>
+        <v>2162</v>
       </c>
       <c r="C96" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D96" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E96" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3483,25 +3483,25 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>1900</v>
+        <v>2139</v>
       </c>
       <c r="C97" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D97" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E97" t="n">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
+          <t>Emma_Noel</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -3515,16 +3515,16 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>1892</v>
+        <v>2116</v>
       </c>
       <c r="C98" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D98" t="n">
         <v>6</v>
       </c>
       <c r="E98" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -3547,30 +3547,30 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>1855</v>
+        <v>2070</v>
       </c>
       <c r="C99" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D99" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E99" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Killian</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Emma_Noel</t>
+          <t>KIKS999</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3579,30 +3579,30 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>1812</v>
+        <v>2032</v>
       </c>
       <c r="C100" t="n">
         <v>31</v>
       </c>
       <c r="D100" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E100" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>JEVAISGAGNER10</t>
+          <t>Valentine___</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3611,30 +3611,30 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>1808</v>
+        <v>1978</v>
       </c>
       <c r="C101" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D101" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E101" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Valentine___</t>
+          <t>Sab_M45</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3643,30 +3643,30 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>1796</v>
+        <v>1939</v>
       </c>
       <c r="C102" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D102" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E102" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sab_M45</t>
+          <t>JEVAISGAGNER10</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3675,30 +3675,30 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>1733</v>
+        <v>1937</v>
       </c>
       <c r="C103" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E103" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Jérémy</t>
+          <t>Léa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>JeremFZ</t>
+          <t>LeaBrd</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3707,30 +3707,30 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>1708</v>
+        <v>1900</v>
       </c>
       <c r="C104" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E104" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>lea</t>
+          <t>Jérémy</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>RBTL</t>
+          <t>JeremFZ</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3739,30 +3739,30 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>1707</v>
+        <v>1900</v>
       </c>
       <c r="C105" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D105" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E105" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>GLR_PRIME</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3771,30 +3771,30 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>1661</v>
+        <v>1892</v>
       </c>
       <c r="C106" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D106" t="n">
         <v>2</v>
       </c>
       <c r="E106" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Killian</t>
+          <t>lea</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>KIKS999</t>
+          <t>RBTL</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3803,30 +3803,30 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>1580</v>
+        <v>1707</v>
       </c>
       <c r="C107" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D107" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E107" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Léa</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>LeaBrd</t>
+          <t>GLR_PRIME</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>

--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -472,7 +472,7 @@
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>3413</v>
+        <v>3477</v>
       </c>
       <c r="C3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>3357</v>
+        <v>3431</v>
       </c>
       <c r="C4" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>3317</v>
+        <v>3421</v>
       </c>
       <c r="C5" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -591,16 +591,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>3290</v>
+        <v>3354</v>
       </c>
       <c r="C6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -623,16 +623,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>3263</v>
+        <v>3327</v>
       </c>
       <c r="C7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -655,16 +655,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>3234</v>
+        <v>3298</v>
       </c>
       <c r="C8" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>3225</v>
+        <v>3266</v>
       </c>
       <c r="C9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>3215</v>
+        <v>3265</v>
       </c>
       <c r="C10" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3201</v>
+        <v>3235</v>
       </c>
       <c r="C11" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -783,30 +783,30 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>3171</v>
+        <v>3225</v>
       </c>
       <c r="C12" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -815,10 +815,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>3152</v>
+        <v>3215</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
         <v>8</v>
@@ -828,17 +828,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -847,30 +847,30 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>3134</v>
+        <v>3208</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -879,30 +879,30 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>3094</v>
+        <v>3198</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D15" t="n">
         <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -911,16 +911,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>3079</v>
+        <v>3193</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -943,16 +943,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>3069</v>
+        <v>3133</v>
       </c>
       <c r="C17" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D17" t="n">
         <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -975,16 +975,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>3061</v>
+        <v>3125</v>
       </c>
       <c r="C18" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D18" t="n">
         <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1007,16 +1007,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>3048</v>
+        <v>3112</v>
       </c>
       <c r="C19" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1039,30 +1039,30 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>3025</v>
+        <v>3085</v>
       </c>
       <c r="C20" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D20" t="n">
         <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1071,16 +1071,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>3021</v>
+        <v>3085</v>
       </c>
       <c r="C21" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1103,16 +1103,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>3012</v>
+        <v>3076</v>
       </c>
       <c r="C22" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D22" t="n">
         <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>2997</v>
+        <v>3075</v>
       </c>
       <c r="C23" t="n">
         <v>45</v>
@@ -1144,16 +1144,16 @@
         <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1167,30 +1167,30 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>2987</v>
+        <v>3061</v>
       </c>
       <c r="C24" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1199,30 +1199,30 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>2971</v>
+        <v>3051</v>
       </c>
       <c r="C25" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Marion1822</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1231,25 +1231,25 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>2961</v>
+        <v>3025</v>
       </c>
       <c r="C26" t="n">
         <v>44</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
         <v>72</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1263,16 +1263,16 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>2942</v>
+        <v>3006</v>
       </c>
       <c r="C27" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D27" t="n">
         <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1295,16 +1295,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>2940</v>
+        <v>3004</v>
       </c>
       <c r="C28" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D28" t="n">
         <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1327,16 +1327,16 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>2929</v>
+        <v>2993</v>
       </c>
       <c r="C29" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D29" t="n">
         <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1359,30 +1359,30 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>2912</v>
+        <v>2985</v>
       </c>
       <c r="C30" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E30" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>Devilrock95</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1391,25 +1391,25 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>2911</v>
+        <v>2976</v>
       </c>
       <c r="C31" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D31" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E31" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1423,30 +1423,30 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>2905</v>
+        <v>2975</v>
       </c>
       <c r="C32" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E32" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>EmyEnzo</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1455,30 +1455,30 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>2894</v>
+        <v>2969</v>
       </c>
       <c r="C33" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D33" t="n">
         <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mathilde</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MT35T</t>
+          <t>EmyEnzo</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1487,30 +1487,30 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>2885</v>
+        <v>2958</v>
       </c>
       <c r="C34" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D34" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E34" t="n">
         <v>72</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>Mathilde</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>MT35T</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1519,25 +1519,25 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>2880</v>
+        <v>2949</v>
       </c>
       <c r="C35" t="n">
         <v>44</v>
       </c>
       <c r="D35" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E35" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1551,30 +1551,30 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>2871</v>
+        <v>2944</v>
       </c>
       <c r="C36" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E36" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Devilrock95</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1583,30 +1583,30 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>2869</v>
+        <v>2940</v>
       </c>
       <c r="C37" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D37" t="n">
         <v>9</v>
       </c>
       <c r="E37" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1615,16 +1615,16 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>2844</v>
+        <v>2908</v>
       </c>
       <c r="C38" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D38" t="n">
         <v>7</v>
       </c>
       <c r="E38" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1647,16 +1647,16 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>2843</v>
+        <v>2907</v>
       </c>
       <c r="C39" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D39" t="n">
         <v>7</v>
       </c>
       <c r="E39" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1675,30 +1675,30 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>2826</v>
+        <v>2878</v>
       </c>
       <c r="C40" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D40" t="n">
         <v>8</v>
       </c>
       <c r="E40" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1707,25 +1707,25 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>2814</v>
+        <v>2869</v>
       </c>
       <c r="C41" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E41" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1739,25 +1739,25 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>2814</v>
+        <v>2863</v>
       </c>
       <c r="C42" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D42" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E42" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1771,30 +1771,30 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>2799</v>
+        <v>2848</v>
       </c>
       <c r="C43" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E43" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1803,25 +1803,25 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>2788</v>
+        <v>2838</v>
       </c>
       <c r="C44" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E44" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Camillewbl</t>
+          <t>Marie__92</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1835,30 +1835,30 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>2784</v>
+        <v>2814</v>
       </c>
       <c r="C45" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D45" t="n">
         <v>8</v>
       </c>
       <c r="E45" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1867,30 +1867,30 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>2774</v>
+        <v>2812</v>
       </c>
       <c r="C46" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E46" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Erwan</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Marie__92</t>
+          <t>Erwan#4G91X</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1899,118 +1899,122 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>2750</v>
+        <v>2796</v>
       </c>
       <c r="C47" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E47" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Francisco93</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>SamSamH8</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>2732</v>
+        <v>2793</v>
       </c>
       <c r="C48" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D48" t="n">
         <v>7</v>
       </c>
       <c r="E48" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Fa_One</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>2729</v>
+        <v>2788</v>
       </c>
       <c r="C49" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E49" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fa_One</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Camillewbl</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>2728</v>
+        <v>2758</v>
       </c>
       <c r="C50" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D50" t="n">
         <v>6</v>
       </c>
       <c r="E50" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Marilena</t>
+          <t>Loïc</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>GOAT#UE2WM8M9</t>
+          <t>Exia95</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2019,62 +2023,58 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>2698</v>
+        <v>2750</v>
       </c>
       <c r="C51" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D51" t="n">
         <v>5</v>
       </c>
       <c r="E51" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Erwan</t>
+          <t>François</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Erwan#4G91X</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>2694</v>
+        <v>2743</v>
       </c>
       <c r="C52" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D52" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E52" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Loïc</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Exia95</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2083,30 +2083,30 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>2679</v>
+        <v>2728</v>
       </c>
       <c r="C53" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D53" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E53" t="n">
         <v>67</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Marilena</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>GOAT#UE2WM8M9</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2115,30 +2115,30 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>2676</v>
+        <v>2722</v>
       </c>
       <c r="C54" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="D54" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E54" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2147,16 +2147,16 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>2641</v>
+        <v>2705</v>
       </c>
       <c r="C55" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D55" t="n">
         <v>7</v>
       </c>
       <c r="E55" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>2620</v>
+        <v>2684</v>
       </c>
       <c r="C56" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D56" t="n">
         <v>5</v>
       </c>
       <c r="E56" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2211,76 +2211,76 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>2608</v>
+        <v>2676</v>
       </c>
       <c r="C57" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D57" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E57" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Melissagzb</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>2608</v>
+        <v>2672</v>
       </c>
       <c r="C58" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E58" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Reste du monde</t>
-        </is>
-      </c>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>2607</v>
+        <v>2671</v>
       </c>
       <c r="C59" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D59" t="n">
         <v>9</v>
       </c>
       <c r="E59" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2303,30 +2303,30 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>2580</v>
+        <v>2659</v>
       </c>
       <c r="C60" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D60" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E60" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>Lison</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>Lyzone</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2335,25 +2335,25 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>2562</v>
+        <v>2659</v>
       </c>
       <c r="C61" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D61" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E61" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>romain</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
+          <t>RomainLect</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2367,30 +2367,30 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>2546</v>
+        <v>2644</v>
       </c>
       <c r="C62" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E62" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>K_Marp</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2399,30 +2399,30 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>2545</v>
+        <v>2626</v>
       </c>
       <c r="C63" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D63" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lison</t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lyzone</t>
+          <t>MatuRenard</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>2545</v>
+        <v>2610</v>
       </c>
       <c r="C64" t="n">
         <v>39</v>
@@ -2440,21 +2440,21 @@
         <v>5</v>
       </c>
       <c r="E64" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>romain</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>RomainLect</t>
+          <t>K_Marp</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2463,16 +2463,16 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>2541</v>
+        <v>2605</v>
       </c>
       <c r="C65" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D65" t="n">
         <v>7</v>
       </c>
       <c r="E65" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2495,30 +2495,30 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>2538</v>
+        <v>2600</v>
       </c>
       <c r="C66" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D66" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E66" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>Cécile</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>Ceciledp</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2527,16 +2527,16 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>2536</v>
+        <v>2600</v>
       </c>
       <c r="C67" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D67" t="n">
         <v>8</v>
       </c>
       <c r="E67" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2559,30 +2559,30 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>2505</v>
+        <v>2561</v>
       </c>
       <c r="C68" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D68" t="n">
         <v>7</v>
       </c>
       <c r="E68" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Priscilla</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>Priscilla#4LCAF</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2591,30 +2591,30 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>2497</v>
+        <v>2553</v>
       </c>
       <c r="C69" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D69" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Priscilla</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Priscilla#4LCAF</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2623,30 +2623,30 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>2496</v>
+        <v>2538</v>
       </c>
       <c r="C70" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D70" t="n">
         <v>6</v>
       </c>
       <c r="E70" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>chaychaychay</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2655,30 +2655,30 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>2496</v>
+        <v>2535</v>
       </c>
       <c r="C71" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D71" t="n">
         <v>7</v>
       </c>
       <c r="E71" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>MxKnight</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2687,25 +2687,25 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>2489</v>
+        <v>2533</v>
       </c>
       <c r="C72" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E72" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Juliie</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>Pipou931</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -2719,30 +2719,30 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>2486</v>
+        <v>2523</v>
       </c>
       <c r="C73" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E73" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Cécile</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ceciledp</t>
+          <t>AudreyB225</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2751,30 +2751,30 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>2471</v>
+        <v>2508</v>
       </c>
       <c r="C74" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D74" t="n">
         <v>7</v>
       </c>
       <c r="E74" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>MxKnight</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2783,30 +2783,30 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>2469</v>
+        <v>2505</v>
       </c>
       <c r="C75" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D75" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E75" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Juliie</t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pipou931</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2815,25 +2815,25 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>2459</v>
+        <v>2496</v>
       </c>
       <c r="C76" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E76" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>AudreyB225</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -2847,30 +2847,30 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>2444</v>
+        <v>2496</v>
       </c>
       <c r="C77" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D77" t="n">
         <v>7</v>
       </c>
       <c r="E77" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>Teddbear</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2879,16 +2879,16 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>2406</v>
+        <v>2470</v>
       </c>
       <c r="C78" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D78" t="n">
         <v>5</v>
       </c>
       <c r="E78" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -2911,30 +2911,30 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>2393</v>
+        <v>2457</v>
       </c>
       <c r="C79" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E79" t="n">
         <v>72</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2943,16 +2943,16 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>2387</v>
+        <v>2451</v>
       </c>
       <c r="C80" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D80" t="n">
         <v>3</v>
       </c>
       <c r="E80" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -2975,16 +2975,16 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>2374</v>
+        <v>2438</v>
       </c>
       <c r="C81" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D81" t="n">
         <v>5</v>
       </c>
       <c r="E81" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3007,25 +3007,25 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>2351</v>
+        <v>2432</v>
       </c>
       <c r="C82" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D82" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E82" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Selver</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>Seesee</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3039,16 +3039,16 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>2343</v>
+        <v>2407</v>
       </c>
       <c r="C83" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D83" t="n">
         <v>4</v>
       </c>
       <c r="E83" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3071,30 +3071,30 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>2343</v>
+        <v>2393</v>
       </c>
       <c r="C84" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D84" t="n">
         <v>4</v>
       </c>
       <c r="E84" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3103,16 +3103,16 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>2320</v>
+        <v>2384</v>
       </c>
       <c r="C85" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D85" t="n">
         <v>6</v>
       </c>
       <c r="E85" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3135,30 +3135,30 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>2318</v>
+        <v>2370</v>
       </c>
       <c r="C86" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D86" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E86" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Seesee</t>
+          <t>dian-bgt</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3167,58 +3167,62 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>2310</v>
+        <v>2351</v>
       </c>
       <c r="C87" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D87" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E87" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ousmane</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Taylor2901</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>HamzaG</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>2306</v>
+        <v>2346</v>
       </c>
       <c r="C88" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D88" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E88" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Cindie</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
+          <t>Cindie_JJA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3227,62 +3231,58 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>2297</v>
+        <v>2310</v>
       </c>
       <c r="C89" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D89" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E89" t="n">
         <v>72</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Damien</t>
+          <t>ousmane</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>PANENKANY</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>2285</v>
+        <v>2297</v>
       </c>
       <c r="C90" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D90" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E90" t="n">
         <v>72</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Damien</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>PANENKANY</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3291,30 +3291,30 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>2282</v>
+        <v>2285</v>
       </c>
       <c r="C91" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E91" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cindie</t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cindie_JJA</t>
+          <t>YassineZ95</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3332,7 @@
         <v>4</v>
       </c>
       <c r="E92" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -3387,30 +3387,30 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>2227</v>
+        <v>2230</v>
       </c>
       <c r="C94" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D94" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ibra</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>PacoSarra</t>
+          <t>Camss</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3419,30 +3419,30 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>2199</v>
+        <v>2227</v>
       </c>
       <c r="C95" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D95" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E95" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Ibra</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>C4M</t>
+          <t>PacoSarra</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3451,16 +3451,16 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>2162</v>
+        <v>2226</v>
       </c>
       <c r="C96" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D96" t="n">
         <v>8</v>
       </c>
       <c r="E96" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3483,16 +3483,16 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>2139</v>
+        <v>2203</v>
       </c>
       <c r="C97" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D97" t="n">
         <v>6</v>
       </c>
       <c r="E97" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -3515,16 +3515,16 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>2116</v>
+        <v>2199</v>
       </c>
       <c r="C98" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D98" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E98" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Camss</t>
+          <t>C4M</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -3579,30 +3579,30 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>2032</v>
+        <v>2053</v>
       </c>
       <c r="C100" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D100" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E100" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Valentine___</t>
+          <t>JEVAISGAGNER10</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3611,16 +3611,16 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>1978</v>
+        <v>2042</v>
       </c>
       <c r="C101" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D101" t="n">
         <v>4</v>
       </c>
       <c r="E101" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -3643,30 +3643,30 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>1939</v>
+        <v>2032</v>
       </c>
       <c r="C102" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D102" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E102" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>JEVAISGAGNER10</t>
+          <t>Valentine___</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>1937</v>
+        <v>2014</v>
       </c>
       <c r="C103" t="n">
         <v>33</v>
@@ -3684,21 +3684,21 @@
         <v>4</v>
       </c>
       <c r="E103" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Léa</t>
+          <t>Jérémy</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>LeaBrd</t>
+          <t>JeremFZ</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3707,30 +3707,30 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>1900</v>
+        <v>2001</v>
       </c>
       <c r="C104" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D104" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E104" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Jérémy</t>
+          <t>Léa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>JeremFZ</t>
+          <t>LeaBrd</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3739,25 +3739,25 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>1900</v>
+        <v>1956</v>
       </c>
       <c r="C105" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D105" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E105" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>lea</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
+          <t>RBTL</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -3771,25 +3771,25 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>1892</v>
+        <v>1900</v>
       </c>
       <c r="C106" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D106" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E106" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>lea</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>RBTL</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">

--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -463,30 +463,30 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3624</v>
+        <v>3676</v>
       </c>
       <c r="C2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -495,30 +495,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>3477</v>
+        <v>3624</v>
       </c>
       <c r="C3" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>3431</v>
+        <v>3553</v>
       </c>
       <c r="C4" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>SabC1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>3421</v>
+        <v>3496</v>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>3354</v>
+        <v>3486</v>
       </c>
       <c r="C6" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SabC1</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>3327</v>
+        <v>3470</v>
       </c>
       <c r="C7" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>3298</v>
+        <v>3454</v>
       </c>
       <c r="C8" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>3266</v>
+        <v>3441</v>
       </c>
       <c r="C9" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>3265</v>
+        <v>3434</v>
       </c>
       <c r="C10" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3235</v>
+        <v>3392</v>
       </c>
       <c r="C11" t="n">
         <v>46</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -783,30 +783,30 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>3225</v>
+        <v>3383</v>
       </c>
       <c r="C12" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -815,30 +815,30 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>3215</v>
+        <v>3350</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -847,25 +847,25 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>3208</v>
+        <v>3331</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -879,30 +879,30 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>3198</v>
+        <v>3293</v>
       </c>
       <c r="C15" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E15" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -911,25 +911,25 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>3193</v>
+        <v>3263</v>
       </c>
       <c r="C16" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -943,30 +943,30 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>3133</v>
+        <v>3260</v>
       </c>
       <c r="C17" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Panaf</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Panaff</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -975,25 +975,25 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>3125</v>
+        <v>3250</v>
       </c>
       <c r="C18" t="n">
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Antonio Moctezuma</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>abihuts</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1007,30 +1007,30 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>3112</v>
+        <v>3210</v>
       </c>
       <c r="C19" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1039,30 +1039,30 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>3085</v>
+        <v>3198</v>
       </c>
       <c r="C20" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>Panaf</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Marion1822</t>
+          <t>Panaff</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1071,30 +1071,30 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>3085</v>
+        <v>3197</v>
       </c>
       <c r="C21" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E21" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1103,30 +1103,30 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>3076</v>
+        <v>3190</v>
       </c>
       <c r="C22" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Antonio Moctezuma</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>abihuts</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1135,30 +1135,30 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>3075</v>
+        <v>3177</v>
       </c>
       <c r="C23" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D23" t="n">
         <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Mathilde</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>MT35T</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1167,30 +1167,30 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>3061</v>
+        <v>3174</v>
       </c>
       <c r="C24" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1199,30 +1199,30 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>3051</v>
+        <v>3170</v>
       </c>
       <c r="C25" t="n">
         <v>46</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1231,30 +1231,30 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>3025</v>
+        <v>3163</v>
       </c>
       <c r="C26" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D26" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E26" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1263,30 +1263,30 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>3006</v>
+        <v>3160</v>
       </c>
       <c r="C27" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E27" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Romain J</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1295,30 +1295,30 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>3004</v>
+        <v>3127</v>
       </c>
       <c r="C28" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E28" t="n">
         <v>73</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1327,25 +1327,25 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>2993</v>
+        <v>3103</v>
       </c>
       <c r="C29" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E29" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>EmyEnzo</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1359,30 +1359,30 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>2985</v>
+        <v>3090</v>
       </c>
       <c r="C30" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Devilrock95</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1391,30 +1391,30 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>2976</v>
+        <v>3085</v>
       </c>
       <c r="C31" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E31" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1423,30 +1423,30 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>2975</v>
+        <v>3071</v>
       </c>
       <c r="C32" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D32" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E32" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>Romain_JO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1455,30 +1455,30 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>2969</v>
+        <v>3063</v>
       </c>
       <c r="C33" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E33" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>EmyEnzo</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1487,30 +1487,30 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>2958</v>
+        <v>3062</v>
       </c>
       <c r="C34" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E34" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mathilde</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>MT35T</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1519,30 +1519,30 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>2949</v>
+        <v>3050</v>
       </c>
       <c r="C35" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D35" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E35" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>Devilrock95</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1551,30 +1551,30 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>2944</v>
+        <v>3037</v>
       </c>
       <c r="C36" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D36" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>Marie__92</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1583,30 +1583,30 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>2940</v>
+        <v>3004</v>
       </c>
       <c r="C37" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1615,30 +1615,30 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>2908</v>
+        <v>3003</v>
       </c>
       <c r="C38" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D38" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E38" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1647,16 +1647,16 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>2907</v>
+        <v>2992</v>
       </c>
       <c r="C39" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E39" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1675,25 +1675,25 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>2878</v>
+        <v>2976</v>
       </c>
       <c r="C40" t="n">
         <v>44</v>
       </c>
       <c r="D40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E40" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1707,30 +1707,30 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>2869</v>
+        <v>2973</v>
       </c>
       <c r="C41" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D41" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E41" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1739,57 +1739,53 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>2863</v>
+        <v>2969</v>
       </c>
       <c r="C42" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D42" t="n">
         <v>7</v>
       </c>
       <c r="E42" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>François</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>2848</v>
+        <v>2963</v>
       </c>
       <c r="C43" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D43" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E43" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1803,25 +1799,25 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>2838</v>
+        <v>2940</v>
       </c>
       <c r="C44" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E44" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Marie__92</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1835,30 +1831,30 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>2814</v>
+        <v>2933</v>
       </c>
       <c r="C45" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E45" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1867,30 +1863,30 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>2812</v>
+        <v>2930</v>
       </c>
       <c r="C46" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D46" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E46" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Erwan</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Erwan#4G91X</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1899,30 +1895,30 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>2796</v>
+        <v>2904</v>
       </c>
       <c r="C47" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D47" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E47" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1931,58 +1927,62 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>2793</v>
+        <v>2902</v>
       </c>
       <c r="C48" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E48" t="n">
         <v>73</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fa_One</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Camillewbl</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>2788</v>
+        <v>2897</v>
       </c>
       <c r="C49" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E49" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Erwan</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Camillewbl</t>
+          <t>Erwan#4G91X</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1991,16 +1991,16 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>2758</v>
+        <v>2823</v>
       </c>
       <c r="C50" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D50" t="n">
         <v>6</v>
       </c>
       <c r="E50" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2023,58 +2023,62 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>2750</v>
+        <v>2819</v>
       </c>
       <c r="C51" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D51" t="n">
         <v>5</v>
       </c>
       <c r="E51" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Lison</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Francisco93</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Lyzone</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>2743</v>
+        <v>2814</v>
       </c>
       <c r="C52" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E52" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2083,16 +2087,16 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>2728</v>
+        <v>2813</v>
       </c>
       <c r="C53" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E53" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2115,30 +2119,30 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>2722</v>
+        <v>2808</v>
       </c>
       <c r="C54" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="D54" t="n">
         <v>9</v>
       </c>
       <c r="E54" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2147,48 +2151,44 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>2705</v>
+        <v>2793</v>
       </c>
       <c r="C55" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D55" t="n">
         <v>7</v>
       </c>
       <c r="E55" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>Fa_One</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>2684</v>
+        <v>2769</v>
       </c>
       <c r="C56" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E56" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2211,30 +2211,30 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>2676</v>
+        <v>2756</v>
       </c>
       <c r="C57" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D57" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E57" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2243,58 +2243,62 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>2672</v>
+        <v>2752</v>
       </c>
       <c r="C58" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D58" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>JKInternational</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>2671</v>
+        <v>2744</v>
       </c>
       <c r="C59" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D59" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E59" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>romain</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>RomainLect</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2303,30 +2307,30 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>2659</v>
+        <v>2742</v>
       </c>
       <c r="C60" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E60" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lison</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lyzone</t>
+          <t>AudreyB225</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2335,30 +2339,30 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>2659</v>
+        <v>2741</v>
       </c>
       <c r="C61" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D61" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E61" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>romain</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>RomainLect</t>
+          <t>Melissagzb</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2367,25 +2371,25 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>2644</v>
+        <v>2722</v>
       </c>
       <c r="C62" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="D62" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E62" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2399,16 +2403,16 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>2626</v>
+        <v>2711</v>
       </c>
       <c r="C63" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E63" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -2431,30 +2435,30 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>2610</v>
+        <v>2690</v>
       </c>
       <c r="C64" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D64" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E64" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>K_Marp</t>
+          <t>Kolas</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2463,30 +2467,30 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>2605</v>
+        <v>2685</v>
       </c>
       <c r="C65" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D65" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E65" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t xml:space="preserve">Liliane </t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Kolas</t>
+          <t>LilianeB</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2495,30 +2499,30 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>2600</v>
+        <v>2675</v>
       </c>
       <c r="C66" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E66" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Cécile</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ceciledp</t>
+          <t>K_Marp</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2527,62 +2531,58 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>2600</v>
+        <v>2672</v>
       </c>
       <c r="C67" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D67" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E67" t="n">
         <v>73</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liliane </t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>LilianeB</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>2561</v>
+        <v>2665</v>
       </c>
       <c r="C68" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D68" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E68" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Priscilla</t>
+          <t>Cécile</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Priscilla#4LCAF</t>
+          <t>Ceciledp</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2591,30 +2591,30 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>2553</v>
+        <v>2644</v>
       </c>
       <c r="C69" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E69" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2623,25 +2623,25 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>2538</v>
+        <v>2626</v>
       </c>
       <c r="C70" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D70" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E70" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>Priscilla</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>Priscilla#4LCAF</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -2655,16 +2655,16 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>2535</v>
+        <v>2620</v>
       </c>
       <c r="C71" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D71" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E71" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2687,16 +2687,16 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>2533</v>
+        <v>2598</v>
       </c>
       <c r="C72" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D72" t="n">
         <v>4</v>
       </c>
       <c r="E72" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -2719,30 +2719,30 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>2523</v>
+        <v>2596</v>
       </c>
       <c r="C73" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E73" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>AudreyB225</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2751,25 +2751,25 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>2508</v>
+        <v>2571</v>
       </c>
       <c r="C74" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D74" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E74" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -2783,16 +2783,16 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>2505</v>
+        <v>2570</v>
       </c>
       <c r="C75" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D75" t="n">
         <v>7</v>
       </c>
       <c r="E75" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -2815,25 +2815,25 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>2496</v>
+        <v>2565</v>
       </c>
       <c r="C76" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D76" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Soraya</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>Soraya-Y</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -2847,30 +2847,30 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>2496</v>
+        <v>2561</v>
       </c>
       <c r="C77" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D77" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E77" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2879,30 +2879,30 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>2470</v>
+        <v>2561</v>
       </c>
       <c r="C78" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D78" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E78" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Timy</t>
+          <t>Teddbear</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2911,30 +2911,30 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>2457</v>
+        <v>2538</v>
       </c>
       <c r="C79" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E79" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>chaychaychay</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2943,30 +2943,30 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>2451</v>
+        <v>2508</v>
       </c>
       <c r="C80" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D80" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E80" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Soraya</t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Soraya-Y</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2975,30 +2975,30 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>2438</v>
+        <v>2497</v>
       </c>
       <c r="C81" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E81" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Brieuc</t>
+          <t>Selver</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Yebri</t>
+          <t>Seesee</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3007,30 +3007,30 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>2432</v>
+        <v>2478</v>
       </c>
       <c r="C82" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E82" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Seesee</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3039,16 +3039,16 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>2407</v>
+        <v>2472</v>
       </c>
       <c r="C83" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D83" t="n">
         <v>4</v>
       </c>
       <c r="E83" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3071,30 +3071,30 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>2393</v>
+        <v>2470</v>
       </c>
       <c r="C84" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E84" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>Timy</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3103,30 +3103,30 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>2384</v>
+        <v>2460</v>
       </c>
       <c r="C85" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D85" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E85" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Cindie</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Maruyama</t>
+          <t>Cindie_JJA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3135,30 +3135,30 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>2370</v>
+        <v>2449</v>
       </c>
       <c r="C86" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D86" t="n">
         <v>6</v>
       </c>
       <c r="E86" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
+          <t>Maruyama</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3167,25 +3167,25 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>2351</v>
+        <v>2445</v>
       </c>
       <c r="C87" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D87" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E87" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3199,30 +3199,30 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>2346</v>
+        <v>2438</v>
       </c>
       <c r="C88" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D88" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E88" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cindie</t>
+          <t>Brieuc</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cindie_JJA</t>
+          <t>Yebri</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3231,90 +3231,90 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>2310</v>
+        <v>2435</v>
       </c>
       <c r="C89" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D89" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E89" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ousmane</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Taylor2901</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>dian-bgt</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>2297</v>
+        <v>2395</v>
       </c>
       <c r="C90" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D90" t="n">
         <v>5</v>
       </c>
       <c r="E90" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Damien</t>
+          <t>ousmane</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>PANENKANY</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>2285</v>
+        <v>2346</v>
       </c>
       <c r="C91" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D91" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E91" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>Fuzo697</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3323,30 +3323,30 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>2261</v>
+        <v>2328</v>
       </c>
       <c r="C92" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D92" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E92" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Laetitia</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fuzo697</t>
+          <t>Laetice2020</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3355,30 +3355,30 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>2243</v>
+        <v>2297</v>
       </c>
       <c r="C93" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D93" t="n">
         <v>5</v>
       </c>
       <c r="E93" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Laetitia</t>
+          <t>Damien</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Laetice2020</t>
+          <t>PANENKANY</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3387,16 +3387,16 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>2230</v>
+        <v>2295</v>
       </c>
       <c r="C94" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D94" t="n">
         <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -3419,30 +3419,30 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>2227</v>
+        <v>2288</v>
       </c>
       <c r="C95" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D95" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E95" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ibra</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>PacoSarra</t>
+          <t>Emma_Noel</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3451,30 +3451,30 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>2226</v>
+        <v>2285</v>
       </c>
       <c r="C96" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D96" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E96" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>YassineZ95</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3483,30 +3483,30 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>2203</v>
+        <v>2264</v>
       </c>
       <c r="C97" t="n">
         <v>37</v>
       </c>
       <c r="D97" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E97" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Emma_Noel</t>
+          <t>C4M</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3515,30 +3515,30 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>2199</v>
+        <v>2227</v>
       </c>
       <c r="C98" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D98" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E98" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Ibra</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>C4M</t>
+          <t>PacoSarra</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3547,16 +3547,16 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>2070</v>
+        <v>2135</v>
       </c>
       <c r="C99" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D99" t="n">
         <v>3</v>
       </c>
       <c r="E99" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -3579,16 +3579,16 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>2053</v>
+        <v>2118</v>
       </c>
       <c r="C100" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D100" t="n">
         <v>6</v>
       </c>
       <c r="E100" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -3611,16 +3611,16 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>2042</v>
+        <v>2107</v>
       </c>
       <c r="C101" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D101" t="n">
         <v>4</v>
       </c>
       <c r="E101" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -3643,30 +3643,30 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>2032</v>
+        <v>2086</v>
       </c>
       <c r="C102" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D102" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E102" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>Léa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Valentine___</t>
+          <t>LeaBrd</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3675,30 +3675,30 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>2014</v>
+        <v>2041</v>
       </c>
       <c r="C103" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D103" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E103" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Jérémy</t>
+          <t>lea</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>JeremFZ</t>
+          <t>RBTL</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3707,30 +3707,30 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>2001</v>
+        <v>2032</v>
       </c>
       <c r="C104" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D104" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E104" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Léa</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>LeaBrd</t>
+          <t>Valentine___</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3739,30 +3739,30 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>1956</v>
+        <v>2014</v>
       </c>
       <c r="C105" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D105" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E105" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>lea</t>
+          <t>Jérémy</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>RBTL</t>
+          <t>JeremFZ</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3803,16 +3803,16 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>1707</v>
+        <v>1772</v>
       </c>
       <c r="C107" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D107" t="n">
         <v>6</v>
       </c>
       <c r="E107" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>

--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3676</v>
+        <v>3828</v>
       </c>
       <c r="C2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,30 +495,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>3624</v>
+        <v>3770</v>
       </c>
       <c r="C3" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>SabC1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>3553</v>
+        <v>3746</v>
       </c>
       <c r="C4" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SabC1</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>3496</v>
+        <v>3733</v>
       </c>
       <c r="C5" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>3486</v>
+        <v>3693</v>
       </c>
       <c r="C6" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>3470</v>
+        <v>3630</v>
       </c>
       <c r="C7" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -655,16 +655,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>3454</v>
+        <v>3576</v>
       </c>
       <c r="C8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D8" t="n">
         <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>3441</v>
+        <v>3567</v>
       </c>
       <c r="C9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>3434</v>
+        <v>3550</v>
       </c>
       <c r="C10" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -751,16 +751,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3392</v>
+        <v>3544</v>
       </c>
       <c r="C11" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -783,30 +783,30 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>3383</v>
+        <v>3528</v>
       </c>
       <c r="C12" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -815,25 +815,25 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>3350</v>
+        <v>3510</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -847,30 +847,30 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>3331</v>
+        <v>3509</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -879,25 +879,25 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>3293</v>
+        <v>3508</v>
       </c>
       <c r="C15" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -911,25 +911,25 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>3263</v>
+        <v>3497</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -943,25 +943,25 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>3260</v>
+        <v>3472</v>
       </c>
       <c r="C17" t="n">
         <v>48</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -975,25 +975,25 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>3250</v>
+        <v>3451</v>
       </c>
       <c r="C18" t="n">
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1007,30 +1007,30 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>3210</v>
+        <v>3417</v>
       </c>
       <c r="C19" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1039,30 +1039,30 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>3198</v>
+        <v>3412</v>
       </c>
       <c r="C20" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Panaf</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Panaff</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1071,30 +1071,30 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>3197</v>
+        <v>3407</v>
       </c>
       <c r="C21" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Antonio Moctezuma</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>abihuts</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1103,30 +1103,30 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>3190</v>
+        <v>3380</v>
       </c>
       <c r="C22" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Antonio Moctezuma</t>
+          <t>Panaf</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>abihuts</t>
+          <t>Panaff</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1135,30 +1135,30 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>3177</v>
+        <v>3377</v>
       </c>
       <c r="C23" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mathilde</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>MT35T</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1167,30 +1167,30 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>3174</v>
+        <v>3340</v>
       </c>
       <c r="C24" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D24" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E24" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Mathilde</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>MT35T</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1199,30 +1199,30 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>3170</v>
+        <v>3332</v>
       </c>
       <c r="C25" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Marion1822</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1231,30 +1231,30 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>3163</v>
+        <v>3319</v>
       </c>
       <c r="C26" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E26" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1263,30 +1263,30 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>3160</v>
+        <v>3290</v>
       </c>
       <c r="C27" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1295,30 +1295,30 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>3127</v>
+        <v>3277</v>
       </c>
       <c r="C28" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>Devilrock95</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1327,25 +1327,25 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>3103</v>
+        <v>3264</v>
       </c>
       <c r="C29" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D29" t="n">
         <v>7</v>
       </c>
       <c r="E29" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>EmyEnzo</t>
+          <t>Marie__92</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1359,30 +1359,30 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>3090</v>
+        <v>3249</v>
       </c>
       <c r="C30" t="n">
         <v>45</v>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E30" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1391,30 +1391,30 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>3085</v>
+        <v>3212</v>
       </c>
       <c r="C31" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E31" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1423,30 +1423,30 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>3071</v>
+        <v>3210</v>
       </c>
       <c r="C32" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E32" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Romain J</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1455,25 +1455,25 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>3063</v>
+        <v>3201</v>
       </c>
       <c r="C33" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D33" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E33" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1487,25 +1487,25 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>3062</v>
+        <v>3193</v>
       </c>
       <c r="C34" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D34" t="n">
         <v>8</v>
       </c>
       <c r="E34" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
+          <t>Romain_JO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1519,57 +1519,53 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>3050</v>
+        <v>3144</v>
       </c>
       <c r="C35" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E35" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Brick</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Devilrock95</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>3037</v>
+        <v>3141</v>
       </c>
       <c r="C36" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E36" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Marie__92</t>
+          <t>EmyEnzo</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1583,30 +1579,30 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>3004</v>
+        <v>3137</v>
       </c>
       <c r="C37" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E37" t="n">
         <v>76</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1615,30 +1611,30 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>3003</v>
+        <v>3123</v>
       </c>
       <c r="C38" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D38" t="n">
         <v>10</v>
       </c>
       <c r="E38" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1647,58 +1643,62 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>2992</v>
+        <v>3121</v>
       </c>
       <c r="C39" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E39" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>BrickXVI</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>FRHTCTD10</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>2976</v>
+        <v>3116</v>
       </c>
       <c r="C40" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D40" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E40" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1707,25 +1707,25 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>2973</v>
+        <v>3100</v>
       </c>
       <c r="C41" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E41" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1739,44 +1739,48 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>2969</v>
+        <v>3099</v>
       </c>
       <c r="C42" t="n">
         <v>46</v>
       </c>
       <c r="D42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E42" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Francisco93</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Camillewbl</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>2963</v>
+        <v>3096</v>
       </c>
       <c r="C43" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E43" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1799,30 +1803,30 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>2940</v>
+        <v>3094</v>
       </c>
       <c r="C44" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D44" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E44" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Erwan</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>Erwan#4G91X</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1831,57 +1835,53 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>2933</v>
+        <v>3091</v>
       </c>
       <c r="C45" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D45" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E45" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>François</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>2930</v>
+        <v>3089</v>
       </c>
       <c r="C46" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E46" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -1895,30 +1895,30 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>2904</v>
+        <v>3082</v>
       </c>
       <c r="C47" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E47" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1927,30 +1927,30 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>2902</v>
+        <v>3060</v>
       </c>
       <c r="C48" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D48" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E48" t="n">
         <v>73</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Marilena</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Camillewbl</t>
+          <t>GOAT#UE2WM8M9</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1959,30 +1959,30 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>2897</v>
+        <v>3042</v>
       </c>
       <c r="C49" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E49" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Erwan</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Erwan#4G91X</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1991,30 +1991,30 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>2823</v>
+        <v>3041</v>
       </c>
       <c r="C50" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D50" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E50" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Loïc</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Exia95</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2023,30 +2023,30 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>2819</v>
+        <v>3001</v>
       </c>
       <c r="C51" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E51" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lison</t>
+          <t>romain</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lyzone</t>
+          <t>RomainLect</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2055,30 +2055,30 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>2814</v>
+        <v>2986</v>
       </c>
       <c r="C52" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D52" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E52" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>William</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>WIL1610</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2087,30 +2087,30 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>2813</v>
+        <v>2971</v>
       </c>
       <c r="C53" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D53" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E53" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Marilena</t>
+          <t>Lison</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>GOAT#UE2WM8M9</t>
+          <t>Lyzone</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2119,16 +2119,16 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>2808</v>
+        <v>2941</v>
       </c>
       <c r="C54" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E54" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2151,58 +2151,62 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>2793</v>
+        <v>2938</v>
       </c>
       <c r="C55" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D55" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E55" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fa_One</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>MatuRenard</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>2769</v>
+        <v>2937</v>
       </c>
       <c r="C56" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D56" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E56" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>WIL1610</t>
+          <t>Kolas</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2211,30 +2215,30 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>2756</v>
+        <v>2919</v>
       </c>
       <c r="C57" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D57" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E57" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2243,62 +2247,58 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>2752</v>
+        <v>2915</v>
       </c>
       <c r="C58" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E58" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>JKInternational</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Fa_One</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>2744</v>
+        <v>2894</v>
       </c>
       <c r="C59" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D59" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E59" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>romain</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>RomainLect</t>
+          <t>AudreyB225</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2307,62 +2307,58 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>2742</v>
+        <v>2889</v>
       </c>
       <c r="C60" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D60" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E60" t="n">
         <v>76</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>AudreyB225</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>compta</t>
-        </is>
-      </c>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>2741</v>
+        <v>2885</v>
       </c>
       <c r="C61" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D61" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2371,30 +2367,30 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>2722</v>
+        <v>2882</v>
       </c>
       <c r="C62" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D62" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E62" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Cécile</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>Ceciledp</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2403,30 +2399,30 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>2711</v>
+        <v>2882</v>
       </c>
       <c r="C63" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E63" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t xml:space="preserve">Liliane </t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
+          <t>LilianeB</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2435,30 +2431,30 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>2690</v>
+        <v>2871</v>
       </c>
       <c r="C64" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D64" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E64" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Kolas</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2467,30 +2463,30 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>2685</v>
+        <v>2863</v>
       </c>
       <c r="C65" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D65" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E65" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liliane </t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>LilianeB</t>
+          <t>Melissagzb</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2499,25 +2495,25 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>2675</v>
+        <v>2861</v>
       </c>
       <c r="C66" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E66" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Loïc</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>K_Marp</t>
+          <t>Exia95</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2531,58 +2527,62 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>2672</v>
+        <v>2852</v>
       </c>
       <c r="C67" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D67" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E67" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>Ze_GOAT</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>2665</v>
+        <v>2843</v>
       </c>
       <c r="C68" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D68" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E68" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Cécile</t>
+          <t>Priscilla</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ceciledp</t>
+          <t>Priscilla#4LCAF</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2591,30 +2591,30 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>2644</v>
+        <v>2797</v>
       </c>
       <c r="C69" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E69" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>K_Marp</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2623,30 +2623,30 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>2626</v>
+        <v>2794</v>
       </c>
       <c r="C70" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D70" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E70" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Priscilla</t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Priscilla#4LCAF</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2655,30 +2655,30 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>2620</v>
+        <v>2768</v>
       </c>
       <c r="C71" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D71" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E71" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>MxKnight</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2687,30 +2687,30 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>2598</v>
+        <v>2753</v>
       </c>
       <c r="C72" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D72" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E72" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Juliie</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pipou931</t>
+          <t>MxKnight</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2719,30 +2719,30 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>2596</v>
+        <v>2750</v>
       </c>
       <c r="C73" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D73" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E73" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Juliie</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>Pipou931</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2751,25 +2751,25 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>2571</v>
+        <v>2718</v>
       </c>
       <c r="C74" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D74" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E74" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -2783,16 +2783,16 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>2570</v>
+        <v>2692</v>
       </c>
       <c r="C75" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D75" t="n">
         <v>7</v>
       </c>
       <c r="E75" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -2815,16 +2815,16 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>2565</v>
+        <v>2687</v>
       </c>
       <c r="C76" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D76" t="n">
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -2847,30 +2847,30 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>2561</v>
+        <v>2687</v>
       </c>
       <c r="C77" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D77" t="n">
         <v>6</v>
       </c>
       <c r="E77" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>Timy</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2879,30 +2879,30 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>2561</v>
+        <v>2683</v>
       </c>
       <c r="C78" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D78" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E78" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2911,25 +2911,25 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>2538</v>
+        <v>2675</v>
       </c>
       <c r="C79" t="n">
         <v>41</v>
       </c>
       <c r="D79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E79" t="n">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -2943,25 +2943,25 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>2508</v>
+        <v>2662</v>
       </c>
       <c r="C80" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D80" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E80" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -2975,16 +2975,16 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>2497</v>
+        <v>2649</v>
       </c>
       <c r="C81" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D81" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E81" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3007,30 +3007,30 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>2478</v>
+        <v>2629</v>
       </c>
       <c r="C82" t="n">
         <v>38</v>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E82" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>Teddbear</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3039,16 +3039,16 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>2472</v>
+        <v>2594</v>
       </c>
       <c r="C83" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D83" t="n">
         <v>4</v>
       </c>
       <c r="E83" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3071,30 +3071,30 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>2470</v>
+        <v>2593</v>
       </c>
       <c r="C84" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D84" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E84" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Timy</t>
+          <t>Fuzo697</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3103,30 +3103,30 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>2460</v>
+        <v>2587</v>
       </c>
       <c r="C85" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D85" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E85" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cindie</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cindie_JJA</t>
+          <t>dian-bgt</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3135,30 +3135,30 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>2449</v>
+        <v>2582</v>
       </c>
       <c r="C86" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D86" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E86" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Cindie</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Maruyama</t>
+          <t>Cindie_JJA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3167,25 +3167,25 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>2445</v>
+        <v>2546</v>
       </c>
       <c r="C87" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D87" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E87" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3199,30 +3199,30 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>2438</v>
+        <v>2538</v>
       </c>
       <c r="C88" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D88" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E88" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Brieuc</t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Yebri</t>
+          <t>chaychaychay</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3231,25 +3231,25 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>2435</v>
+        <v>2513</v>
       </c>
       <c r="C89" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D89" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E89" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Brieuc</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
+          <t>Yebri</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3263,53 +3263,57 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>2395</v>
+        <v>2487</v>
       </c>
       <c r="C90" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E90" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ousmane</t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Taylor2901</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>Maruyama</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>2346</v>
+        <v>2479</v>
       </c>
       <c r="C91" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D91" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E91" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Damien</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fuzo697</t>
+          <t>PANENKANY</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3323,62 +3327,58 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>2328</v>
+        <v>2463</v>
       </c>
       <c r="C92" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D92" t="n">
         <v>6</v>
       </c>
       <c r="E92" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Laetitia</t>
+          <t>ousmane</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Laetice2020</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>2297</v>
+        <v>2454</v>
       </c>
       <c r="C93" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D93" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E93" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Damien</t>
+          <t>Ibra</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>PANENKANY</t>
+          <t>PacoSarra</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3387,30 +3387,30 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>2295</v>
+        <v>2431</v>
       </c>
       <c r="C94" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D94" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E94" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Camss</t>
+          <t>Emma_Noel</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3419,30 +3419,30 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>2288</v>
+        <v>2366</v>
       </c>
       <c r="C95" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D95" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E95" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Laetitia</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Emma_Noel</t>
+          <t>Laetice2020</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3451,30 +3451,30 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>2285</v>
+        <v>2348</v>
       </c>
       <c r="C96" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D96" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E96" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>C4M</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3483,16 +3483,16 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>2264</v>
+        <v>2333</v>
       </c>
       <c r="C97" t="n">
         <v>37</v>
       </c>
       <c r="D97" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E97" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>C4M</t>
+          <t>Camss</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -3515,30 +3515,30 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>2227</v>
+        <v>2323</v>
       </c>
       <c r="C98" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D98" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E98" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ibra</t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>PacoSarra</t>
+          <t>YassineZ95</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3547,30 +3547,30 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>2135</v>
+        <v>2303</v>
       </c>
       <c r="C99" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D99" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E99" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Killian</t>
+          <t>Léa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>KIKS999</t>
+          <t>LeaBrd</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3579,30 +3579,30 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>2118</v>
+        <v>2193</v>
       </c>
       <c r="C100" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D100" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E100" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>lea</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>JEVAISGAGNER10</t>
+          <t>RBTL</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3611,30 +3611,30 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>2107</v>
+        <v>2184</v>
       </c>
       <c r="C101" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D101" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E101" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sab_M45</t>
+          <t>Valentine___</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3643,30 +3643,30 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>2086</v>
+        <v>2173</v>
       </c>
       <c r="C102" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D102" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E102" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Léa</t>
+          <t>Killian</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>LeaBrd</t>
+          <t>KIKS999</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3675,30 +3675,30 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>2041</v>
+        <v>2156</v>
       </c>
       <c r="C103" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D103" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E103" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>lea</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>RBTL</t>
+          <t>JEVAISGAGNER10</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3707,30 +3707,30 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>2032</v>
+        <v>2117</v>
       </c>
       <c r="C104" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D104" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E104" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Valentine___</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3739,25 +3739,25 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>2014</v>
+        <v>2107</v>
       </c>
       <c r="C105" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D105" t="n">
         <v>4</v>
       </c>
       <c r="E105" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Jérémy</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>JeremFZ</t>
+          <t>Sab_M45</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -3771,30 +3771,30 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>1900</v>
+        <v>2052</v>
       </c>
       <c r="C106" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D106" t="n">
         <v>4</v>
       </c>
       <c r="E106" t="n">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>Jérémy</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
+          <t>JeremFZ</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3803,16 +3803,16 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>1772</v>
+        <v>1999</v>
       </c>
       <c r="C107" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D107" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E107" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -3863,16 +3863,16 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>983</v>
+        <v>1021</v>
       </c>
       <c r="C109" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D109" t="n">
         <v>2</v>
       </c>
       <c r="E109" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3828</v>
+        <v>3867</v>
       </c>
       <c r="C2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>3770</v>
+        <v>3809</v>
       </c>
       <c r="C3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>3746</v>
+        <v>3772</v>
       </c>
       <c r="C4" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>3733</v>
+        <v>3746</v>
       </c>
       <c r="C5" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -591,16 +591,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>3693</v>
+        <v>3732</v>
       </c>
       <c r="C6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -623,16 +623,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>3630</v>
+        <v>3669</v>
       </c>
       <c r="C7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -655,16 +655,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>3576</v>
+        <v>3615</v>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" t="n">
         <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -687,16 +687,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>3567</v>
+        <v>3606</v>
       </c>
       <c r="C9" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>3550</v>
+        <v>3598</v>
       </c>
       <c r="C10" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3544</v>
+        <v>3589</v>
       </c>
       <c r="C11" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -783,30 +783,30 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>3528</v>
+        <v>3586</v>
       </c>
       <c r="C12" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -815,25 +815,25 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>3510</v>
+        <v>3583</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -847,30 +847,30 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>3509</v>
+        <v>3567</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -879,30 +879,30 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>3508</v>
+        <v>3561</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
         <v>79</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -911,25 +911,25 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>3497</v>
+        <v>3549</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E16" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -943,30 +943,30 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>3472</v>
+        <v>3547</v>
       </c>
       <c r="C17" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -975,16 +975,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>3451</v>
+        <v>3490</v>
       </c>
       <c r="C18" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
         <v>15</v>
       </c>
       <c r="E18" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1007,30 +1007,30 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>3417</v>
+        <v>3466</v>
       </c>
       <c r="C19" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Marion1822</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1039,30 +1039,30 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>3412</v>
+        <v>3456</v>
       </c>
       <c r="C20" t="n">
         <v>50</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E20" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1071,30 +1071,30 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>3407</v>
+        <v>3451</v>
       </c>
       <c r="C21" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Antonio Moctezuma</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>abihuts</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1103,30 +1103,30 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>3380</v>
+        <v>3446</v>
       </c>
       <c r="C22" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Panaf</t>
+          <t>Antonio Moctezuma</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Panaff</t>
+          <t>abihuts</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1135,30 +1135,30 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>3377</v>
+        <v>3419</v>
       </c>
       <c r="C23" t="n">
         <v>49</v>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Panaf</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>Panaff</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1167,25 +1167,25 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>3340</v>
+        <v>3408</v>
       </c>
       <c r="C24" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mathilde</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>MT35T</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1199,30 +1199,30 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>3332</v>
+        <v>3379</v>
       </c>
       <c r="C25" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
         <v>79</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Mathilde</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>MT35T</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1231,30 +1231,30 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>3319</v>
+        <v>3371</v>
       </c>
       <c r="C26" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1263,16 +1263,16 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>3290</v>
+        <v>3329</v>
       </c>
       <c r="C27" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D27" t="n">
         <v>10</v>
       </c>
       <c r="E27" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1295,16 +1295,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>3277</v>
+        <v>3316</v>
       </c>
       <c r="C28" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D28" t="n">
         <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1327,16 +1327,16 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>3264</v>
+        <v>3303</v>
       </c>
       <c r="C29" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D29" t="n">
         <v>7</v>
       </c>
       <c r="E29" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1359,16 +1359,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>3249</v>
+        <v>3288</v>
       </c>
       <c r="C30" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D30" t="n">
         <v>7</v>
       </c>
       <c r="E30" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1391,30 +1391,30 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>3212</v>
+        <v>3282</v>
       </c>
       <c r="C31" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D31" t="n">
         <v>9</v>
       </c>
       <c r="E31" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Romain_JO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1423,30 +1423,30 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>3210</v>
+        <v>3251</v>
       </c>
       <c r="C32" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D32" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E32" t="n">
         <v>79</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1455,25 +1455,25 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>3201</v>
+        <v>3249</v>
       </c>
       <c r="C33" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D33" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E33" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1487,90 +1487,90 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>3193</v>
+        <v>3233</v>
       </c>
       <c r="C34" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E34" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Romain J</t>
+          <t>Brick</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>3144</v>
+        <v>3230</v>
       </c>
       <c r="C35" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E35" t="n">
         <v>79</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>BrickXVI</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>EmyEnzo</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>3141</v>
+        <v>3201</v>
       </c>
       <c r="C36" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D36" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E36" t="n">
         <v>78</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>EmyEnzo</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1579,30 +1579,30 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>3137</v>
+        <v>3185</v>
       </c>
       <c r="C37" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E37" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1611,30 +1611,30 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>3123</v>
+        <v>3178</v>
       </c>
       <c r="C38" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D38" t="n">
         <v>10</v>
       </c>
       <c r="E38" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1643,30 +1643,30 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>3121</v>
+        <v>3176</v>
       </c>
       <c r="C39" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D39" t="n">
         <v>9</v>
       </c>
       <c r="E39" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1675,30 +1675,30 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>3116</v>
+        <v>3171</v>
       </c>
       <c r="C40" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D40" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E40" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1707,25 +1707,25 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>3100</v>
+        <v>3162</v>
       </c>
       <c r="C41" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D41" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E41" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1739,30 +1739,30 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>3099</v>
+        <v>3160</v>
       </c>
       <c r="C42" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E42" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Camillewbl</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1771,30 +1771,30 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>3096</v>
+        <v>3155</v>
       </c>
       <c r="C43" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D43" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E43" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1803,25 +1803,25 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>3094</v>
+        <v>3139</v>
       </c>
       <c r="C44" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E44" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Erwan</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Erwan#4G91X</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1835,58 +1835,62 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>3091</v>
+        <v>3138</v>
       </c>
       <c r="C45" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E45" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Francisco93</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>Camillewbl</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>3089</v>
+        <v>3133</v>
       </c>
       <c r="C46" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D46" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E46" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Erwan</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>Erwan#4G91X</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1895,30 +1899,30 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>3082</v>
+        <v>3099</v>
       </c>
       <c r="C47" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D47" t="n">
         <v>9</v>
       </c>
       <c r="E47" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>Marilena</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>GOAT#UE2WM8M9</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1927,57 +1931,53 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>3060</v>
+        <v>3091</v>
       </c>
       <c r="C48" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D48" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E48" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Marilena</t>
+          <t>François</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>GOAT#UE2WM8M9</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>3042</v>
+        <v>3080</v>
       </c>
       <c r="C49" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D49" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E49" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -1991,25 +1991,25 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="C50" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D50" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E50" t="n">
         <v>79</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2023,16 +2023,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>3001</v>
+        <v>3040</v>
       </c>
       <c r="C51" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D51" t="n">
         <v>9</v>
       </c>
       <c r="E51" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2055,16 +2055,16 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>2986</v>
+        <v>3025</v>
       </c>
       <c r="C52" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D52" t="n">
         <v>7</v>
       </c>
       <c r="E52" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2087,16 +2087,16 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>2971</v>
+        <v>3010</v>
       </c>
       <c r="C53" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D53" t="n">
         <v>6</v>
       </c>
       <c r="E53" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2119,30 +2119,30 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>2941</v>
+        <v>3008</v>
       </c>
       <c r="C54" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D54" t="n">
         <v>10</v>
       </c>
       <c r="E54" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2151,62 +2151,58 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>2938</v>
+        <v>3004</v>
       </c>
       <c r="C55" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D55" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E55" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Reste du monde</t>
-        </is>
-      </c>
+          <t>Fa_One</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>2937</v>
+        <v>2980</v>
       </c>
       <c r="C56" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D56" t="n">
         <v>10</v>
       </c>
       <c r="E56" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Kolas</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2215,25 +2211,25 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>2919</v>
+        <v>2977</v>
       </c>
       <c r="C57" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D57" t="n">
         <v>9</v>
       </c>
       <c r="E57" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>MatuRenard</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2247,58 +2243,62 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>2915</v>
+        <v>2976</v>
       </c>
       <c r="C58" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D58" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E58" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fa_One</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Kolas</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>2894</v>
+        <v>2974</v>
       </c>
       <c r="C59" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D59" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E59" t="n">
         <v>79</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>AudreyB225</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2307,76 +2307,76 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>2889</v>
+        <v>2933</v>
       </c>
       <c r="C60" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D60" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E60" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>AudreyB225</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>2885</v>
+        <v>2928</v>
       </c>
       <c r="C61" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E61" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>JKInternational</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>2882</v>
+        <v>2921</v>
       </c>
       <c r="C62" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D62" t="n">
         <v>5</v>
       </c>
       <c r="E62" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -2399,16 +2399,16 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>2882</v>
+        <v>2921</v>
       </c>
       <c r="C63" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D63" t="n">
         <v>9</v>
       </c>
       <c r="E63" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -2431,30 +2431,30 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>2871</v>
+        <v>2902</v>
       </c>
       <c r="C64" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D64" t="n">
         <v>7</v>
       </c>
       <c r="E64" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>Melissagzb</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2463,30 +2463,30 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>2863</v>
+        <v>2900</v>
       </c>
       <c r="C65" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D65" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E65" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Loïc</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>Exia95</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2495,30 +2495,30 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>2861</v>
+        <v>2882</v>
       </c>
       <c r="C66" t="n">
         <v>47</v>
       </c>
       <c r="D66" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E66" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Loïc</t>
+          <t>Priscilla</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Exia95</t>
+          <t>Priscilla#4LCAF</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2527,30 +2527,30 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>2852</v>
+        <v>2871</v>
       </c>
       <c r="C67" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D67" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E67" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2559,30 +2559,30 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>2843</v>
+        <v>2852</v>
       </c>
       <c r="C68" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D68" t="n">
         <v>8</v>
       </c>
       <c r="E68" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Priscilla</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Priscilla#4LCAF</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2591,25 +2591,25 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>2797</v>
+        <v>2842</v>
       </c>
       <c r="C69" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>K_Marp</t>
+          <t>MxKnight</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -2623,30 +2623,30 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>2794</v>
+        <v>2836</v>
       </c>
       <c r="C70" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E70" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>K_Marp</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2655,30 +2655,30 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>2768</v>
+        <v>2794</v>
       </c>
       <c r="C71" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E71" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2687,30 +2687,30 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>2753</v>
+        <v>2789</v>
       </c>
       <c r="C72" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D72" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E72" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Juliie</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>MxKnight</t>
+          <t>Pipou931</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2719,30 +2719,30 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>2750</v>
+        <v>2781</v>
       </c>
       <c r="C73" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E73" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Juliie</t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pipou931</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2751,25 +2751,25 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>2718</v>
+        <v>2768</v>
       </c>
       <c r="C74" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D74" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E74" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -2783,30 +2783,30 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>2692</v>
+        <v>2764</v>
       </c>
       <c r="C75" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D75" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E75" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2815,30 +2815,30 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>2687</v>
+        <v>2757</v>
       </c>
       <c r="C76" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D76" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E76" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Soraya</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Soraya-Y</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2847,16 +2847,16 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>2687</v>
+        <v>2726</v>
       </c>
       <c r="C77" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D77" t="n">
         <v>6</v>
       </c>
       <c r="E77" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -2879,16 +2879,16 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>2683</v>
+        <v>2722</v>
       </c>
       <c r="C78" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D78" t="n">
         <v>6</v>
       </c>
       <c r="E78" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -2911,30 +2911,30 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>2675</v>
+        <v>2688</v>
       </c>
       <c r="C79" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D79" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E79" t="n">
         <v>79</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Selver</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>Seesee</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2943,30 +2943,30 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>2662</v>
+        <v>2687</v>
       </c>
       <c r="C80" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D80" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E80" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Soraya</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>Soraya-Y</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2975,30 +2975,30 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>2649</v>
+        <v>2676</v>
       </c>
       <c r="C81" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D81" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E81" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Seesee</t>
+          <t>dian-bgt</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3007,30 +3007,30 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>2629</v>
+        <v>2662</v>
       </c>
       <c r="C82" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D82" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E82" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3039,16 +3039,16 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>2594</v>
+        <v>2633</v>
       </c>
       <c r="C83" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D83" t="n">
         <v>4</v>
       </c>
       <c r="E83" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3071,16 +3071,16 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>2593</v>
+        <v>2632</v>
       </c>
       <c r="C84" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D84" t="n">
         <v>7</v>
       </c>
       <c r="E84" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -3103,30 +3103,30 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>2587</v>
+        <v>2629</v>
       </c>
       <c r="C85" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D85" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E85" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
+          <t>Teddbear</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3135,30 +3135,30 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>2582</v>
+        <v>2585</v>
       </c>
       <c r="C86" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D86" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E86" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cindie</t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cindie_JJA</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3167,30 +3167,30 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>2546</v>
+        <v>2582</v>
       </c>
       <c r="C87" t="n">
         <v>41</v>
       </c>
       <c r="D87" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E87" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t>Cindie</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>Cindie_JJA</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3199,30 +3199,30 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>2538</v>
+        <v>2552</v>
       </c>
       <c r="C88" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D88" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E88" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>Brieuc</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>Yebri</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3231,30 +3231,30 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>2513</v>
+        <v>2538</v>
       </c>
       <c r="C89" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D89" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E89" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Brieuc</t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Yebri</t>
+          <t>chaychaychay</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3263,30 +3263,30 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>2487</v>
+        <v>2518</v>
       </c>
       <c r="C90" t="n">
         <v>39</v>
       </c>
       <c r="D90" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E90" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Damien</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Maruyama</t>
+          <t>PANENKANY</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3295,90 +3295,90 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>2479</v>
+        <v>2502</v>
       </c>
       <c r="C91" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D91" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E91" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Damien</t>
+          <t>ousmane</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>PANENKANY</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>2463</v>
+        <v>2487</v>
       </c>
       <c r="C92" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D92" t="n">
         <v>6</v>
       </c>
       <c r="E92" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ousmane</t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Taylor2901</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
+          <t>Maruyama</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>2454</v>
+        <v>2470</v>
       </c>
       <c r="C93" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D93" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E93" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ibra</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>PacoSarra</t>
+          <t>Emma_Noel</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3387,30 +3387,30 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>2431</v>
+        <v>2454</v>
       </c>
       <c r="C94" t="n">
         <v>40</v>
       </c>
       <c r="D94" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E94" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Ibra</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Emma_Noel</t>
+          <t>PacoSarra</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3419,16 +3419,16 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>2366</v>
+        <v>2405</v>
       </c>
       <c r="C95" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D95" t="n">
         <v>6</v>
       </c>
       <c r="E95" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -3451,16 +3451,16 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>2348</v>
+        <v>2387</v>
       </c>
       <c r="C96" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D96" t="n">
         <v>5</v>
       </c>
       <c r="E96" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3483,16 +3483,16 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>2333</v>
+        <v>2372</v>
       </c>
       <c r="C97" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D97" t="n">
         <v>7</v>
       </c>
       <c r="E97" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -3515,16 +3515,16 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>2323</v>
+        <v>2362</v>
       </c>
       <c r="C98" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D98" t="n">
         <v>6</v>
       </c>
       <c r="E98" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -3547,16 +3547,16 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>2303</v>
+        <v>2342</v>
       </c>
       <c r="C99" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D99" t="n">
         <v>6</v>
       </c>
       <c r="E99" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -3579,16 +3579,16 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>2193</v>
+        <v>2232</v>
       </c>
       <c r="C100" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D100" t="n">
         <v>4</v>
       </c>
       <c r="E100" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -3611,25 +3611,25 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>2184</v>
+        <v>2212</v>
       </c>
       <c r="C101" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D101" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E101" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>Killian</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Valentine___</t>
+          <t>KIKS999</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -3643,30 +3643,30 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>2173</v>
+        <v>2195</v>
       </c>
       <c r="C102" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D102" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E102" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Killian</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>KIKS999</t>
+          <t>JEVAISGAGNER10</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3675,30 +3675,30 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>2156</v>
+        <v>2184</v>
       </c>
       <c r="C103" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D103" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E103" t="n">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>JEVAISGAGNER10</t>
+          <t>Valentine___</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3707,16 +3707,16 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>2117</v>
+        <v>2156</v>
       </c>
       <c r="C104" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D104" t="n">
         <v>5</v>
       </c>
       <c r="E104" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -3739,16 +3739,16 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>2107</v>
+        <v>2146</v>
       </c>
       <c r="C105" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D105" t="n">
         <v>4</v>
       </c>
       <c r="E105" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -3771,16 +3771,16 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>2052</v>
+        <v>2091</v>
       </c>
       <c r="C106" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D106" t="n">
         <v>4</v>
       </c>
       <c r="E106" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -3803,16 +3803,16 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>1999</v>
+        <v>2038</v>
       </c>
       <c r="C107" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D107" t="n">
         <v>7</v>
       </c>
       <c r="E107" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>2</v>
       </c>
       <c r="E109" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -463,25 +463,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3867</v>
+        <v>3941</v>
       </c>
       <c r="C2" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
         <v>80</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>SabC1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -495,30 +495,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>3809</v>
+        <v>3904</v>
       </c>
       <c r="C3" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SabC1</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>3772</v>
+        <v>3878</v>
       </c>
       <c r="C4" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>3746</v>
+        <v>3867</v>
       </c>
       <c r="C5" t="n">
         <v>49</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -591,16 +591,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>3732</v>
+        <v>3784</v>
       </c>
       <c r="C6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -623,25 +623,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>3669</v>
+        <v>3730</v>
       </c>
       <c r="C7" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>80</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>3615</v>
+        <v>3721</v>
       </c>
       <c r="C8" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>3606</v>
+        <v>3721</v>
       </c>
       <c r="C9" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>3598</v>
+        <v>3718</v>
       </c>
       <c r="C10" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3589</v>
+        <v>3678</v>
       </c>
       <c r="C11" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -783,30 +783,30 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>3586</v>
+        <v>3667</v>
       </c>
       <c r="C12" t="n">
         <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -815,16 +815,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>3583</v>
+        <v>3635</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
         <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -847,16 +847,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>3567</v>
+        <v>3619</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
         <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -879,25 +879,25 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>3561</v>
+        <v>3618</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -911,30 +911,30 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>3549</v>
+        <v>3613</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -943,30 +943,30 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>3547</v>
+        <v>3601</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -975,30 +975,30 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>3490</v>
+        <v>3599</v>
       </c>
       <c r="C18" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1007,25 +1007,25 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>3466</v>
+        <v>3583</v>
       </c>
       <c r="C19" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1039,30 +1039,30 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>3456</v>
+        <v>3578</v>
       </c>
       <c r="C20" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D20" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>Antonio Moctezuma</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Marion1822</t>
+          <t>abihuts</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1071,30 +1071,30 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>3451</v>
+        <v>3551</v>
       </c>
       <c r="C21" t="n">
         <v>51</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Panaf</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>Panaff</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1103,25 +1103,25 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>3446</v>
+        <v>3542</v>
       </c>
       <c r="C22" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E22" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Antonio Moctezuma</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>abihuts</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1135,30 +1135,30 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>3419</v>
+        <v>3528</v>
       </c>
       <c r="C23" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E23" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Panaf</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Panaff</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1167,25 +1167,25 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>3408</v>
+        <v>3511</v>
       </c>
       <c r="C24" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D24" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E24" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Mathilde</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>MT35T</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1199,25 +1199,25 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>3379</v>
+        <v>3460</v>
       </c>
       <c r="C25" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E25" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mathilde</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MT35T</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1231,25 +1231,25 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>3371</v>
+        <v>3455</v>
       </c>
       <c r="C26" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D26" t="n">
         <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>Marie__92</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1263,30 +1263,30 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>3329</v>
+        <v>3423</v>
       </c>
       <c r="C27" t="n">
         <v>49</v>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1295,30 +1295,30 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>3316</v>
+        <v>3401</v>
       </c>
       <c r="C28" t="n">
         <v>53</v>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E28" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Devilrock95</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1327,30 +1327,30 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>3303</v>
+        <v>3388</v>
       </c>
       <c r="C29" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Marie__92</t>
+          <t>Devilrock95</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1359,30 +1359,30 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>3288</v>
+        <v>3383</v>
       </c>
       <c r="C30" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1391,30 +1391,30 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>3282</v>
+        <v>3329</v>
       </c>
       <c r="C31" t="n">
         <v>49</v>
       </c>
       <c r="D31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E31" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Romain J</t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1423,30 +1423,30 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>3251</v>
+        <v>3288</v>
       </c>
       <c r="C32" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D32" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E32" t="n">
         <v>79</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1455,76 +1455,76 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>3249</v>
+        <v>3285</v>
       </c>
       <c r="C33" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D33" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E33" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Brick</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>3233</v>
+        <v>3282</v>
       </c>
       <c r="C34" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>BrickXVI</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Romain_JO</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>3230</v>
+        <v>3282</v>
       </c>
       <c r="C35" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D35" t="n">
         <v>8</v>
       </c>
       <c r="E35" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1547,30 +1547,30 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>3201</v>
+        <v>3270</v>
       </c>
       <c r="C36" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D36" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>Camillewbl</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1579,30 +1579,30 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>3185</v>
+        <v>3265</v>
       </c>
       <c r="C37" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D37" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E37" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>Erwan</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>Erwan#4G91X</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1611,25 +1611,25 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>3178</v>
+        <v>3253</v>
       </c>
       <c r="C38" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D38" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E38" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1643,30 +1643,30 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>3176</v>
+        <v>3251</v>
       </c>
       <c r="C39" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E39" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Marilena</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>GOAT#UE2WM8M9</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1675,25 +1675,25 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>3171</v>
+        <v>3250</v>
       </c>
       <c r="C40" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E40" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1707,30 +1707,30 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>3162</v>
+        <v>3237</v>
       </c>
       <c r="C41" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E41" t="n">
         <v>80</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1739,25 +1739,25 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>3160</v>
+        <v>3234</v>
       </c>
       <c r="C42" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D42" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E42" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1771,25 +1771,25 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>3155</v>
+        <v>3191</v>
       </c>
       <c r="C43" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D43" t="n">
         <v>8</v>
       </c>
       <c r="E43" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1803,30 +1803,30 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>3139</v>
+        <v>3176</v>
       </c>
       <c r="C44" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E44" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1835,30 +1835,30 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>3138</v>
+        <v>3171</v>
       </c>
       <c r="C45" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D45" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E45" t="n">
         <v>77</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Camillewbl</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1867,25 +1867,25 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>3133</v>
+        <v>3160</v>
       </c>
       <c r="C46" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D46" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E46" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Erwan</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Erwan#4G91X</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -1899,25 +1899,25 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>3099</v>
+        <v>3155</v>
       </c>
       <c r="C47" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E47" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Marilena</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>GOAT#UE2WM8M9</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -1931,76 +1931,76 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>3091</v>
+        <v>3152</v>
       </c>
       <c r="C48" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D48" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E48" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>François</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Francisco93</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Ilan_260_</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>3080</v>
+        <v>3136</v>
       </c>
       <c r="C49" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E49" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Fa_One</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>3042</v>
+        <v>3114</v>
       </c>
       <c r="C50" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E50" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2023,30 +2023,30 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>3040</v>
+        <v>3106</v>
       </c>
       <c r="C51" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D51" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E51" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>romain</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>RomainLect</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2055,25 +2055,25 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>3025</v>
+        <v>3092</v>
       </c>
       <c r="C52" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D52" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E52" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>romain</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>WIL1610</t>
+          <t>RomainLect</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2087,62 +2087,58 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>3010</v>
+        <v>3091</v>
       </c>
       <c r="C53" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E53" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lison</t>
+          <t>François</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lyzone</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>3008</v>
+        <v>3082</v>
       </c>
       <c r="C54" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D54" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E54" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Lison</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>Lyzone</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2151,58 +2147,62 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>3004</v>
+        <v>3077</v>
       </c>
       <c r="C55" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D55" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E55" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>William</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fa_One</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>WIL1610</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>2980</v>
+        <v>3060</v>
       </c>
       <c r="C56" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D56" t="n">
         <v>10</v>
       </c>
       <c r="E56" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2211,30 +2211,30 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>2977</v>
+        <v>3034</v>
       </c>
       <c r="C57" t="n">
         <v>47</v>
       </c>
       <c r="D57" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E57" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
+          <t>Melissagzb</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2243,30 +2243,30 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>2976</v>
+        <v>3032</v>
       </c>
       <c r="C58" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D58" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E58" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Loïc</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Kolas</t>
+          <t>Exia95</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2275,30 +2275,30 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>2974</v>
+        <v>3029</v>
       </c>
       <c r="C59" t="n">
         <v>48</v>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E59" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>MatuRenard</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2307,30 +2307,30 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>2933</v>
+        <v>3028</v>
       </c>
       <c r="C60" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D60" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E60" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>AudreyB225</t>
+          <t>Kolas</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2339,58 +2339,62 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>2928</v>
+        <v>3005</v>
       </c>
       <c r="C61" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E61" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>AudreyB225</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>2921</v>
+        <v>3003</v>
       </c>
       <c r="C62" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D62" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E62" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cécile</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ceciledp</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2399,30 +2403,30 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>2921</v>
+        <v>2994</v>
       </c>
       <c r="C63" t="n">
         <v>46</v>
       </c>
       <c r="D63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E63" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liliane </t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>LilianeB</t>
+          <t>MxKnight</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2431,30 +2435,30 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>2902</v>
+        <v>2993</v>
       </c>
       <c r="C64" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D64" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E64" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t xml:space="preserve">Liliane </t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>LilianeB</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2463,30 +2467,30 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>2900</v>
+        <v>2984</v>
       </c>
       <c r="C65" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D65" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Loïc</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Exia95</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2495,30 +2499,30 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>2882</v>
+        <v>2980</v>
       </c>
       <c r="C66" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D66" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E66" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Priscilla</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Priscilla#4LCAF</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2527,30 +2531,30 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>2871</v>
+        <v>2973</v>
       </c>
       <c r="C67" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D67" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E67" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>Cécile</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>Ceciledp</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2559,30 +2563,30 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>2852</v>
+        <v>2934</v>
       </c>
       <c r="C68" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D68" t="n">
         <v>8</v>
       </c>
       <c r="E68" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Priscilla</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Priscilla#4LCAF</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2591,48 +2595,44 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>2842</v>
+        <v>2928</v>
       </c>
       <c r="C69" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D69" t="n">
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>MxKnight</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>compta</t>
-        </is>
-      </c>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>2836</v>
+        <v>2908</v>
       </c>
       <c r="C70" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E70" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -2655,16 +2655,16 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>2794</v>
+        <v>2846</v>
       </c>
       <c r="C71" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D71" t="n">
         <v>10</v>
       </c>
       <c r="E71" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2687,16 +2687,16 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>2789</v>
+        <v>2841</v>
       </c>
       <c r="C72" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D72" t="n">
         <v>5</v>
       </c>
       <c r="E72" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -2719,16 +2719,16 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>2781</v>
+        <v>2833</v>
       </c>
       <c r="C73" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D73" t="n">
         <v>8</v>
       </c>
       <c r="E73" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -2751,25 +2751,25 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>2768</v>
+        <v>2829</v>
       </c>
       <c r="C74" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D74" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E74" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -2783,30 +2783,30 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>2764</v>
+        <v>2820</v>
       </c>
       <c r="C75" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E75" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2815,30 +2815,30 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>2757</v>
+        <v>2785</v>
       </c>
       <c r="C76" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D76" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E76" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>Elisewiss</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2847,16 +2847,16 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>2726</v>
+        <v>2778</v>
       </c>
       <c r="C77" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D77" t="n">
         <v>6</v>
       </c>
       <c r="E77" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -2879,16 +2879,16 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>2722</v>
+        <v>2774</v>
       </c>
       <c r="C78" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D78" t="n">
         <v>6</v>
       </c>
       <c r="E78" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -2911,30 +2911,30 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>2688</v>
+        <v>2764</v>
       </c>
       <c r="C79" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D79" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E79" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Seesee</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2943,30 +2943,30 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>2687</v>
+        <v>2748</v>
       </c>
       <c r="C80" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D80" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E80" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Soraya</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Soraya-Y</t>
+          <t>dian-bgt</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2975,30 +2975,30 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>2676</v>
+        <v>2740</v>
       </c>
       <c r="C81" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D81" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E81" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Selver</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
+          <t>Seesee</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3007,30 +3007,30 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>2662</v>
+        <v>2739</v>
       </c>
       <c r="C82" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D82" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Soraya</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>Soraya-Y</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3039,30 +3039,30 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>2633</v>
+        <v>2714</v>
       </c>
       <c r="C83" t="n">
         <v>42</v>
       </c>
       <c r="D83" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E83" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Elise</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Elisewiss</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3071,16 +3071,16 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>2632</v>
+        <v>2712</v>
       </c>
       <c r="C84" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D84" t="n">
         <v>7</v>
       </c>
       <c r="E84" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -3103,16 +3103,16 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>2629</v>
+        <v>2681</v>
       </c>
       <c r="C85" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D85" t="n">
         <v>8</v>
       </c>
       <c r="E85" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3135,30 +3135,30 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>2585</v>
+        <v>2670</v>
       </c>
       <c r="C86" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D86" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E86" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t>Damien</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>PANENKANY</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3167,16 +3167,16 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>2582</v>
+        <v>2654</v>
       </c>
       <c r="C87" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D87" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E87" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -3199,30 +3199,30 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>2552</v>
+        <v>2637</v>
       </c>
       <c r="C88" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D88" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E88" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Brieuc</t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Yebri</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3231,25 +3231,25 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>2538</v>
+        <v>2622</v>
       </c>
       <c r="C89" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D89" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E89" t="n">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>Emma_Noel</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3263,30 +3263,30 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>2518</v>
+        <v>2604</v>
       </c>
       <c r="C90" t="n">
         <v>39</v>
       </c>
       <c r="D90" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E90" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Damien</t>
+          <t>Brieuc</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>PANENKANY</t>
+          <t>Yebri</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3295,16 +3295,16 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>2502</v>
+        <v>2554</v>
       </c>
       <c r="C91" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D91" t="n">
         <v>6</v>
       </c>
       <c r="E91" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -3323,16 +3323,16 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>2487</v>
+        <v>2539</v>
       </c>
       <c r="C92" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D92" t="n">
         <v>6</v>
       </c>
       <c r="E92" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -3355,25 +3355,25 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>2470</v>
+        <v>2538</v>
       </c>
       <c r="C93" t="n">
         <v>41</v>
       </c>
       <c r="D93" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E93" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Emma_Noel</t>
+          <t>chaychaychay</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3387,30 +3387,30 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>2454</v>
+        <v>2537</v>
       </c>
       <c r="C94" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D94" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E94" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ibra</t>
+          <t>Laetitia</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>PacoSarra</t>
+          <t>Laetice2020</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3419,30 +3419,30 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>2405</v>
+        <v>2506</v>
       </c>
       <c r="C95" t="n">
         <v>41</v>
       </c>
       <c r="D95" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E95" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Laetitia</t>
+          <t>Ibra</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Laetice2020</t>
+          <t>PacoSarra</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3451,16 +3451,16 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>2387</v>
+        <v>2504</v>
       </c>
       <c r="C96" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D96" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E96" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>C4M</t>
+          <t>Camss</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -3483,30 +3483,30 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>2372</v>
+        <v>2494</v>
       </c>
       <c r="C97" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D97" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E97" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Camss</t>
+          <t>YassineZ95</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3515,30 +3515,30 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>2362</v>
+        <v>2394</v>
       </c>
       <c r="C98" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D98" t="n">
         <v>6</v>
       </c>
       <c r="E98" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Léa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>LeaBrd</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3547,30 +3547,30 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>2342</v>
+        <v>2387</v>
       </c>
       <c r="C99" t="n">
         <v>39</v>
       </c>
       <c r="D99" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E99" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Léa</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>LeaBrd</t>
+          <t>C4M</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3579,16 +3579,16 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>2232</v>
+        <v>2384</v>
       </c>
       <c r="C100" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E100" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -3611,30 +3611,30 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>2212</v>
+        <v>2347</v>
       </c>
       <c r="C101" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D101" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E101" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Killian</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>KIKS999</t>
+          <t>JEVAISGAGNER10</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3643,30 +3643,30 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>2195</v>
+        <v>2298</v>
       </c>
       <c r="C102" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D102" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E102" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>JEVAISGAGNER10</t>
+          <t>Sab_M45</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3675,30 +3675,30 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>2184</v>
+        <v>2288</v>
       </c>
       <c r="C103" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D103" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E103" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Valentine___</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3707,30 +3707,30 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>2156</v>
+        <v>2264</v>
       </c>
       <c r="C104" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D104" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E104" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>Killian</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
+          <t>KIKS999</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3739,30 +3739,30 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>2146</v>
+        <v>2184</v>
       </c>
       <c r="C105" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D105" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E105" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Sab_M45</t>
+          <t>Valentine___</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3771,16 +3771,16 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>2091</v>
+        <v>2163</v>
       </c>
       <c r="C106" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D106" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E106" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -3803,16 +3803,16 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>2038</v>
+        <v>2110</v>
       </c>
       <c r="C107" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D107" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E107" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>2</v>
       </c>
       <c r="E109" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3941</v>
+        <v>4136</v>
       </c>
       <c r="C2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>3904</v>
+        <v>4099</v>
       </c>
       <c r="C3" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,16 +527,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>3878</v>
+        <v>4053</v>
       </c>
       <c r="C4" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>3867</v>
+        <v>3959</v>
       </c>
       <c r="C5" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>3784</v>
+        <v>3923</v>
       </c>
       <c r="C6" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -623,25 +623,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>3730</v>
+        <v>3916</v>
       </c>
       <c r="C7" t="n">
         <v>54</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>3721</v>
+        <v>3913</v>
       </c>
       <c r="C8" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>3721</v>
+        <v>3908</v>
       </c>
       <c r="C9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>3718</v>
+        <v>3896</v>
       </c>
       <c r="C10" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3678</v>
+        <v>3844</v>
       </c>
       <c r="C11" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -783,25 +783,25 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>3667</v>
+        <v>3843</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -815,30 +815,30 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>3635</v>
+        <v>3801</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -847,30 +847,30 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>3619</v>
+        <v>3778</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -879,30 +879,30 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>3618</v>
+        <v>3753</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Antonio Moctezuma</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>abihuts</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -911,30 +911,30 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>3613</v>
+        <v>3751</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D16" t="n">
         <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -943,30 +943,30 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>3601</v>
+        <v>3747</v>
       </c>
       <c r="C17" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -975,30 +975,30 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>3599</v>
+        <v>3746</v>
       </c>
       <c r="C18" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Panaf</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Panaff</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1007,30 +1007,30 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>3583</v>
+        <v>3737</v>
       </c>
       <c r="C19" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1039,30 +1039,30 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>3578</v>
+        <v>3733</v>
       </c>
       <c r="C20" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Antonio Moctezuma</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>abihuts</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1071,30 +1071,30 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>3551</v>
+        <v>3703</v>
       </c>
       <c r="C21" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E21" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Panaf</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Panaff</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1103,30 +1103,30 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>3542</v>
+        <v>3703</v>
       </c>
       <c r="C22" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E22" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1135,30 +1135,30 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>3528</v>
+        <v>3644</v>
       </c>
       <c r="C23" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Marion1822</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1167,30 +1167,30 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>3511</v>
+        <v>3618</v>
       </c>
       <c r="C24" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E24" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mathilde</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>MT35T</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1199,30 +1199,30 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>3460</v>
+        <v>3608</v>
       </c>
       <c r="C25" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E25" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1231,16 +1231,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>3455</v>
+        <v>3607</v>
       </c>
       <c r="C26" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1263,30 +1263,30 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>3423</v>
+        <v>3602</v>
       </c>
       <c r="C27" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E27" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Mathilde</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>MT35T</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1295,16 +1295,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>3401</v>
+        <v>3596</v>
       </c>
       <c r="C28" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E28" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1327,30 +1327,30 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>3388</v>
+        <v>3574</v>
       </c>
       <c r="C29" t="n">
         <v>54</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E29" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Devilrock95</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1359,30 +1359,30 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>3383</v>
+        <v>3563</v>
       </c>
       <c r="C30" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D30" t="n">
         <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Devilrock95</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1391,30 +1391,30 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>3329</v>
+        <v>3537</v>
       </c>
       <c r="C31" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E31" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>Romain_JO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1423,25 +1423,25 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>3288</v>
+        <v>3477</v>
       </c>
       <c r="C32" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D32" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E32" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>EmyEnzo</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1455,90 +1455,90 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>3285</v>
+        <v>3463</v>
       </c>
       <c r="C33" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E33" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>BrickXVI</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Cleem22</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>3282</v>
+        <v>3460</v>
       </c>
       <c r="C34" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E34" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Romain J</t>
+          <t>Brick</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>3282</v>
+        <v>3440</v>
       </c>
       <c r="C35" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E35" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Erwan</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>EmyEnzo</t>
+          <t>Erwan#4G91X</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1547,30 +1547,30 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>3270</v>
+        <v>3432</v>
       </c>
       <c r="C36" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E36" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Camillewbl</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1579,30 +1579,30 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>3265</v>
+        <v>3428</v>
       </c>
       <c r="C37" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D37" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E37" t="n">
         <v>82</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Erwan</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Erwan#4G91X</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1611,30 +1611,30 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>3253</v>
+        <v>3416</v>
       </c>
       <c r="C38" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D38" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E38" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1643,30 +1643,30 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>3251</v>
+        <v>3402</v>
       </c>
       <c r="C39" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D39" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E39" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Marilena</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>GOAT#UE2WM8M9</t>
+          <t>Camillewbl</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1675,30 +1675,30 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>3250</v>
+        <v>3401</v>
       </c>
       <c r="C40" t="n">
         <v>48</v>
       </c>
       <c r="D40" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E40" t="n">
         <v>82</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1707,30 +1707,30 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>3237</v>
+        <v>3385</v>
       </c>
       <c r="C41" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D41" t="n">
         <v>11</v>
       </c>
       <c r="E41" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>Marilena</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>GOAT#UE2WM8M9</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1739,30 +1739,30 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>3234</v>
+        <v>3352</v>
       </c>
       <c r="C42" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D42" t="n">
         <v>11</v>
       </c>
       <c r="E42" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1771,25 +1771,25 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>3191</v>
+        <v>3348</v>
       </c>
       <c r="C43" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D43" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E43" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1803,62 +1803,58 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>3176</v>
+        <v>3331</v>
       </c>
       <c r="C44" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D44" t="n">
         <v>9</v>
       </c>
       <c r="E44" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>Fa_One</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>3171</v>
+        <v>3329</v>
       </c>
       <c r="C45" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D45" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E45" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1867,30 +1863,30 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>3160</v>
+        <v>3305</v>
       </c>
       <c r="C46" t="n">
         <v>47</v>
       </c>
       <c r="D46" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E46" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1899,30 +1895,30 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>3155</v>
+        <v>3284</v>
       </c>
       <c r="C47" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D47" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E47" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1931,30 +1927,30 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>3152</v>
+        <v>3269</v>
       </c>
       <c r="C48" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D48" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E48" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1963,58 +1959,62 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>3136</v>
+        <v>3255</v>
       </c>
       <c r="C49" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D49" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E49" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fa_One</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Krol#4R8XC</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>3114</v>
+        <v>3255</v>
       </c>
       <c r="C50" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D50" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E50" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2023,30 +2023,30 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>3106</v>
+        <v>3249</v>
       </c>
       <c r="C51" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D51" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E51" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>MxKnight</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2055,30 +2055,30 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>3092</v>
+        <v>3248</v>
       </c>
       <c r="C52" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E52" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>romain</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>RomainLect</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2087,53 +2087,57 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>3091</v>
+        <v>3227</v>
       </c>
       <c r="C53" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D53" t="n">
         <v>7</v>
       </c>
       <c r="E53" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>Loïc</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Francisco93</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Exia95</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>3082</v>
+        <v>3208</v>
       </c>
       <c r="C54" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D54" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E54" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lison</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lyzone</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2147,25 +2151,25 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>3077</v>
+        <v>3204</v>
       </c>
       <c r="C55" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D55" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E55" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>WIL1610</t>
+          <t>MatuRenard</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2179,30 +2183,30 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>3060</v>
+        <v>3201</v>
       </c>
       <c r="C56" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E56" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2211,30 +2215,30 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>3034</v>
+        <v>3200</v>
       </c>
       <c r="C57" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D57" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E57" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>AudreyB225</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2243,30 +2247,30 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>3032</v>
+        <v>3188</v>
       </c>
       <c r="C58" t="n">
         <v>50</v>
       </c>
       <c r="D58" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E58" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Loïc</t>
+          <t xml:space="preserve">Liliane </t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Exia95</t>
+          <t>LilianeB</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2275,25 +2279,25 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>3029</v>
+        <v>3179</v>
       </c>
       <c r="C59" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D59" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E59" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>William</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
+          <t>WIL1610</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2307,30 +2311,30 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>3028</v>
+        <v>3168</v>
       </c>
       <c r="C60" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D60" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E60" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Kolas</t>
+          <t>Melissagzb</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2339,30 +2343,30 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>3005</v>
+        <v>3162</v>
       </c>
       <c r="C61" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D61" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E61" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>AudreyB225</t>
+          <t>Kolas</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2371,25 +2375,25 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>3003</v>
+        <v>3133</v>
       </c>
       <c r="C62" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D62" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E62" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>romain</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>RomainLect</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2403,57 +2407,53 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>2994</v>
+        <v>3132</v>
       </c>
       <c r="C63" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D63" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>François</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>MxKnight</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>compta</t>
-        </is>
-      </c>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>2993</v>
+        <v>3123</v>
       </c>
       <c r="C64" t="n">
         <v>47</v>
       </c>
       <c r="D64" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E64" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liliane </t>
+          <t>Lison</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>LilianeB</t>
+          <t>Lyzone</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2467,30 +2467,30 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>2984</v>
+        <v>3117</v>
       </c>
       <c r="C65" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D65" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E65" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2499,30 +2499,30 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>2980</v>
+        <v>3116</v>
       </c>
       <c r="C66" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E66" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2531,30 +2531,30 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>2973</v>
+        <v>3109</v>
       </c>
       <c r="C67" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D67" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E67" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Cécile</t>
+          <t>Priscilla</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ceciledp</t>
+          <t>Priscilla#4LCAF</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2563,30 +2563,30 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>2934</v>
+        <v>3087</v>
       </c>
       <c r="C68" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E68" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Priscilla</t>
+          <t>Cécile</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Priscilla#4LCAF</t>
+          <t>Ceciledp</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2595,90 +2595,90 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>2928</v>
+        <v>3086</v>
       </c>
       <c r="C69" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D69" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E69" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Juliie</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>Pipou931</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>2908</v>
+        <v>3062</v>
       </c>
       <c r="C70" t="n">
         <v>44</v>
       </c>
       <c r="D70" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E70" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>K_Marp</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>compta</t>
-        </is>
-      </c>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>2846</v>
+        <v>3040</v>
       </c>
       <c r="C71" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D71" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E71" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>K_Marp</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2687,25 +2687,25 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>2841</v>
+        <v>3023</v>
       </c>
       <c r="C72" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D72" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E72" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Juliie</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pipou931</t>
+          <t>dian-bgt</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -2719,30 +2719,30 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>2833</v>
+        <v>3010</v>
       </c>
       <c r="C73" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D73" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E73" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>Elisewiss</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2751,30 +2751,30 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>2829</v>
+        <v>2956</v>
       </c>
       <c r="C74" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D74" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E74" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2783,30 +2783,30 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>2820</v>
+        <v>2937</v>
       </c>
       <c r="C75" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D75" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E75" t="n">
         <v>81</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2815,30 +2815,30 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>2785</v>
+        <v>2931</v>
       </c>
       <c r="C76" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D76" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E76" t="n">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Elise</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Elisewiss</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2847,30 +2847,30 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>2778</v>
+        <v>2922</v>
       </c>
       <c r="C77" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E77" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Timy</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2879,30 +2879,30 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>2774</v>
+        <v>2916</v>
       </c>
       <c r="C78" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D78" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E78" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2911,30 +2911,30 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>2764</v>
+        <v>2909</v>
       </c>
       <c r="C79" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D79" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E79" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2943,30 +2943,30 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>2748</v>
+        <v>2896</v>
       </c>
       <c r="C80" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D80" t="n">
         <v>9</v>
       </c>
       <c r="E80" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
+          <t>Fuzo697</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2975,25 +2975,25 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>2740</v>
+        <v>2874</v>
       </c>
       <c r="C81" t="n">
         <v>41</v>
       </c>
       <c r="D81" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E81" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Seesee</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3007,30 +3007,30 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>2739</v>
+        <v>2842</v>
       </c>
       <c r="C82" t="n">
         <v>43</v>
       </c>
       <c r="D82" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E82" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Soraya</t>
+          <t>Selver</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Soraya-Y</t>
+          <t>Seesee</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3039,30 +3039,30 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>2714</v>
+        <v>2819</v>
       </c>
       <c r="C83" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D83" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E83" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>Timy</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3071,30 +3071,30 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>2712</v>
+        <v>2799</v>
       </c>
       <c r="C84" t="n">
         <v>42</v>
       </c>
       <c r="D84" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E84" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Brieuc</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fuzo697</t>
+          <t>Yebri</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3103,30 +3103,30 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>2681</v>
+        <v>2780</v>
       </c>
       <c r="C85" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D85" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t>Soraya</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>Soraya-Y</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3135,30 +3135,30 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>2670</v>
+        <v>2756</v>
       </c>
       <c r="C86" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D86" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E86" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Damien</t>
+          <t>Cindie</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>PANENKANY</t>
+          <t>Cindie_JJA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3167,48 +3167,44 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>2654</v>
+        <v>2738</v>
       </c>
       <c r="C87" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D87" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E87" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cindie</t>
+          <t>ousmane</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cindie_JJA</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>compta</t>
-        </is>
-      </c>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>2637</v>
+        <v>2730</v>
       </c>
       <c r="C88" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D88" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E88" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -3231,16 +3227,16 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>2622</v>
+        <v>2724</v>
       </c>
       <c r="C89" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D89" t="n">
         <v>9</v>
       </c>
       <c r="E89" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -3263,30 +3259,30 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>2604</v>
+        <v>2722</v>
       </c>
       <c r="C90" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D90" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E90" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Brieuc</t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Yebri</t>
+          <t>Teddbear</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3295,58 +3291,62 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>2554</v>
+        <v>2711</v>
       </c>
       <c r="C91" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D91" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E91" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ousmane</t>
+          <t>Damien</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Taylor2901</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+          <t>PANENKANY</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>2539</v>
+        <v>2671</v>
       </c>
       <c r="C92" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D92" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E92" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Laetitia</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Maruyama</t>
+          <t>Laetice2020</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3355,30 +3355,30 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>2538</v>
+        <v>2653</v>
       </c>
       <c r="C93" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D93" t="n">
         <v>6</v>
       </c>
       <c r="E93" t="n">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>Maruyama</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3387,30 +3387,30 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>2537</v>
+        <v>2639</v>
       </c>
       <c r="C94" t="n">
         <v>43</v>
       </c>
       <c r="D94" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Laetitia</t>
+          <t>lea</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Laetice2020</t>
+          <t>RBTL</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3419,16 +3419,16 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>2506</v>
+        <v>2638</v>
       </c>
       <c r="C95" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D95" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E95" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -3451,16 +3451,16 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>2504</v>
+        <v>2545</v>
       </c>
       <c r="C96" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D96" t="n">
         <v>7</v>
       </c>
       <c r="E96" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3483,25 +3483,25 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>2494</v>
+        <v>2542</v>
       </c>
       <c r="C97" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D97" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>JEVAISGAGNER10</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -3515,25 +3515,25 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>2394</v>
+        <v>2538</v>
       </c>
       <c r="C98" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D98" t="n">
         <v>6</v>
       </c>
       <c r="E98" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Léa</t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>LeaBrd</t>
+          <t>chaychaychay</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -3547,30 +3547,30 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>2387</v>
+        <v>2535</v>
       </c>
       <c r="C99" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E99" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>C4M</t>
+          <t>YassineZ95</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3579,30 +3579,30 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>2384</v>
+        <v>2493</v>
       </c>
       <c r="C100" t="n">
         <v>40</v>
       </c>
       <c r="D100" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E100" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>lea</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>RBTL</t>
+          <t>Sab_M45</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3611,30 +3611,30 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>2347</v>
+        <v>2435</v>
       </c>
       <c r="C101" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D101" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E101" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Léa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>JEVAISGAGNER10</t>
+          <t>LeaBrd</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3643,25 +3643,25 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>2298</v>
+        <v>2428</v>
       </c>
       <c r="C102" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D102" t="n">
         <v>5</v>
       </c>
       <c r="E102" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sab_M45</t>
+          <t>C4M</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -3675,30 +3675,30 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>2288</v>
+        <v>2378</v>
       </c>
       <c r="C103" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D103" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E103" t="n">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>Killian</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
+          <t>KIKS999</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3707,30 +3707,30 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>2264</v>
+        <v>2329</v>
       </c>
       <c r="C104" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D104" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E104" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Killian</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>KIKS999</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3739,30 +3739,30 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>2184</v>
+        <v>2277</v>
       </c>
       <c r="C105" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D105" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E105" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>Jérémy</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Valentine___</t>
+          <t>JeremFZ</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3771,25 +3771,25 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>2163</v>
+        <v>2274</v>
       </c>
       <c r="C106" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D106" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E106" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Jérémy</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>JeremFZ</t>
+          <t>GLR_PRIME</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -3803,30 +3803,30 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>2110</v>
+        <v>2184</v>
       </c>
       <c r="C107" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D107" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E107" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>GLR_PRIME</t>
+          <t>Valentine___</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3872,7 +3872,7 @@
         <v>2</v>
       </c>
       <c r="E109" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4136</v>
+        <v>4353</v>
       </c>
       <c r="C2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>4099</v>
+        <v>4190</v>
       </c>
       <c r="C3" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D3" t="n">
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,16 +527,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>4053</v>
+        <v>4119</v>
       </c>
       <c r="C4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>3959</v>
+        <v>4110</v>
       </c>
       <c r="C5" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>3923</v>
+        <v>4100</v>
       </c>
       <c r="C6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -623,25 +623,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>3916</v>
+        <v>4061</v>
       </c>
       <c r="C7" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>3913</v>
+        <v>4057</v>
       </c>
       <c r="C8" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>3908</v>
+        <v>4018</v>
       </c>
       <c r="C9" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>3896</v>
+        <v>4014</v>
       </c>
       <c r="C10" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3844</v>
+        <v>3999</v>
       </c>
       <c r="C11" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -783,30 +783,30 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>3843</v>
+        <v>3987</v>
       </c>
       <c r="C12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -815,25 +815,25 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>3801</v>
+        <v>3919</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -847,30 +847,30 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>3778</v>
+        <v>3878</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -879,30 +879,30 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>3753</v>
+        <v>3874</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
         <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Antonio Moctezuma</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>abihuts</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -911,30 +911,30 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>3751</v>
+        <v>3868</v>
       </c>
       <c r="C16" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E16" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -943,30 +943,30 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>3747</v>
+        <v>3844</v>
       </c>
       <c r="C17" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Antonio Moctezuma</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>abihuts</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -975,30 +975,30 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>3746</v>
+        <v>3838</v>
       </c>
       <c r="C18" t="n">
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Panaf</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Panaff</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1007,30 +1007,30 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>3737</v>
+        <v>3837</v>
       </c>
       <c r="C19" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Panaf</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>Panaff</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1039,25 +1039,25 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>3733</v>
+        <v>3819</v>
       </c>
       <c r="C20" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E20" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>3703</v>
+        <v>3794</v>
       </c>
       <c r="C21" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D21" t="n">
         <v>13</v>
       </c>
       <c r="E21" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1103,25 +1103,25 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>3703</v>
+        <v>3776</v>
       </c>
       <c r="C22" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D22" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Marion1822</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1135,16 +1135,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>3644</v>
+        <v>3735</v>
       </c>
       <c r="C23" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D23" t="n">
         <v>15</v>
       </c>
       <c r="E23" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1167,16 +1167,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>3618</v>
+        <v>3709</v>
       </c>
       <c r="C24" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D24" t="n">
         <v>9</v>
       </c>
       <c r="E24" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1199,30 +1199,30 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>3608</v>
+        <v>3704</v>
       </c>
       <c r="C25" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Devilrock95</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1231,30 +1231,30 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>3607</v>
+        <v>3699</v>
       </c>
       <c r="C26" t="n">
         <v>55</v>
       </c>
       <c r="D26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E26" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Marie__92</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1263,30 +1263,30 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>3602</v>
+        <v>3698</v>
       </c>
       <c r="C27" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E27" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mathilde</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>MT35T</t>
+          <t>Marie__92</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1295,30 +1295,30 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>3596</v>
+        <v>3693</v>
       </c>
       <c r="C28" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D28" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E28" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Mathilde</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>MT35T</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1327,30 +1327,30 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>3574</v>
+        <v>3687</v>
       </c>
       <c r="C29" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D29" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E29" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1359,25 +1359,25 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>3563</v>
+        <v>3678</v>
       </c>
       <c r="C30" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E30" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Devilrock95</t>
+          <t>Romain_JO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1391,30 +1391,30 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>3537</v>
+        <v>3665</v>
       </c>
       <c r="C31" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E31" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Romain J</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1423,30 +1423,30 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>3477</v>
+        <v>3602</v>
       </c>
       <c r="C32" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D32" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E32" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Marilena</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>EmyEnzo</t>
+          <t>GOAT#UE2WM8M9</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1455,30 +1455,30 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>3463</v>
+        <v>3581</v>
       </c>
       <c r="C33" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D33" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>Erwan</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>Erwan#4G91X</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1487,58 +1487,62 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>3460</v>
+        <v>3569</v>
       </c>
       <c r="C34" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E34" t="n">
         <v>85</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>BrickXVI</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>A-MOE</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>3440</v>
+        <v>3554</v>
       </c>
       <c r="C35" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E35" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Erwan</t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Erwan#4G91X</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1547,62 +1551,58 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>3432</v>
+        <v>3551</v>
       </c>
       <c r="C36" t="n">
         <v>52</v>
       </c>
       <c r="D36" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E36" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>Brick</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Liliuus</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>3428</v>
+        <v>3543</v>
       </c>
       <c r="C37" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E37" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>EmyEnzo</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1611,30 +1611,30 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>3416</v>
+        <v>3523</v>
       </c>
       <c r="C38" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D38" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E38" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1643,30 +1643,30 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>3402</v>
+        <v>3507</v>
       </c>
       <c r="C39" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E39" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Camillewbl</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1675,25 +1675,25 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>3401</v>
+        <v>3493</v>
       </c>
       <c r="C40" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E40" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>Camillewbl</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1707,30 +1707,30 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>3385</v>
+        <v>3472</v>
       </c>
       <c r="C41" t="n">
         <v>50</v>
       </c>
       <c r="D41" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E41" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Marilena</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>GOAT#UE2WM8M9</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1739,25 +1739,25 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>3352</v>
+        <v>3446</v>
       </c>
       <c r="C42" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E42" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1771,30 +1771,30 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>3348</v>
+        <v>3445</v>
       </c>
       <c r="C43" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D43" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E43" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1803,58 +1803,62 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>3331</v>
+        <v>3443</v>
       </c>
       <c r="C44" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D44" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E44" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fa_One</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Davido#4BZ54</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>3329</v>
+        <v>3439</v>
       </c>
       <c r="C45" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D45" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E45" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1863,30 +1867,30 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>3305</v>
+        <v>3401</v>
       </c>
       <c r="C46" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D46" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E46" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1895,30 +1899,30 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>3284</v>
+        <v>3396</v>
       </c>
       <c r="C47" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E47" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>William</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>WIL1610</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1927,30 +1931,30 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>3269</v>
+        <v>3385</v>
       </c>
       <c r="C48" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E48" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
+          <t>Melissagzb</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1959,30 +1963,30 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>3255</v>
+        <v>3360</v>
       </c>
       <c r="C49" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D49" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E49" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1991,48 +1995,44 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>3255</v>
+        <v>3356</v>
       </c>
       <c r="C50" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D50" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E50" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Reste du monde</t>
-        </is>
-      </c>
+          <t>Fa_One</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>3249</v>
+        <v>3340</v>
       </c>
       <c r="C51" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D51" t="n">
         <v>13</v>
       </c>
       <c r="E51" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2055,30 +2055,30 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>3248</v>
+        <v>3321</v>
       </c>
       <c r="C52" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D52" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E52" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2087,16 +2087,16 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>3227</v>
+        <v>3318</v>
       </c>
       <c r="C53" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D53" t="n">
         <v>7</v>
       </c>
       <c r="E53" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2119,25 +2119,25 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>3208</v>
+        <v>3309</v>
       </c>
       <c r="C54" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D54" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E54" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2151,16 +2151,16 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>3204</v>
+        <v>3295</v>
       </c>
       <c r="C55" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D55" t="n">
         <v>9</v>
       </c>
       <c r="E55" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2183,16 +2183,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>3201</v>
+        <v>3292</v>
       </c>
       <c r="C56" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D56" t="n">
         <v>9</v>
       </c>
       <c r="E56" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2215,30 +2215,30 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>3200</v>
+        <v>3279</v>
       </c>
       <c r="C57" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E57" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t xml:space="preserve">Liliane </t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>AudreyB225</t>
+          <t>LilianeB</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2247,25 +2247,25 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>3188</v>
+        <v>3248</v>
       </c>
       <c r="C58" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D58" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E58" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liliane </t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>LilianeB</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2279,30 +2279,30 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>3179</v>
+        <v>3233</v>
       </c>
       <c r="C59" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D59" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E59" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>WIL1610</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2311,30 +2311,30 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>3168</v>
+        <v>3225</v>
       </c>
       <c r="C60" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D60" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E60" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>AudreyB225</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2343,30 +2343,30 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>3162</v>
+        <v>3214</v>
       </c>
       <c r="C61" t="n">
         <v>49</v>
       </c>
       <c r="D61" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E61" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Lison</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Kolas</t>
+          <t>Lyzone</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2375,30 +2375,30 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>3133</v>
+        <v>3200</v>
       </c>
       <c r="C62" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E62" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>romain</t>
+          <t>Priscilla</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>RomainLect</t>
+          <t>Priscilla#4LCAF</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2407,58 +2407,62 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>3132</v>
+        <v>3199</v>
       </c>
       <c r="C63" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D63" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E63" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>François</t>
+          <t>romain</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Francisco93</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>RomainLect</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>3123</v>
+        <v>3187</v>
       </c>
       <c r="C64" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D64" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E64" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lison</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lyzone</t>
+          <t>Kolas</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2467,30 +2471,30 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>3117</v>
+        <v>3178</v>
       </c>
       <c r="C65" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D65" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E65" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>Cécile</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>Ceciledp</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2499,30 +2503,30 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>3116</v>
+        <v>3177</v>
       </c>
       <c r="C66" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D66" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E66" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Juliie</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Pipou931</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2531,30 +2535,30 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>3109</v>
+        <v>3173</v>
       </c>
       <c r="C67" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D67" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Priscilla</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Priscilla#4LCAF</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2563,62 +2567,58 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>3087</v>
+        <v>3157</v>
       </c>
       <c r="C68" t="n">
         <v>50</v>
       </c>
       <c r="D68" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E68" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Cécile</t>
+          <t>François</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ceciledp</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Francisco93</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>3086</v>
+        <v>3141</v>
       </c>
       <c r="C69" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D69" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E69" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Juliie</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pipou931</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2627,90 +2627,90 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>3062</v>
+        <v>3131</v>
       </c>
       <c r="C70" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D70" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E70" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>K_Marp</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>3040</v>
+        <v>3128</v>
       </c>
       <c r="C71" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D71" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E71" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>K_Marp</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>compta</t>
-        </is>
-      </c>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>3023</v>
+        <v>3117</v>
       </c>
       <c r="C72" t="n">
         <v>48</v>
       </c>
       <c r="D72" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E72" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2719,30 +2719,30 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>3010</v>
+        <v>3114</v>
       </c>
       <c r="C73" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D73" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E73" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Elise</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Elisewiss</t>
+          <t>dian-bgt</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2751,25 +2751,25 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>2956</v>
+        <v>3101</v>
       </c>
       <c r="C74" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D74" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E74" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>Elisewiss</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -2783,16 +2783,16 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>2937</v>
+        <v>3088</v>
       </c>
       <c r="C75" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D75" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E75" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -2815,16 +2815,16 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>2931</v>
+        <v>3082</v>
       </c>
       <c r="C76" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D76" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E76" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -2847,16 +2847,16 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>2922</v>
+        <v>3013</v>
       </c>
       <c r="C77" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D77" t="n">
         <v>5</v>
       </c>
       <c r="E77" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -2879,30 +2879,30 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>2916</v>
+        <v>3000</v>
       </c>
       <c r="C78" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D78" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E78" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2911,30 +2911,30 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>2909</v>
+        <v>2987</v>
       </c>
       <c r="C79" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D79" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E79" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>Fuzo697</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -2943,30 +2943,30 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>2896</v>
+        <v>2965</v>
       </c>
       <c r="C80" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D80" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E80" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuzo697</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2975,30 +2975,30 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>2874</v>
+        <v>2941</v>
       </c>
       <c r="C81" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D81" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E81" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3007,30 +3007,30 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>2842</v>
+        <v>2935</v>
       </c>
       <c r="C82" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D82" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E82" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Seesee</t>
+          <t>Timy</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3039,30 +3039,30 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>2819</v>
+        <v>2928</v>
       </c>
       <c r="C83" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D83" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E83" t="n">
         <v>83</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Damien</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Timy</t>
+          <t>PANENKANY</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3071,30 +3071,30 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>2799</v>
+        <v>2873</v>
       </c>
       <c r="C84" t="n">
         <v>42</v>
       </c>
       <c r="D84" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E84" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Brieuc</t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Yebri</t>
+          <t>Teddbear</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3103,16 +3103,16 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>2780</v>
+        <v>2871</v>
       </c>
       <c r="C85" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D85" t="n">
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3135,30 +3135,30 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>2756</v>
+        <v>2867</v>
       </c>
       <c r="C86" t="n">
         <v>44</v>
       </c>
       <c r="D86" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E86" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cindie</t>
+          <t>Selver</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cindie_JJA</t>
+          <t>Seesee</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3167,58 +3167,62 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>2738</v>
+        <v>2865</v>
       </c>
       <c r="C87" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D87" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E87" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ousmane</t>
+          <t>Brieuc</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Taylor2901</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>Yebri</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>2730</v>
+        <v>2847</v>
       </c>
       <c r="C88" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D88" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E88" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t>Cindie</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>Cindie_JJA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3227,30 +3231,30 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>2724</v>
+        <v>2822</v>
       </c>
       <c r="C89" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D89" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E89" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Laetitia</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Emma_Noel</t>
+          <t>Laetice2020</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3259,30 +3263,30 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>2722</v>
+        <v>2821</v>
       </c>
       <c r="C90" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D90" t="n">
         <v>8</v>
       </c>
       <c r="E90" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3291,62 +3295,58 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>2711</v>
+        <v>2804</v>
       </c>
       <c r="C91" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D91" t="n">
         <v>8</v>
       </c>
       <c r="E91" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Damien</t>
+          <t>ousmane</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>PANENKANY</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>2671</v>
+        <v>2804</v>
       </c>
       <c r="C92" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D92" t="n">
         <v>7</v>
       </c>
       <c r="E92" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Laetitia</t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Laetice2020</t>
+          <t>Maruyama</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3355,30 +3355,30 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>2653</v>
+        <v>2787</v>
       </c>
       <c r="C93" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D93" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E93" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Maruyama</t>
+          <t>Camss</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3387,16 +3387,16 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>2639</v>
+        <v>2780</v>
       </c>
       <c r="C94" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D94" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E94" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -3419,30 +3419,30 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>2638</v>
+        <v>2749</v>
       </c>
       <c r="C95" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D95" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E95" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ibra</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>PacoSarra</t>
+          <t>Emma_Noel</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3451,30 +3451,30 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>2545</v>
+        <v>2663</v>
       </c>
       <c r="C96" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D96" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E96" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Ibra</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Camss</t>
+          <t>PacoSarra</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3483,16 +3483,16 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>2542</v>
+        <v>2633</v>
       </c>
       <c r="C97" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D97" t="n">
         <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -3515,30 +3515,30 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>2538</v>
+        <v>2560</v>
       </c>
       <c r="C98" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D98" t="n">
         <v>6</v>
       </c>
       <c r="E98" t="n">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>YassineZ95</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3547,30 +3547,30 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>2535</v>
+        <v>2538</v>
       </c>
       <c r="C99" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D99" t="n">
         <v>6</v>
       </c>
       <c r="E99" t="n">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>chaychaychay</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3579,30 +3579,30 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>2493</v>
+        <v>2526</v>
       </c>
       <c r="C100" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D100" t="n">
         <v>6</v>
       </c>
       <c r="E100" t="n">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Léa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sab_M45</t>
+          <t>LeaBrd</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3611,30 +3611,30 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>2435</v>
+        <v>2519</v>
       </c>
       <c r="C101" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D101" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E101" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Léa</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>LeaBrd</t>
+          <t>C4M</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3643,25 +3643,25 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>2428</v>
+        <v>2493</v>
       </c>
       <c r="C102" t="n">
         <v>40</v>
       </c>
       <c r="D102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E102" t="n">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>C4M</t>
+          <t>Sab_M45</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -3675,16 +3675,16 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>2378</v>
+        <v>2469</v>
       </c>
       <c r="C103" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D103" t="n">
         <v>3</v>
       </c>
       <c r="E103" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -3707,30 +3707,30 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>2329</v>
+        <v>2376</v>
       </c>
       <c r="C104" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D104" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E104" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
+          <t>Valentine___</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3739,16 +3739,16 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>2277</v>
+        <v>2368</v>
       </c>
       <c r="C105" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D105" t="n">
         <v>5</v>
       </c>
       <c r="E105" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -3771,16 +3771,16 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>2274</v>
+        <v>2365</v>
       </c>
       <c r="C106" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D106" t="n">
         <v>9</v>
       </c>
       <c r="E106" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -3803,30 +3803,30 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>2184</v>
+        <v>2354</v>
       </c>
       <c r="C107" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D107" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E107" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Valentine___</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3863,16 +3863,16 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>1021</v>
+        <v>1147</v>
       </c>
       <c r="C109" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E109" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4353</v>
+        <v>4449</v>
       </c>
       <c r="C2" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>4190</v>
+        <v>4286</v>
       </c>
       <c r="C3" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D3" t="n">
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,16 +527,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>4119</v>
+        <v>4285</v>
       </c>
       <c r="C4" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -559,16 +559,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>4110</v>
+        <v>4206</v>
       </c>
       <c r="C5" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -591,16 +591,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>4100</v>
+        <v>4196</v>
       </c>
       <c r="C6" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -623,16 +623,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>4061</v>
+        <v>4157</v>
       </c>
       <c r="C7" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D7" t="n">
         <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -655,16 +655,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>4057</v>
+        <v>4153</v>
       </c>
       <c r="C8" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -687,16 +687,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>4018</v>
+        <v>4114</v>
       </c>
       <c r="C9" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D9" t="n">
         <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -719,16 +719,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>4014</v>
+        <v>4110</v>
       </c>
       <c r="C10" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -751,16 +751,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3999</v>
+        <v>4095</v>
       </c>
       <c r="C11" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -783,16 +783,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>3987</v>
+        <v>4083</v>
       </c>
       <c r="C12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D12" t="n">
         <v>15</v>
       </c>
       <c r="E12" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -815,16 +815,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>3919</v>
+        <v>4015</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -847,16 +847,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>3878</v>
+        <v>3974</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -879,30 +879,30 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>3874</v>
+        <v>3964</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -911,30 +911,30 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>3868</v>
+        <v>3942</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -943,16 +943,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>3844</v>
+        <v>3940</v>
       </c>
       <c r="C17" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -975,16 +975,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>3838</v>
+        <v>3934</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
         <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1007,16 +1007,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>3837</v>
+        <v>3933</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1039,16 +1039,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>3819</v>
+        <v>3915</v>
       </c>
       <c r="C20" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D20" t="n">
         <v>14</v>
       </c>
       <c r="E20" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1071,16 +1071,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>3794</v>
+        <v>3890</v>
       </c>
       <c r="C21" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D21" t="n">
         <v>13</v>
       </c>
       <c r="E21" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1103,16 +1103,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>3776</v>
+        <v>3872</v>
       </c>
       <c r="C22" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D22" t="n">
         <v>11</v>
       </c>
       <c r="E22" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>3735</v>
+        <v>3831</v>
       </c>
       <c r="C23" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D23" t="n">
         <v>15</v>
       </c>
       <c r="E23" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1167,16 +1167,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>3709</v>
+        <v>3805</v>
       </c>
       <c r="C24" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D24" t="n">
         <v>9</v>
       </c>
       <c r="E24" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1199,16 +1199,16 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>3704</v>
+        <v>3800</v>
       </c>
       <c r="C25" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D25" t="n">
         <v>10</v>
       </c>
       <c r="E25" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1231,30 +1231,30 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>3699</v>
+        <v>3794</v>
       </c>
       <c r="C26" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Marie__92</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1263,30 +1263,30 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>3698</v>
+        <v>3789</v>
       </c>
       <c r="C27" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E27" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Mathilde</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Marie__92</t>
+          <t>MT35T</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1295,30 +1295,30 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>3693</v>
+        <v>3783</v>
       </c>
       <c r="C28" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D28" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E28" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mathilde</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MT35T</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1327,30 +1327,30 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>3687</v>
+        <v>3774</v>
       </c>
       <c r="C29" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D29" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E29" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>Romain_JO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1359,30 +1359,30 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>3678</v>
+        <v>3761</v>
       </c>
       <c r="C30" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D30" t="n">
         <v>12</v>
       </c>
       <c r="E30" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Romain J</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1391,30 +1391,30 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>3665</v>
+        <v>3727</v>
       </c>
       <c r="C31" t="n">
         <v>56</v>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E31" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1423,16 +1423,16 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>3602</v>
+        <v>3698</v>
       </c>
       <c r="C32" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D32" t="n">
         <v>12</v>
       </c>
       <c r="E32" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1455,16 +1455,16 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>3581</v>
+        <v>3677</v>
       </c>
       <c r="C33" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D33" t="n">
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1487,16 +1487,16 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>3569</v>
+        <v>3665</v>
       </c>
       <c r="C34" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D34" t="n">
         <v>14</v>
       </c>
       <c r="E34" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1519,16 +1519,16 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>3554</v>
+        <v>3650</v>
       </c>
       <c r="C35" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D35" t="n">
         <v>11</v>
       </c>
       <c r="E35" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1551,16 +1551,16 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>3551</v>
+        <v>3647</v>
       </c>
       <c r="C36" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D36" t="n">
         <v>10</v>
       </c>
       <c r="E36" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1579,16 +1579,16 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>3543</v>
+        <v>3639</v>
       </c>
       <c r="C37" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D37" t="n">
         <v>9</v>
       </c>
       <c r="E37" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1611,16 +1611,16 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>3523</v>
+        <v>3619</v>
       </c>
       <c r="C38" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D38" t="n">
         <v>12</v>
       </c>
       <c r="E38" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1643,16 +1643,16 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>3507</v>
+        <v>3603</v>
       </c>
       <c r="C39" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D39" t="n">
         <v>10</v>
       </c>
       <c r="E39" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1675,16 +1675,16 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>3493</v>
+        <v>3589</v>
       </c>
       <c r="C40" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D40" t="n">
         <v>7</v>
       </c>
       <c r="E40" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1707,30 +1707,30 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>3472</v>
+        <v>3541</v>
       </c>
       <c r="C41" t="n">
         <v>50</v>
       </c>
       <c r="D41" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E41" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1739,25 +1739,25 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>3446</v>
+        <v>3500</v>
       </c>
       <c r="C42" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E42" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1771,25 +1771,25 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>3445</v>
+        <v>3497</v>
       </c>
       <c r="C43" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E43" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1803,30 +1803,30 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>3443</v>
+        <v>3492</v>
       </c>
       <c r="C44" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D44" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E44" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>William</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>WIL1610</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1835,30 +1835,30 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>3439</v>
+        <v>3481</v>
       </c>
       <c r="C45" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D45" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E45" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>Melissagzb</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1867,30 +1867,30 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>3401</v>
+        <v>3474</v>
       </c>
       <c r="C46" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D46" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E46" t="n">
         <v>85</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1899,30 +1899,30 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>3396</v>
+        <v>3467</v>
       </c>
       <c r="C47" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D47" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E47" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>WIL1610</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1931,30 +1931,30 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>3385</v>
+        <v>3456</v>
       </c>
       <c r="C48" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D48" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E48" t="n">
         <v>88</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1963,76 +1963,76 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>3360</v>
+        <v>3452</v>
       </c>
       <c r="C49" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E49" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>Fa_One</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>3356</v>
+        <v>3443</v>
       </c>
       <c r="C50" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D50" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E50" t="n">
         <v>88</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fa_One</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>Davido#4BZ54</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>3340</v>
+        <v>3436</v>
       </c>
       <c r="C51" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D51" t="n">
         <v>13</v>
       </c>
       <c r="E51" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2055,16 +2055,16 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>3321</v>
+        <v>3417</v>
       </c>
       <c r="C52" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D52" t="n">
         <v>11</v>
       </c>
       <c r="E52" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2087,30 +2087,30 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>3318</v>
+        <v>3405</v>
       </c>
       <c r="C53" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D53" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E53" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Loïc</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Exia95</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2119,30 +2119,30 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>3309</v>
+        <v>3391</v>
       </c>
       <c r="C54" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D54" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E54" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>MatuRenard</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2151,30 +2151,30 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>3295</v>
+        <v>3388</v>
       </c>
       <c r="C55" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D55" t="n">
         <v>9</v>
       </c>
       <c r="E55" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2183,30 +2183,30 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>3292</v>
+        <v>3386</v>
       </c>
       <c r="C56" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D56" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E56" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Loïc</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>Exia95</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2215,16 +2215,16 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>3279</v>
+        <v>3375</v>
       </c>
       <c r="C57" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D57" t="n">
         <v>11</v>
       </c>
       <c r="E57" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2247,25 +2247,25 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>3248</v>
+        <v>3329</v>
       </c>
       <c r="C58" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="D58" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E58" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2279,30 +2279,30 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>3233</v>
+        <v>3321</v>
       </c>
       <c r="C59" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E59" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>AudreyB225</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2311,30 +2311,30 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>3225</v>
+        <v>3316</v>
       </c>
       <c r="C60" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D60" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E60" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>AudreyB225</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2343,16 +2343,16 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>3214</v>
+        <v>3310</v>
       </c>
       <c r="C61" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D61" t="n">
         <v>7</v>
       </c>
       <c r="E61" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2375,16 +2375,16 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>3200</v>
+        <v>3296</v>
       </c>
       <c r="C62" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D62" t="n">
         <v>8</v>
       </c>
       <c r="E62" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>3199</v>
+        <v>3295</v>
       </c>
       <c r="C63" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D63" t="n">
         <v>9</v>
       </c>
       <c r="E63" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -2439,16 +2439,16 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>3187</v>
+        <v>3283</v>
       </c>
       <c r="C64" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D64" t="n">
         <v>11</v>
       </c>
       <c r="E64" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2471,16 +2471,16 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>3178</v>
+        <v>3274</v>
       </c>
       <c r="C65" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D65" t="n">
         <v>5</v>
       </c>
       <c r="E65" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2503,16 +2503,16 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>3177</v>
+        <v>3273</v>
       </c>
       <c r="C66" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D66" t="n">
         <v>7</v>
       </c>
       <c r="E66" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2535,16 +2535,16 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>3173</v>
+        <v>3269</v>
       </c>
       <c r="C67" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D67" t="n">
         <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2567,16 +2567,16 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>3157</v>
+        <v>3253</v>
       </c>
       <c r="C68" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D68" t="n">
         <v>7</v>
       </c>
       <c r="E68" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2595,16 +2595,16 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>3141</v>
+        <v>3237</v>
       </c>
       <c r="C69" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D69" t="n">
         <v>9</v>
       </c>
       <c r="E69" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2627,16 +2627,16 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>3131</v>
+        <v>3227</v>
       </c>
       <c r="C70" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D70" t="n">
         <v>7</v>
       </c>
       <c r="E70" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -2659,58 +2659,62 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>3128</v>
+        <v>3210</v>
       </c>
       <c r="C71" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D71" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E71" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>dian-bgt</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>3117</v>
+        <v>3197</v>
       </c>
       <c r="C72" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D72" t="n">
         <v>7</v>
       </c>
       <c r="E72" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>Elisewiss</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -2719,39 +2723,35 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>3114</v>
+        <v>3196</v>
       </c>
       <c r="C73" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D73" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E73" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Julie_Romao</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>3101</v>
+        <v>3185</v>
       </c>
       <c r="C74" t="n">
         <v>49</v>
@@ -2760,21 +2760,21 @@
         <v>7</v>
       </c>
       <c r="E74" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Elise</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Elisewiss</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2783,16 +2783,16 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>3088</v>
+        <v>3184</v>
       </c>
       <c r="C75" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D75" t="n">
         <v>12</v>
       </c>
       <c r="E75" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -2815,25 +2815,25 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>3082</v>
+        <v>3109</v>
       </c>
       <c r="C76" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E76" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -2847,30 +2847,30 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>3013</v>
+        <v>3101</v>
       </c>
       <c r="C77" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D77" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E77" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>Timy</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2879,16 +2879,16 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>3000</v>
+        <v>3096</v>
       </c>
       <c r="C78" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D78" t="n">
         <v>12</v>
       </c>
       <c r="E78" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -2911,30 +2911,30 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>2987</v>
+        <v>3082</v>
       </c>
       <c r="C79" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D79" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E79" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fuzo697</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -2943,16 +2943,16 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>2965</v>
+        <v>3061</v>
       </c>
       <c r="C80" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D80" t="n">
         <v>8</v>
       </c>
       <c r="E80" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -2975,16 +2975,16 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>2941</v>
+        <v>3037</v>
       </c>
       <c r="C81" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D81" t="n">
         <v>7</v>
       </c>
       <c r="E81" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3007,30 +3007,30 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>2935</v>
+        <v>2987</v>
       </c>
       <c r="C82" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E82" t="n">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Timy</t>
+          <t>Fuzo697</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3039,30 +3039,30 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>2928</v>
+        <v>2967</v>
       </c>
       <c r="C83" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D83" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E83" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Damien</t>
+          <t>Soraya</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>PANENKANY</t>
+          <t>Soraya-Y</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3071,30 +3071,30 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>2873</v>
+        <v>2963</v>
       </c>
       <c r="C84" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D84" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E84" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t>Selver</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>Seesee</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3103,30 +3103,30 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>2871</v>
+        <v>2956</v>
       </c>
       <c r="C85" t="n">
         <v>46</v>
       </c>
       <c r="D85" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E85" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Soraya</t>
+          <t>Damien</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Soraya-Y</t>
+          <t>PANENKANY</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3135,30 +3135,30 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>2867</v>
+        <v>2943</v>
       </c>
       <c r="C86" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D86" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E86" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t>Cindie</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Seesee</t>
+          <t>Cindie_JJA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -3167,30 +3167,30 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>2865</v>
+        <v>2941</v>
       </c>
       <c r="C87" t="n">
         <v>43</v>
       </c>
       <c r="D87" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E87" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Brieuc</t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Yebri</t>
+          <t>Teddbear</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3199,30 +3199,30 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>2847</v>
+        <v>2918</v>
       </c>
       <c r="C88" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D88" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E88" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cindie</t>
+          <t>Laetitia</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cindie_JJA</t>
+          <t>Laetice2020</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3231,30 +3231,30 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>2822</v>
+        <v>2917</v>
       </c>
       <c r="C89" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D89" t="n">
         <v>8</v>
       </c>
       <c r="E89" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Laetitia</t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Laetice2020</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3263,25 +3263,25 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>2821</v>
+        <v>2900</v>
       </c>
       <c r="C90" t="n">
         <v>46</v>
       </c>
       <c r="D90" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E90" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>Maruyama</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3295,58 +3295,62 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>2804</v>
+        <v>2893</v>
       </c>
       <c r="C91" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D91" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E91" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ousmane</t>
+          <t>Brieuc</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Taylor2901</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+          <t>Yebri</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>2804</v>
+        <v>2883</v>
       </c>
       <c r="C92" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D92" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E92" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Maruyama</t>
+          <t>Camss</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3355,30 +3359,30 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>2787</v>
+        <v>2876</v>
       </c>
       <c r="C93" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D93" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E93" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>lea</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Camss</t>
+          <t>RBTL</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3387,25 +3391,25 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>2780</v>
+        <v>2845</v>
       </c>
       <c r="C94" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D94" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E94" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>lea</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>RBTL</t>
+          <t>Emma_Noel</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -3419,62 +3423,58 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>2749</v>
+        <v>2832</v>
       </c>
       <c r="C95" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D95" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E95" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>ousmane</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Emma_Noel</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>Taylor2901</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>2663</v>
+        <v>2799</v>
       </c>
       <c r="C96" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D96" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E96" t="n">
         <v>88</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ibra</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>PacoSarra</t>
+          <t>JEVAISGAGNER10</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -3483,25 +3483,25 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>2633</v>
+        <v>2698</v>
       </c>
       <c r="C97" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D97" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E97" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>JEVAISGAGNER10</t>
+          <t>YassineZ95</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -3515,30 +3515,30 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>2560</v>
+        <v>2691</v>
       </c>
       <c r="C98" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D98" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E98" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Ibra</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>PacoSarra</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3547,25 +3547,25 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>2538</v>
+        <v>2622</v>
       </c>
       <c r="C99" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D99" t="n">
         <v>6</v>
       </c>
       <c r="E99" t="n">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>Léa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>LeaBrd</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -3579,30 +3579,30 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>2526</v>
+        <v>2615</v>
       </c>
       <c r="C100" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D100" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E100" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Léa</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>LeaBrd</t>
+          <t>C4M</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3611,30 +3611,30 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>2519</v>
+        <v>2538</v>
       </c>
       <c r="C101" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E101" t="n">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>C4M</t>
+          <t>chaychaychay</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3643,25 +3643,25 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>2493</v>
+        <v>2531</v>
       </c>
       <c r="C102" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D102" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E102" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sab_M45</t>
+          <t>GLR_PRIME</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -3675,30 +3675,30 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>2469</v>
+        <v>2521</v>
       </c>
       <c r="C103" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D103" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E103" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Killian</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>KIKS999</t>
+          <t>Sab_M45</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -3707,25 +3707,25 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>2376</v>
+        <v>2497</v>
       </c>
       <c r="C104" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D104" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E104" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>Killian</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Valentine___</t>
+          <t>KIKS999</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -3739,30 +3739,30 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>2368</v>
+        <v>2450</v>
       </c>
       <c r="C105" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D105" t="n">
         <v>5</v>
       </c>
       <c r="E105" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Jérémy</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>JeremFZ</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -3771,25 +3771,25 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>2365</v>
+        <v>2436</v>
       </c>
       <c r="C106" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D106" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E106" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Jérémy</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>GLR_PRIME</t>
+          <t>JeremFZ</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -3803,30 +3803,30 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>2354</v>
+        <v>2404</v>
       </c>
       <c r="C107" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E107" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
+          <t>Valentine___</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -3863,16 +3863,16 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>1147</v>
+        <v>1215</v>
       </c>
       <c r="C109" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D109" t="n">
         <v>3</v>
       </c>
       <c r="E109" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>

--- a/classement_individuel.xlsx
+++ b/classement_individuel.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4449</v>
+        <v>4542</v>
       </c>
       <c r="C2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>4286</v>
+        <v>4379</v>
       </c>
       <c r="C3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D3" t="n">
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>4285</v>
+        <v>4289</v>
       </c>
       <c r="C4" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>4206</v>
+        <v>4285</v>
       </c>
       <c r="C5" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -591,25 +591,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>4196</v>
+        <v>4250</v>
       </c>
       <c r="C6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
         <v>90</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -623,25 +623,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>4157</v>
+        <v>4246</v>
       </c>
       <c r="C7" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>4153</v>
+        <v>4206</v>
       </c>
       <c r="C8" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>4114</v>
+        <v>4203</v>
       </c>
       <c r="C9" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>4110</v>
+        <v>4176</v>
       </c>
       <c r="C10" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>4095</v>
+        <v>4114</v>
       </c>
       <c r="C11" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -783,30 +783,30 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>4083</v>
+        <v>4095</v>
       </c>
       <c r="C12" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -815,30 +815,30 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>4015</v>
+        <v>4065</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -847,30 +847,30 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>3974</v>
+        <v>4026</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Panaf</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>Panaff</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -879,25 +879,25 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>3964</v>
+        <v>4015</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -911,30 +911,30 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>3942</v>
+        <v>3974</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -943,30 +943,30 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>3940</v>
+        <v>3964</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E17" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Antonio Moctezuma</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>abihuts</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -975,30 +975,30 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>3934</v>
+        <v>3942</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1007,30 +1007,30 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>3933</v>
+        <v>3940</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Panaf</t>
+          <t>Antonio Moctezuma</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Panaff</t>
+          <t>abihuts</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1039,30 +1039,30 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>3915</v>
+        <v>3934</v>
       </c>
       <c r="C20" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E20" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Marion1822</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1071,30 +1071,30 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>3890</v>
+        <v>3898</v>
       </c>
       <c r="C21" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D21" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1103,30 +1103,30 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>3872</v>
+        <v>3893</v>
       </c>
       <c r="C22" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Devilrock95</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1135,25 +1135,25 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>3831</v>
+        <v>3890</v>
       </c>
       <c r="C23" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D23" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E23" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1167,30 +1167,30 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>3805</v>
+        <v>3872</v>
       </c>
       <c r="C24" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E24" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1199,25 +1199,25 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>3800</v>
+        <v>3867</v>
       </c>
       <c r="C25" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E25" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Devilrock95</t>
+          <t>Romain_JO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1231,30 +1231,30 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>3794</v>
+        <v>3854</v>
       </c>
       <c r="C26" t="n">
         <v>59</v>
       </c>
       <c r="D26" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E26" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Marie__92</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1263,30 +1263,30 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>3789</v>
+        <v>3831</v>
       </c>
       <c r="C27" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D27" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E27" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mathilde</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>MT35T</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1295,30 +1295,30 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>3783</v>
+        <v>3827</v>
       </c>
       <c r="C28" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D28" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E28" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Erwan</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>Erwan#4G91X</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1327,30 +1327,30 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>3774</v>
+        <v>3820</v>
       </c>
       <c r="C29" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E29" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Romain J</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1359,30 +1359,30 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>3761</v>
+        <v>3800</v>
       </c>
       <c r="C30" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D30" t="n">
         <v>12</v>
       </c>
       <c r="E30" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1391,62 +1391,58 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>3727</v>
+        <v>3797</v>
       </c>
       <c r="C31" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D31" t="n">
         <v>11</v>
       </c>
       <c r="E31" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Brick</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Reste du monde</t>
-        </is>
-      </c>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>3698</v>
+        <v>3794</v>
       </c>
       <c r="C32" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D32" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E32" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Marilena</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>GOAT#UE2WM8M9</t>
+          <t>Marie__92</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1455,30 +1451,30 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>3677</v>
+        <v>3789</v>
       </c>
       <c r="C33" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E33" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Erwan</t>
+          <t>Mathilde</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Erwan#4G91X</t>
+          <t>MT35T</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -1487,25 +1483,25 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>3665</v>
+        <v>3783</v>
       </c>
       <c r="C34" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D34" t="n">
         <v>14</v>
       </c>
       <c r="E34" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1519,30 +1515,30 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>3650</v>
+        <v>3732</v>
       </c>
       <c r="C35" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D35" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E35" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>EmyEnzo</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1551,58 +1547,62 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>3647</v>
+        <v>3712</v>
       </c>
       <c r="C36" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E36" t="n">
         <v>90</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>BrickXVI</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Liliuus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>3639</v>
+        <v>3698</v>
       </c>
       <c r="C37" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E37" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Marilena</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>EmyEnzo</t>
+          <t>GOAT#UE2WM8M9</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1611,30 +1611,30 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>3619</v>
+        <v>3696</v>
       </c>
       <c r="C38" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D38" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E38" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1643,62 +1643,58 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>3603</v>
+        <v>3695</v>
       </c>
       <c r="C39" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D39" t="n">
         <v>10</v>
       </c>
       <c r="E39" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>Fa_One</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>3589</v>
+        <v>3665</v>
       </c>
       <c r="C40" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D40" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E40" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Camillewbl</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1707,25 +1703,25 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>3541</v>
+        <v>3627</v>
       </c>
       <c r="C41" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D41" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E41" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1739,25 +1735,25 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>3500</v>
+        <v>3617</v>
       </c>
       <c r="C42" t="n">
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E42" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1771,30 +1767,30 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>3497</v>
+        <v>3597</v>
       </c>
       <c r="C43" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E43" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -1803,30 +1799,30 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>3492</v>
+        <v>3593</v>
       </c>
       <c r="C44" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D44" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E44" t="n">
         <v>90</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>WIL1610</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -1835,25 +1831,25 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>3481</v>
+        <v>3589</v>
       </c>
       <c r="C45" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D45" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E45" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>Camillewbl</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -1867,30 +1863,30 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>3474</v>
+        <v>3585</v>
       </c>
       <c r="C46" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D46" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E46" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>William</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>WIL1610</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -1899,30 +1895,30 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>3467</v>
+        <v>3574</v>
       </c>
       <c r="C47" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D47" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E47" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>Melissagzb</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -1931,16 +1927,16 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>3456</v>
+        <v>3549</v>
       </c>
       <c r="C48" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D48" t="n">
         <v>8</v>
       </c>
       <c r="E48" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1963,58 +1959,62 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>3452</v>
+        <v>3541</v>
       </c>
       <c r="C49" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E49" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fa_One</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Anais757817</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>3443</v>
+        <v>3510</v>
       </c>
       <c r="C50" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D50" t="n">
         <v>11</v>
       </c>
       <c r="E50" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2023,30 +2023,30 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>3436</v>
+        <v>3500</v>
       </c>
       <c r="C51" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D51" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E51" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>MxKnight</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2055,30 +2055,30 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>3417</v>
+        <v>3498</v>
       </c>
       <c r="C52" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D52" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E52" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2087,30 +2087,30 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>3405</v>
+        <v>3484</v>
       </c>
       <c r="C53" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D53" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E53" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>MatuRenard</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -2119,30 +2119,30 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>3391</v>
+        <v>3468</v>
       </c>
       <c r="C54" t="n">
         <v>55</v>
       </c>
       <c r="D54" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E54" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t xml:space="preserve">Liliane </t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
+          <t>LilianeB</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2151,30 +2151,30 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>3388</v>
+        <v>3466</v>
       </c>
       <c r="C55" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D55" t="n">
         <v>9</v>
       </c>
       <c r="E55" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -2183,25 +2183,25 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>3386</v>
+        